--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -87,10 +87,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ApplyTarget</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>!SkillApplyTarget</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1321,10 +1317,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>!int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1367,9 +1359,6 @@
   </si>
   <si>
     <t>OnHit</t>
-  </si>
-  <si>
-    <t>OnHit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1389,10 +1378,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CastingParam</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1418,10 +1403,6 @@
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1490,6 +1471,26 @@
   </si>
   <si>
     <t>Circle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2000,28 +2001,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2041,15 +2042,15 @@
         <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2057,15 +2058,15 @@
         <v>12</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2073,89 +2074,89 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
         <v>177</v>
-      </c>
-      <c r="C17" t="s">
-        <v>178</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" t="s">
         <v>181</v>
-      </c>
-      <c r="C19" t="s">
-        <v>182</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2170,14 +2171,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2186,7 +2187,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2195,7 +2196,7 @@
     <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="13"/>
@@ -2209,77 +2210,77 @@
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="E30" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -2319,7 +2320,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -2330,134 +2331,134 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>196</v>
+        <v>99</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H4" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="4">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K4" s="4">
         <v>0.2</v>
@@ -2466,84 +2467,84 @@
         <v>1</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="F5">
         <v>50</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H5" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K5" s="4">
         <v>0.1</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H6" s="4">
         <v>99999</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H7" s="4">
         <v>99999</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2552,13 +2553,13 @@
         <v>4</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H8" s="4">
         <v>100</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K8" s="4">
         <v>0.3</v>
@@ -2567,15 +2568,15 @@
         <v>1</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2584,13 +2585,13 @@
         <v>4</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H9" s="4">
         <v>100</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K9" s="4">
         <v>0.3</v>
@@ -2599,15 +2600,15 @@
         <v>1</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2616,13 +2617,13 @@
         <v>4</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H10" s="4">
         <v>100</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K10" s="4">
         <v>0.3</v>
@@ -2631,15 +2632,15 @@
         <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2648,13 +2649,13 @@
         <v>4</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H11" s="4">
         <v>100</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K11" s="4">
         <v>0.3</v>
@@ -2663,15 +2664,15 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2680,13 +2681,13 @@
         <v>4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H12" s="4">
         <v>100</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K12" s="4">
         <v>0.3</v>
@@ -2695,15 +2696,15 @@
         <v>1</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -2712,13 +2713,13 @@
         <v>4</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H13" s="4">
         <v>100</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K13" s="4">
         <v>0.3</v>
@@ -2727,47 +2728,47 @@
         <v>1</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H14" s="4">
         <v>100</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K14" s="4">
         <v>0.1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2776,53 +2777,53 @@
         <v>4</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H15" s="4">
         <v>99999</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H16" s="4">
         <v>99999</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H17" s="4">
         <v>99999</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2851,7 +2852,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -2865,51 +2866,51 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="K2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>6</v>
@@ -2935,25 +2936,25 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="G4" s="4">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
@@ -2961,25 +2962,25 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G5" s="4">
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -2987,25 +2988,25 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G6" s="4">
         <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -3013,25 +3014,25 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G7" s="4">
         <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3039,25 +3040,25 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G8" s="4">
         <v>70</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -3065,25 +3066,25 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G9" s="4">
         <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -3091,25 +3092,25 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G10" s="4">
         <v>150</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -3117,25 +3118,25 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G11" s="4">
         <v>200</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -3143,36 +3144,36 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H13" s="4">
         <v>20</v>
@@ -3180,36 +3181,36 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="4">
         <v>30</v>
@@ -3217,19 +3218,19 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H16" s="4">
         <v>2</v>
@@ -3240,36 +3241,36 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="F17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H18" s="4">
         <v>200</v>
@@ -3277,19 +3278,19 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H19" s="4">
         <v>100</v>
@@ -3297,36 +3298,36 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="4">
         <v>20</v>
@@ -3334,25 +3335,25 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="4">
         <v>200</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I22" s="4">
         <v>2</v>
@@ -3383,97 +3384,97 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3498,10 +3499,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3509,39 +3510,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="F2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3549,19 +3550,19 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3569,10 +3570,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3580,10 +3581,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3591,13 +3592,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3605,16 +3606,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="235">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1301,10 +1301,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>!SkillScanType</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1491,6 +1487,14 @@
   </si>
   <si>
     <t>ApplyTarget</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1968,7 +1972,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2001,28 +2005,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2047,7 +2051,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>20</v>
@@ -2091,13 +2095,13 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>178</v>
@@ -2171,14 +2175,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2187,7 +2191,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2196,7 +2200,7 @@
     <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="13"/>
@@ -2230,7 +2234,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
@@ -2334,28 +2338,28 @@
         <v>38</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>24</v>
@@ -2393,13 +2397,13 @@
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>99</v>
@@ -2408,10 +2412,10 @@
         <v>100</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>22</v>
@@ -2437,7 +2441,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>104</v>
+        <v>233</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>157</v>
@@ -2458,7 +2462,7 @@
         <v>120</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K4" s="4">
         <v>0.2</v>
@@ -2467,36 +2471,36 @@
         <v>1</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F5">
         <v>50</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H5" s="4">
         <v>0.5</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K5" s="4">
         <v>0.1</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -2507,10 +2511,10 @@
         <v>54</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H6" s="4">
         <v>99999</v>
@@ -2527,10 +2531,10 @@
         <v>75</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H7" s="4">
         <v>99999</v>
@@ -2553,13 +2557,13 @@
         <v>4</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H8" s="4">
         <v>100</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K8" s="4">
         <v>0.3</v>
@@ -2585,13 +2589,13 @@
         <v>4</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H9" s="4">
         <v>100</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K9" s="4">
         <v>0.3</v>
@@ -2617,13 +2621,13 @@
         <v>4</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H10" s="4">
         <v>100</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K10" s="4">
         <v>0.3</v>
@@ -2649,13 +2653,13 @@
         <v>4</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H11" s="4">
         <v>100</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K11" s="4">
         <v>0.3</v>
@@ -2681,13 +2685,13 @@
         <v>4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H12" s="4">
         <v>100</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K12" s="4">
         <v>0.3</v>
@@ -2713,13 +2717,13 @@
         <v>4</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H13" s="4">
         <v>100</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K13" s="4">
         <v>0.3</v>
@@ -2742,19 +2746,19 @@
         <v>5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H14" s="4">
         <v>100</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K14" s="4">
         <v>0.1</v>
@@ -2777,7 +2781,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H15" s="4">
         <v>99999</v>
@@ -2797,7 +2801,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H16" s="4">
         <v>99999</v>
@@ -2817,7 +2821,7 @@
         <v>4</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H17" s="4">
         <v>99999</v>
@@ -2866,10 +2870,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>124</v>
@@ -2907,7 +2911,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>32</v>
@@ -2945,7 +2949,7 @@
         <v>55</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>56</v>
@@ -2971,7 +2975,7 @@
         <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>56</v>
@@ -2997,7 +3001,7 @@
         <v>55</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>56</v>
@@ -3023,7 +3027,7 @@
         <v>55</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>56</v>
@@ -3049,7 +3053,7 @@
         <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>56</v>
@@ -3075,7 +3079,7 @@
         <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>56</v>
@@ -3101,7 +3105,7 @@
         <v>55</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>56</v>
@@ -3127,7 +3131,7 @@
         <v>55</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>56</v>
@@ -3335,16 +3339,16 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>15</v>
@@ -3353,7 +3357,7 @@
         <v>200</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I22" s="4">
         <v>2</v>
@@ -3556,7 +3560,7 @@
         <v>104</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>105</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -1972,7 +1972,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2465,7 +2465,7 @@
         <v>196</v>
       </c>
       <c r="K4" s="4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L4" s="4" t="b">
         <v>1</v>
@@ -2495,9 +2495,6 @@
       </c>
       <c r="J5" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0.1</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>219</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="241">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -245,10 +245,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MontagePath</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Effect</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1495,6 +1491,34 @@
   </si>
   <si>
     <t>ScanType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-blue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RootVFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1972,7 +1996,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2005,28 +2029,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2051,7 +2075,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>20</v>
@@ -2067,7 +2091,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>21</v>
@@ -2078,89 +2102,89 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>175</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
         <v>176</v>
-      </c>
-      <c r="C17" t="s">
-        <v>177</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" t="s">
         <v>180</v>
-      </c>
-      <c r="C19" t="s">
-        <v>181</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2175,14 +2199,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2191,7 +2215,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2200,7 +2224,7 @@
     <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="13"/>
@@ -2226,15 +2250,15 @@
         <v>15</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>30</v>
@@ -2245,13 +2269,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="E30" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2259,10 +2283,10 @@
         <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2270,21 +2294,21 @@
         <v>17</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -2305,7 +2329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2314,20 +2338,21 @@
     <col min="4" max="4" width="15" style="4" customWidth="1"/>
     <col min="5" max="11" width="23.75" style="4" customWidth="1"/>
     <col min="12" max="12" width="14.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="22" style="4" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="4"/>
+    <col min="13" max="13" width="14.25" style="4" customWidth="1"/>
+    <col min="14" max="14" width="34.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="22" style="4" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2335,90 +2360,93 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>193</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>22</v>
@@ -2438,13 +2466,16 @@
       <c r="S3" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" s="4">
         <v>0.2</v>
@@ -2453,7 +2484,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H4" s="4">
         <v>0.5</v>
@@ -2462,7 +2493,7 @@
         <v>120</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K4" s="4">
         <v>0.1</v>
@@ -2470,82 +2501,85 @@
       <c r="L4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N4" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F5">
         <v>50</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H5" s="4">
         <v>0.5</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H6" s="4">
         <v>99999</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H7" s="4">
         <v>99999</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N7" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2554,13 +2588,13 @@
         <v>4</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H8" s="4">
         <v>100</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K8" s="4">
         <v>0.3</v>
@@ -2568,16 +2602,16 @@
       <c r="L8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N8" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2586,13 +2620,13 @@
         <v>4</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H9" s="4">
         <v>100</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K9" s="4">
         <v>0.3</v>
@@ -2600,16 +2634,16 @@
       <c r="L9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N9" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2618,13 +2652,13 @@
         <v>4</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H10" s="4">
         <v>100</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K10" s="4">
         <v>0.3</v>
@@ -2632,16 +2666,16 @@
       <c r="L10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N10" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2650,13 +2684,13 @@
         <v>4</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H11" s="4">
         <v>100</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K11" s="4">
         <v>0.3</v>
@@ -2664,16 +2698,16 @@
       <c r="L11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N11" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2682,13 +2716,13 @@
         <v>4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H12" s="4">
         <v>100</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K12" s="4">
         <v>0.3</v>
@@ -2696,16 +2730,16 @@
       <c r="L12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N12" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -2714,13 +2748,13 @@
         <v>4</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H13" s="4">
         <v>100</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K13" s="4">
         <v>0.3</v>
@@ -2728,48 +2762,48 @@
       <c r="L13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N13" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H14" s="4">
         <v>100</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K14" s="4">
         <v>0.1</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N14" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2778,53 +2812,53 @@
         <v>4</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H15" s="4">
         <v>99999</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N15" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H16" s="4">
         <v>99999</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="N16" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H17" s="4">
         <v>99999</v>
       </c>
-      <c r="M17" s="4" t="s">
-        <v>70</v>
+      <c r="N17" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2836,30 +2870,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="51" style="4" customWidth="1"/>
     <col min="3" max="3" width="40.125" style="4" customWidth="1"/>
-    <col min="4" max="5" width="17.375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="23.125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="32.25" style="4" customWidth="1"/>
-    <col min="8" max="8" width="29.375" style="4" customWidth="1"/>
-    <col min="9" max="11" width="13.875" style="4" customWidth="1"/>
-    <col min="12" max="13" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="4"/>
+    <col min="4" max="6" width="17.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="23.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="32.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="29.375" style="4" customWidth="1"/>
+    <col min="10" max="12" width="13.875" style="4" customWidth="1"/>
+    <col min="13" max="14" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2867,37 +2901,40 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>124</v>
+        <v>238</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="I2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2908,13 +2945,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>6</v>
@@ -2934,429 +2971,438 @@
       <c r="M3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="H4" s="4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="4">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="4">
+        <v>30</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="4">
+        <v>70</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="4">
+        <v>30</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="4">
+        <v>150</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="4">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="4">
+        <v>200</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="4">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="4">
-        <v>20</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="4">
-        <v>30</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="4">
-        <v>70</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="4">
-        <v>30</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I9" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="4">
-        <v>150</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="4">
-        <v>200</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H12" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="G13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="4">
+        <v>137</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H14" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="H15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="4">
+      <c r="H16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="4">
         <v>2</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H18" s="4">
+      <c r="H18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="4">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H19" s="4">
+      <c r="H19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H21" s="4">
+        <v>66</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="4">
+        <v>200</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4">
-        <v>200</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="I22" s="4">
+      <c r="J22" s="4">
         <v>2</v>
       </c>
     </row>
@@ -3385,41 +3431,41 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>22</v>
@@ -3430,52 +3476,52 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3500,10 +3546,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3511,39 +3557,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="F2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3551,19 +3597,19 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3571,10 +3617,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3582,10 +3628,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3593,13 +3639,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3607,16 +3653,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -1996,7 +1996,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2874,8 +2874,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="51" style="4" customWidth="1"/>
-    <col min="3" max="3" width="40.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="37.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.75" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="17.375" style="4" customWidth="1"/>
     <col min="7" max="7" width="23.125" style="4" customWidth="1"/>
     <col min="8" max="8" width="32.25" style="4" customWidth="1"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="249">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1520,6 +1520,37 @@
   <si>
     <t>SkillVFX</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RootSFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_hit_finisher_52</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2339,12 +2370,13 @@
     <col min="5" max="11" width="23.75" style="4" customWidth="1"/>
     <col min="12" max="12" width="14.25" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.25" style="4" customWidth="1"/>
-    <col min="14" max="14" width="34.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="22" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="4"/>
+    <col min="14" max="14" width="19.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="22" style="4" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2352,7 +2384,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2390,28 +2422,31 @@
         <v>240</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>129</v>
       </c>
@@ -2449,7 +2484,7 @@
         <v>234</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="O3" s="4" t="s">
         <v>22</v>
@@ -2469,8 +2504,11 @@
       <c r="T3" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>232</v>
       </c>
@@ -2501,11 +2539,11 @@
       <c r="L4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>225</v>
       </c>
@@ -2531,10 +2569,13 @@
         <v>239</v>
       </c>
       <c r="N5" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>104</v>
       </c>
@@ -2550,11 +2591,11 @@
       <c r="H6" s="4">
         <v>99999</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>73</v>
       </c>
@@ -2570,11 +2611,11 @@
       <c r="H7" s="4">
         <v>99999</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>152</v>
       </c>
@@ -2602,11 +2643,11 @@
       <c r="L8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>153</v>
       </c>
@@ -2634,11 +2675,11 @@
       <c r="L9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>154</v>
       </c>
@@ -2666,11 +2707,11 @@
       <c r="L10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>145</v>
       </c>
@@ -2698,11 +2739,11 @@
       <c r="L11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>155</v>
       </c>
@@ -2730,11 +2771,11 @@
       <c r="L12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="O12" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>148</v>
       </c>
@@ -2762,11 +2803,11 @@
       <c r="L13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="O13" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>150</v>
       </c>
@@ -2794,11 +2835,11 @@
       <c r="K14" s="4">
         <v>0.1</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="O14" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>130</v>
       </c>
@@ -2817,11 +2858,11 @@
       <c r="H15" s="4">
         <v>99999</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="O15" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>131</v>
       </c>
@@ -2837,11 +2878,11 @@
       <c r="H16" s="4">
         <v>99999</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="O16" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>76</v>
       </c>
@@ -2857,7 +2898,7 @@
       <c r="H17" s="4">
         <v>99999</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="O17" s="4" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2870,22 +2911,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="37.25" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.75" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="17.375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="23.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="32.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="29.375" style="4" customWidth="1"/>
-    <col min="10" max="12" width="13.875" style="4" customWidth="1"/>
-    <col min="13" max="14" width="13.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="4"/>
+    <col min="7" max="7" width="19.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="32.25" style="4" customWidth="1"/>
+    <col min="10" max="10" width="29.375" style="4" customWidth="1"/>
+    <col min="11" max="13" width="13.875" style="4" customWidth="1"/>
+    <col min="14" max="15" width="13.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
@@ -2893,7 +2935,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2910,31 +2952,34 @@
         <v>238</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2951,10 +2996,10 @@
         <v>234</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -2974,8 +3019,11 @@
       <c r="N3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>87</v>
       </c>
@@ -2992,19 +3040,22 @@
         <v>235</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>10</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>164</v>
       </c>
@@ -3017,20 +3068,20 @@
       <c r="E5" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <v>10</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>165</v>
       </c>
@@ -3043,20 +3094,20 @@
       <c r="E6" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>20</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>166</v>
       </c>
@@ -3069,20 +3120,20 @@
       <c r="E7" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>30</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>167</v>
       </c>
@@ -3095,20 +3146,20 @@
       <c r="E8" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>70</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>168</v>
       </c>
@@ -3121,20 +3172,20 @@
       <c r="E9" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>30</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>170</v>
       </c>
@@ -3147,20 +3198,20 @@
       <c r="E10" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>150</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>171</v>
       </c>
@@ -3173,20 +3224,20 @@
       <c r="E11" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>200</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>72</v>
       </c>
@@ -3196,14 +3247,14 @@
       <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>68</v>
       </c>
@@ -3213,17 +3264,17 @@
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I13" s="4">
+      <c r="J13" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>78</v>
       </c>
@@ -3233,14 +3284,14 @@
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>79</v>
       </c>
@@ -3250,17 +3301,17 @@
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>133</v>
       </c>
@@ -3270,20 +3321,20 @@
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>2</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>134</v>
       </c>
@@ -3293,14 +3344,14 @@
       <c r="D17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>67</v>
       </c>
@@ -3310,17 +3361,17 @@
       <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I18" s="4">
+      <c r="J18" s="4">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>83</v>
       </c>
@@ -3330,17 +3381,17 @@
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I19" s="4">
+      <c r="J19" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>69</v>
       </c>
@@ -3350,14 +3401,14 @@
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>71</v>
       </c>
@@ -3367,17 +3418,17 @@
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="H21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I21" s="4">
+      <c r="J21" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>224</v>
       </c>
@@ -3394,15 +3445,18 @@
         <v>237</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="4">
+      <c r="I22" s="4">
         <v>200</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="J22" s="4">
+      <c r="K22" s="4">
         <v>2</v>
       </c>
     </row>
@@ -3414,19 +3468,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="32" style="4" customWidth="1"/>
     <col min="3" max="3" width="44" style="4" customWidth="1"/>
-    <col min="4" max="5" width="18.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="30.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="4" max="6" width="18.625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3434,7 +3488,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>102</v>
       </c>
@@ -3448,13 +3502,16 @@
         <v>236</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>126</v>
       </c>
@@ -3468,35 +3525,38 @@
         <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>245</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>92</v>
       </c>
@@ -3506,21 +3566,21 @@
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>86</v>
       </c>
     </row>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="255">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1238,11 +1238,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Chain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전이되는 스킬</t>
+    <t>!SkillScanType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1266,69 +1274,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 전이횟수 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 전이 가능 거리</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> : 사정거리</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1482,10 +1427,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>!string</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1579,6 +1520,18 @@
   <si>
     <t>SkillEffectTypes</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2063,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2088,28 +2041,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2134,7 +2087,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -2178,13 +2131,13 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>176</v>
@@ -2235,37 +2188,33 @@
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
-      <c r="B20" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>187</v>
-      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="13"/>
-      <c r="E20" s="9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" s="6"/>
+      <c r="B21" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2273,125 +2222,116 @@
     </row>
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
-      <c r="B24" s="4" t="s">
-        <v>212</v>
+      <c r="B24" t="s">
+        <v>210</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" t="s">
-        <v>213</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="8" t="s">
+      <c r="B26" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="8" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D35" s="6"/>
+      <c r="B34" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F37"/>
+        <v>241</v>
+      </c>
+      <c r="F36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2402,24 +2342,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="36.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="19.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="4" customWidth="1"/>
-    <col min="5" max="11" width="23.75" style="4" customWidth="1"/>
-    <col min="12" max="12" width="14.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="4" customWidth="1"/>
-    <col min="14" max="14" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="22" style="4" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="4"/>
+    <col min="4" max="5" width="15" style="4" customWidth="1"/>
+    <col min="6" max="12" width="23.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.25" style="4" customWidth="1"/>
+    <col min="15" max="15" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="22" style="4" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2427,7 +2367,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2438,61 +2378,64 @@
         <v>36</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="P2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>128</v>
       </c>
@@ -2503,40 +2446,40 @@
         <v>97</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>208</v>
-      </c>
       <c r="M3" s="4" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>21</v>
@@ -2556,10 +2499,13 @@
       <c r="V3" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W3" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>155</v>
@@ -2567,107 +2513,110 @@
       <c r="D4" s="4">
         <v>0.2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>0.5</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>120</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K4" s="4">
+      <c r="K4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L4" s="4">
         <v>0.1</v>
       </c>
-      <c r="L4" s="4" t="b">
+      <c r="M4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q4" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F5">
+      <c r="G5">
         <v>50</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="H5" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I5" s="4">
         <v>0.5</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>236</v>
+      <c r="K5" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="F6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="4">
         <v>99999</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="F7" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="4">
         <v>99999</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>151</v>
       </c>
@@ -2677,29 +2626,29 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H8" s="4">
-        <v>100</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K8" s="4">
+      <c r="H8" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L8" s="4">
         <v>0.3</v>
       </c>
-      <c r="L8" s="4" t="b">
+      <c r="M8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>152</v>
       </c>
@@ -2709,29 +2658,29 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="4">
-        <v>100</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K9" s="4">
+      <c r="H9" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L9" s="4">
         <v>0.3</v>
       </c>
-      <c r="L9" s="4" t="b">
+      <c r="M9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="Q9" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>153</v>
       </c>
@@ -2741,29 +2690,29 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H10" s="4">
-        <v>100</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K10" s="4">
+      <c r="H10" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L10" s="4">
         <v>0.3</v>
       </c>
-      <c r="L10" s="4" t="b">
+      <c r="M10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>144</v>
       </c>
@@ -2773,29 +2722,29 @@
       <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H11" s="4">
-        <v>100</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="H11" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L11" s="4">
         <v>0.3</v>
       </c>
-      <c r="L11" s="4" t="b">
+      <c r="M11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>154</v>
       </c>
@@ -2805,29 +2754,29 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H12" s="4">
-        <v>100</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K12" s="4">
+      <c r="H12" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L12" s="4">
         <v>0.3</v>
       </c>
-      <c r="L12" s="4" t="b">
+      <c r="M12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="Q12" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>147</v>
       </c>
@@ -2837,29 +2786,29 @@
       <c r="D13" s="4">
         <v>3</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H13" s="4">
-        <v>100</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K13" s="4">
+      <c r="H13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L13" s="4">
         <v>0.3</v>
       </c>
-      <c r="L13" s="4" t="b">
+      <c r="M13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="Q13" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>149</v>
       </c>
@@ -2869,29 +2818,29 @@
       <c r="D14" s="4">
         <v>5</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="F14" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="4">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="H14" s="4">
-        <v>100</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="K14" s="4">
+      <c r="L14" s="4">
         <v>0.1</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="Q14" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>129</v>
       </c>
@@ -2901,56 +2850,56 @@
       <c r="D15" s="4">
         <v>5</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="H15" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I15" s="4">
         <v>99999</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H16" s="4">
+      <c r="H16" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I16" s="4">
         <v>99999</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="H17" s="4">
+      <c r="H17" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="4">
         <v>99999</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="Q17" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2995,16 +2944,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>122</v>
@@ -3042,13 +2991,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>31</v>
@@ -3086,13 +3035,13 @@
         <v>53</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>54</v>
@@ -3118,7 +3067,7 @@
         <v>53</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>54</v>
@@ -3144,7 +3093,7 @@
         <v>53</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>54</v>
@@ -3170,7 +3119,7 @@
         <v>53</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>54</v>
@@ -3196,7 +3145,7 @@
         <v>53</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>54</v>
@@ -3222,7 +3171,7 @@
         <v>53</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>54</v>
@@ -3248,7 +3197,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>54</v>
@@ -3274,10 +3223,10 @@
         <v>53</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I11" s="4">
         <v>200</v>
@@ -3482,31 +3431,31 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="4">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
@@ -3551,13 +3500,13 @@
         <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>33</v>
@@ -3580,10 +3529,10 @@
         <v>100</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>21</v>
@@ -3600,7 +3549,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>67</v>
@@ -3614,7 +3563,7 @@
         <v>79</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>78</v>
@@ -3631,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>69</v>
@@ -3645,7 +3594,7 @@
         <v>62</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>81</v>
@@ -3733,7 +3682,7 @@
         <v>102</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>103</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="258">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -500,6 +500,473 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>포션 사용 버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 감소 효과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 감소 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecreaseAttribute</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_HP_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>패시브2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포션1 사용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SLOW_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈진 상태</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_ATTACKSPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도 증가 버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도 증가 효과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_HP_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_HP_INTERVAL_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 회복 지속효과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_HP_INTERVAL_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_POTION_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_POTION_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_ATTACKSPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_ATTACKSPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 캐릭터 스킬세트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>버섯 몬스터 스킬세트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 몬스터 스킬세트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 몬스터 스킬세트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마 몬스터 스킬세트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!BuffInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_USE_POSTION_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_USE_SCROLL_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크롤1 사용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_POTION_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_SCROLL_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크롤 사용 버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MUSHROOM_ATTACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_GOBLIN_ATTACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DEMON_ATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DEMON_ATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_DEMON_ATTACK_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DEMON_ATTACK_03</t>
+  </si>
+  <si>
+    <t>SKILL_DEMON_ATTACK_03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MUSHROOM_ATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_GOBLIN_ATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DEMON_ATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>버섯 몬스터 공격1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 몬스터 공격1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 몬스터 공격1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 몬스터 공격2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마 몬스터 공격1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마 몬스터 공격2</t>
+  </si>
+  <si>
+    <t>악마 몬스터 공격3</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_06</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_07</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_08</t>
+  </si>
+  <si>
+    <t>SkillScanType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>타겟팅스킬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부채꼴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>원형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Donut</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>도넛 모양</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>직선 궤적</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -510,7 +977,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_1]</t>
+      <t>[ScanParam_1]</t>
     </r>
     <r>
       <rPr>
@@ -520,19 +987,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 기본데미지 </t>
-    </r>
+      <t xml:space="preserve"> : 반지름</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
+        <color theme="8"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_2]</t>
+      <t>[ScanParam_1]</t>
     </r>
     <r>
       <rPr>
@@ -542,7 +1012,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 데미지 계수 속성 </t>
+      <t xml:space="preserve"> : 반지름 </t>
     </r>
     <r>
       <rPr>
@@ -554,7 +1024,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_3]</t>
+      <t>[Param_2]</t>
     </r>
     <r>
       <rPr>
@@ -564,499 +1034,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 데미지 계수값</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>포션 사용 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도 감소 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DecreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_HP_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>패시브2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>포션1 사용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SLOW_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>탈진 상태</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격속도 증가 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격속도 증가 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_HP_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_HP_INTERVAL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 회복 지속효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_HP_INTERVAL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 캐릭터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!BuffInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_USE_POSTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_USE_SCROLL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스크롤1 사용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_SCROLL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스크롤 사용 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MUSHROOM_ATTACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_GOBLIN_ATTACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_03</t>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MUSHROOM_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_GOBLIN_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 몬스터 공격2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 몬스터 공격2</t>
-  </si>
-  <si>
-    <t>악마 몬스터 공격3</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_03</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_06</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_07</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_08</t>
-  </si>
-  <si>
-    <t>SkillScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타겟팅스킬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sector</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부채꼴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>원형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Donut</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>도넛 모양</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>직선 궤적</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> : 각도</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
+        <color theme="4" tint="-0.249977111117893"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 반지름</t>
+      <t/>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1081,7 +1071,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 반지름 </t>
+      <t xml:space="preserve"> : 길이 </t>
     </r>
     <r>
       <rPr>
@@ -1103,7 +1093,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 각도</t>
+      <t xml:space="preserve"> : 너비</t>
     </r>
     <r>
       <rPr>
@@ -1140,7 +1130,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 길이 </t>
+      <t xml:space="preserve"> : 외경 </t>
     </r>
     <r>
       <rPr>
@@ -1162,7 +1152,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 너비</t>
+      <t xml:space="preserve"> : 내경</t>
     </r>
     <r>
       <rPr>
@@ -1179,6 +1169,22 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>!SkillScanType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1199,19 +1205,289 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 외경 </t>
-    </r>
+      <t xml:space="preserve"> : 사정거리</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시 적용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingParam</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시발동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionEffectTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillDamageType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 데미지 효과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-blue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_hit_finisher_52</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>Root</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFXAnchor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillAnchorType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFXAnchor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAnchorType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectTypes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraShake</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shake_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
+        <color theme="8"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_2]</t>
+      <t>[Param_1]</t>
     </r>
     <r>
       <rPr>
@@ -1221,7 +1497,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 내경</t>
+      <t xml:space="preserve"> : 기본데미지 </t>
     </r>
     <r>
       <rPr>
@@ -1233,38 +1509,29 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 데미지 계수 속성 </t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
+        <color theme="4" tint="-0.249977111117893"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[ScanParam_1]</t>
+      <t>[Param_3]</t>
     </r>
     <r>
       <rPr>
@@ -1274,263 +1541,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 사정거리</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>상시 적용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingParam</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉시발동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionEffectTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillDamageType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 데미지 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hit-blue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>Root</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFXAnchor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillAnchorType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillAnchorType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ApplyTarget</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffectTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
+      <t xml:space="preserve"> : 데미지 계수값 [Param_4] : 브레이크데미지 배율</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2041,28 +2053,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2087,7 +2099,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -2114,76 +2126,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" t="s">
         <v>174</v>
-      </c>
-      <c r="C17" t="s">
-        <v>175</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" t="s">
         <v>178</v>
-      </c>
-      <c r="C19" t="s">
-        <v>179</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2198,14 +2210,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2214,7 +2226,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2223,7 +2235,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2237,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
@@ -2249,15 +2261,15 @@
         <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>29</v>
@@ -2318,18 +2330,18 @@
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F36"/>
     </row>
@@ -2342,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2354,20 +2366,21 @@
     <col min="14" max="14" width="14.25" style="4" customWidth="1"/>
     <col min="15" max="15" width="16.25" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="22" style="4" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="4"/>
+    <col min="17" max="17" width="19.375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="34.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="22" style="4" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2378,111 +2391,114 @@
         <v>36</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2502,13 +2518,16 @@
       <c r="W3" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D4" s="4">
         <v>0.2</v>
@@ -2520,7 +2539,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2529,7 +2548,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2537,91 +2556,94 @@
       <c r="M4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R4" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I5" s="4">
         <v>0.5</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I6" s="4">
         <v>99999</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="R6" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I7" s="4">
         <v>99999</v>
       </c>
-      <c r="Q7" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R7" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2630,13 +2652,13 @@
         <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L8" s="4">
         <v>0.3</v>
@@ -2644,16 +2666,16 @@
       <c r="M8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R8" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2662,13 +2684,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L9" s="4">
         <v>0.3</v>
@@ -2676,16 +2698,16 @@
       <c r="M9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R9" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2694,13 +2716,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -2708,16 +2730,16 @@
       <c r="M10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R10" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2726,13 +2748,13 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L11" s="4">
         <v>0.3</v>
@@ -2740,16 +2762,16 @@
       <c r="M11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R11" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2758,13 +2780,13 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L12" s="4">
         <v>0.3</v>
@@ -2772,16 +2794,16 @@
       <c r="M12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R12" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -2790,13 +2812,13 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L13" s="4">
         <v>0.3</v>
@@ -2804,48 +2826,48 @@
       <c r="M13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R13" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G14" s="4">
         <v>2</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L14" s="4">
         <v>0.1</v>
       </c>
-      <c r="Q14" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R14" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2854,53 +2876,53 @@
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
-      <c r="Q15" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="R15" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I16" s="4">
         <v>99999</v>
       </c>
-      <c r="Q16" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="R16" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I17" s="4">
         <v>99999</v>
       </c>
-      <c r="Q17" s="4" t="s">
-        <v>68</v>
+      <c r="R17" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2930,7 +2952,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -2944,25 +2966,25 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>26</v>
@@ -2971,13 +2993,13 @@
         <v>27</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -2991,13 +3013,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>31</v>
@@ -3026,7 +3048,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>59</v>
@@ -3035,13 +3057,13 @@
         <v>53</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>54</v>
@@ -3050,7 +3072,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3058,16 +3080,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>54</v>
@@ -3076,7 +3098,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -3084,16 +3106,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>54</v>
@@ -3102,7 +3124,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3110,16 +3132,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>54</v>
@@ -3128,7 +3150,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3136,16 +3158,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>54</v>
@@ -3154,7 +3176,7 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3162,16 +3184,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>54</v>
@@ -3180,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3188,16 +3210,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>54</v>
@@ -3206,7 +3228,7 @@
         <v>150</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3214,25 +3236,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I11" s="4">
         <v>200</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3240,7 +3262,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>56</v>
@@ -3252,12 +3274,12 @@
         <v>28</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>58</v>
@@ -3266,10 +3288,10 @@
         <v>11</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J13" s="4">
         <v>20</v>
@@ -3277,10 +3299,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
@@ -3289,15 +3311,15 @@
         <v>28</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3306,7 +3328,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J15" s="4">
         <v>30</v>
@@ -3314,10 +3336,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
@@ -3326,7 +3348,7 @@
         <v>28</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J16" s="4">
         <v>2</v>
@@ -3337,24 +3359,24 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="H17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>60</v>
@@ -3366,7 +3388,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J18" s="4">
         <v>200</v>
@@ -3374,10 +3396,10 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
@@ -3386,7 +3408,7 @@
         <v>15</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J19" s="4">
         <v>100</v>
@@ -3394,10 +3416,10 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
@@ -3406,24 +3428,24 @@
         <v>57</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J21" s="4">
         <v>20</v>
@@ -3431,22 +3453,22 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
@@ -3455,7 +3477,7 @@
         <v>25</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
@@ -3486,12 +3508,12 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
@@ -3500,39 +3522,39 @@
         <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>21</v>
@@ -3543,35 +3565,35 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>50</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>51</v>
@@ -3580,27 +3602,27 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3625,10 +3647,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3636,39 +3658,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="F2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3676,19 +3698,19 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3696,10 +3718,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3707,10 +3729,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3718,13 +3740,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3732,16 +3754,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="275">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -256,10 +256,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>IsDebuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Effect_3</t>
   </si>
   <si>
@@ -271,10 +267,6 @@
   </si>
   <si>
     <t>스탯 감소(Target은 Self만 가능)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateAura</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -484,10 +476,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>이동속도 증가 효과</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -551,14 +539,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_SLOW_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>탈진 상태</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -619,10 +599,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>EffectParam_5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -635,11 +611,55 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>!float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>BUFF_MOVESPEED_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>!float</t>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -647,54 +667,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Desc</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -732,10 +704,6 @@
   </si>
   <si>
     <t>데미지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1473,10 +1441,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Shake_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1543,6 +1507,110 @@
       </rPr>
       <t xml:space="preserve"> : 데미지 계수값 [Param_4] : 브레이크데미지 배율</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_POTION_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_BREAK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy-hit-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태이상 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동불가 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DREAK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_STUN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_SILENCE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_BINDING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDebuff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2020,7 +2088,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2053,28 +2121,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2099,7 +2167,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -2115,7 +2183,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>20</v>
@@ -2126,76 +2194,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2210,14 +2278,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2226,7 +2294,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2235,7 +2303,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2249,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
@@ -2261,15 +2329,15 @@
         <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>29</v>
@@ -2280,13 +2348,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2294,10 +2362,10 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2305,21 +2373,21 @@
         <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>42</v>
+        <v>265</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2330,18 +2398,18 @@
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F36"/>
     </row>
@@ -2377,7 +2445,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2391,43 +2459,43 @@
         <v>36</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>23</v>
@@ -2442,10 +2510,10 @@
         <v>22</v>
       </c>
       <c r="V2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>24</v>
@@ -2453,52 +2521,52 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2524,10 +2592,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D4" s="4">
         <v>0.2</v>
@@ -2539,7 +2607,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2548,7 +2616,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2557,93 +2625,90 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F5" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I5" s="4">
         <v>0.5</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I6" s="4">
         <v>99999</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I7" s="4">
         <v>99999</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2652,13 +2717,13 @@
         <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L8" s="4">
         <v>0.3</v>
@@ -2667,15 +2732,15 @@
         <v>1</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2684,13 +2749,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L9" s="4">
         <v>0.3</v>
@@ -2699,15 +2764,15 @@
         <v>1</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2716,13 +2781,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -2731,15 +2796,15 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2748,13 +2813,13 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L11" s="4">
         <v>0.3</v>
@@ -2763,15 +2828,15 @@
         <v>1</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2780,13 +2845,13 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L12" s="4">
         <v>0.3</v>
@@ -2795,15 +2860,15 @@
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -2812,13 +2877,13 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L13" s="4">
         <v>0.3</v>
@@ -2827,47 +2892,47 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G14" s="4">
         <v>2</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="L14" s="4">
         <v>0.1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2876,53 +2941,65 @@
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I16" s="4">
         <v>99999</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>74</v>
+        <v>249</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="I17" s="4">
         <v>99999</v>
       </c>
+      <c r="N17" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="R17" s="4" t="s">
-        <v>67</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -2934,12 +3011,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="37.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="17.375" style="4" customWidth="1"/>
     <col min="7" max="7" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.125" style="4" customWidth="1"/>
@@ -2952,7 +3029,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -2966,25 +3043,25 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>120</v>
+        <v>273</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>26</v>
@@ -2993,13 +3070,13 @@
         <v>27</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3013,13 +3090,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>31</v>
@@ -3048,31 +3125,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3080,25 +3157,25 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I5" s="4">
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -3106,25 +3183,25 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3132,25 +3209,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3158,25 +3235,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3184,25 +3261,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I9" s="4">
         <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3210,25 +3287,25 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I10" s="4">
         <v>150</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3236,25 +3313,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I11" s="4">
         <v>200</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3262,36 +3339,36 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>95</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J13" s="4">
         <v>20</v>
@@ -3299,10 +3376,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
@@ -3311,15 +3388,15 @@
         <v>28</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3328,7 +3405,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="J15" s="4">
         <v>30</v>
@@ -3336,10 +3413,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
@@ -3348,7 +3425,7 @@
         <v>28</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J16" s="4">
         <v>2</v>
@@ -3359,27 +3436,27 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
@@ -3388,7 +3465,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="J18" s="4">
         <v>200</v>
@@ -3396,10 +3473,10 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
@@ -3408,7 +3485,7 @@
         <v>15</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="J19" s="4">
         <v>100</v>
@@ -3416,36 +3493,36 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>57</v>
+        <v>261</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>91</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="J21" s="4">
         <v>20</v>
@@ -3453,22 +3530,22 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
@@ -3477,10 +3554,30 @@
         <v>25</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="J23" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3491,15 +3588,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="32" style="4" customWidth="1"/>
     <col min="3" max="3" width="44" style="4" customWidth="1"/>
-    <col min="4" max="7" width="18.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="30.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="18.625" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -3508,121 +3606,153 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>33</v>
+        <v>233</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>82</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>235</v>
+        <v>92</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>68</v>
+      <c r="E6" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D8" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" s="4" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3647,10 +3777,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3658,39 +3788,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3698,19 +3828,19 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3718,10 +3848,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3729,10 +3859,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3740,13 +3870,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3754,16 +3884,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="288">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -126,10 +126,6 @@
     <t>Effect_2</t>
   </si>
   <si>
-    <t>StartEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FinishEffect</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -153,10 +149,6 @@
   </si>
   <si>
     <t>EffectType에 따라 EffectParam1~5에 넣을 값이 달라짐.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -245,13 +237,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_1</t>
-  </si>
-  <si>
     <t>CooltimeSec</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -519,10 +504,6 @@
     <t>SE_DECREASE_MOVESPEED_01</t>
   </si>
   <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -592,10 +573,6 @@
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1322,10 +1299,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>!string</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1417,147 +1390,283 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraShake</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_POTION_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy-hit-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동불가 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDebuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 기본데미지 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 데미지 계수 속성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 데미지 계수값  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_5]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 디버프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_KNOCKBACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SkillEffectTypes</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CameraShake</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 기본데미지 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 데미지 계수 속성 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_3]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 데미지 계수값 [Param_4] : 브레이크데미지 배율</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BREAK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_ACTIVATE_BUFF_BREAK_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_KNOCKBACKREGIST_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 감소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>브레이크 디버프</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>브레이크</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashy-hit-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태이상 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Self</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_SILENCE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BINDING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>ActivateBuff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1566,51 +1675,39 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateAura</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스턴 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>침묵 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동불가 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DREAK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_STUN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_SILENCE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_BINDING</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDebuff</t>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_KNOCKBACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짧은기간 넉백 효과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1618,7 +1715,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1678,6 +1775,15 @@
       <b/>
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -2088,7 +2194,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2121,28 +2227,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2167,7 +2273,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -2183,7 +2289,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>20</v>
@@ -2194,76 +2300,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2278,14 +2384,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2294,7 +2400,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2303,7 +2409,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2317,11 +2423,11 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2329,32 +2435,32 @@
         <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2362,10 +2468,10 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2373,21 +2479,21 @@
         <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2398,18 +2504,18 @@
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F36"/>
     </row>
@@ -2445,7 +2551,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2456,117 +2562,117 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>246</v>
-      </c>
       <c r="R2" s="4" t="s">
-        <v>23</v>
+        <v>287</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>35</v>
+        <v>286</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2592,10 +2698,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>218</v>
+        <v>284</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D4" s="4">
         <v>0.2</v>
@@ -2607,7 +2713,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2616,7 +2722,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2625,90 +2731,93 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I5" s="4">
         <v>0.5</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I6" s="4">
         <v>99999</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I7" s="4">
         <v>99999</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2717,13 +2826,13 @@
         <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L8" s="4">
         <v>0.3</v>
@@ -2732,15 +2841,15 @@
         <v>1</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2749,13 +2858,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L9" s="4">
         <v>0.3</v>
@@ -2764,15 +2873,15 @@
         <v>1</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2781,13 +2890,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -2796,15 +2905,15 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2813,13 +2922,13 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L11" s="4">
         <v>0.3</v>
@@ -2828,15 +2937,15 @@
         <v>1</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2845,13 +2954,13 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L12" s="4">
         <v>0.3</v>
@@ -2860,15 +2969,15 @@
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -2877,13 +2986,13 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L13" s="4">
         <v>0.3</v>
@@ -2892,47 +3001,47 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G14" s="4">
         <v>2</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L14" s="4">
         <v>0.1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2941,65 +3050,68 @@
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I16" s="4">
         <v>99999</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I17" s="4">
         <v>99999</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>255</v>
+        <v>264</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3011,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3029,7 +3141,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -3043,40 +3155,40 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3090,16 +3202,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3125,57 +3237,63 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
       </c>
+      <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I5" s="4">
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -3183,25 +3301,25 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3209,25 +3327,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3235,25 +3353,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3261,25 +3379,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I9" s="4">
         <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3287,25 +3405,25 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I10" s="4">
         <v>150</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3313,25 +3431,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I11" s="4">
         <v>200</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3339,36 +3457,36 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J13" s="4">
         <v>20</v>
@@ -3376,27 +3494,27 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3405,7 +3523,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J15" s="4">
         <v>30</v>
@@ -3413,19 +3531,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J16" s="4">
         <v>2</v>
@@ -3434,29 +3552,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
@@ -3465,18 +3583,18 @@
         <v>15</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J18" s="4">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
@@ -3485,67 +3603,67 @@
         <v>15</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J19" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>66</v>
+        <v>265</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J21" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
@@ -3554,30 +3672,76 @@
         <v>25</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="4">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="I23" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="J23" s="4">
-        <v>1</v>
+      <c r="H24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="J24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" s="4">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3588,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3606,44 +3770,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>21</v>
@@ -3652,71 +3816,71 @@
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -3724,10 +3888,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -3735,10 +3899,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -3746,12 +3910,23 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3777,10 +3952,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3788,39 +3963,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3828,19 +4003,19 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3848,10 +4023,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3859,10 +4034,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3870,13 +4045,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3884,16 +4059,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="292">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -137,9 +137,6 @@
     <t>EffectParam_3</t>
   </si>
   <si>
-    <t>EffectParam_4</t>
-  </si>
-  <si>
     <t>ActivateBuff</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -485,10 +482,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DecreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_INCREASE_HP_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1410,10 +1403,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_BREAK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1431,10 +1420,6 @@
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 디버프</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1611,39 +1596,103 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Self</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_SILENCE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BINDING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_KNOCKBACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짧은기간 넉백 효과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 데미지 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크(받는 데미지 증가)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SkillEffectTypes</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_ACTIVATE_BUFF_BREAK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_KNOCKBACKREGIST_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 감소</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
+    <t>EffectParam_4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1651,31 +1700,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_KNOCKBACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_KNOCKBACK</t>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecreaseAttribute</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1683,31 +1716,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_KNOCKBACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>짧은기간 넉백 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_DAMAGETAKEN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2202,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2227,171 +2244,180 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+    <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>201</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B13" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5" t="s">
-        <v>166</v>
+      <c r="D14" s="13"/>
+      <c r="E14" s="9" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
+      </c>
+      <c r="C16" t="s">
+        <v>158</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" t="s">
         <v>160</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" t="s">
         <v>162</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
-      <c r="B19" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" t="s">
-        <v>164</v>
-      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="13"/>
-      <c r="E19" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="6"/>
+      <c r="B20" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2399,73 +2425,75 @@
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
-      <c r="B23" s="4" t="s">
-        <v>194</v>
+      <c r="B23" t="s">
+        <v>193</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="8" t="s">
-        <v>29</v>
+      <c r="B25" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>259</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>35</v>
@@ -2476,48 +2504,37 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>16</v>
+        <v>249</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>36</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D34" s="6"/>
+      <c r="B33" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F36"/>
+        <v>223</v>
+      </c>
+      <c r="F35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2542,7 +2559,9 @@
     <col min="16" max="16" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="4" customWidth="1"/>
     <col min="18" max="18" width="34.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="22" style="4" customWidth="1"/>
+    <col min="19" max="19" width="36.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="22" style="4" customWidth="1"/>
     <col min="25" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2551,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2562,64 +2581,64 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="V2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>23</v>
@@ -2627,52 +2646,52 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>190</v>
-      </c>
       <c r="N3" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2698,10 +2717,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D4" s="4">
         <v>0.2</v>
@@ -2713,7 +2732,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2722,7 +2741,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2731,93 +2750,93 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G5">
         <v>50</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I5" s="4">
         <v>0.5</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I6" s="4">
         <v>99999</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I7" s="4">
         <v>99999</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2826,13 +2845,13 @@
         <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L8" s="4">
         <v>0.3</v>
@@ -2841,15 +2860,15 @@
         <v>1</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2858,13 +2877,13 @@
         <v>4</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L9" s="4">
         <v>0.3</v>
@@ -2873,15 +2892,15 @@
         <v>1</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2890,13 +2909,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -2905,15 +2924,15 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2922,13 +2941,13 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L11" s="4">
         <v>0.3</v>
@@ -2937,15 +2956,15 @@
         <v>1</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2954,13 +2973,13 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L12" s="4">
         <v>0.3</v>
@@ -2969,15 +2988,15 @@
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -2986,13 +3005,13 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L13" s="4">
         <v>0.3</v>
@@ -3001,47 +3020,47 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D14" s="4">
         <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G14" s="4">
         <v>2</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L14" s="4">
         <v>0.1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -3050,68 +3069,68 @@
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I16" s="4">
         <v>99999</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I17" s="4">
         <v>99999</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3123,12 +3142,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="37.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.75" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="17.375" style="4" customWidth="1"/>
     <col min="7" max="7" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.125" style="4" customWidth="1"/>
@@ -3141,7 +3160,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -3155,40 +3174,40 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>217</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>26</v>
+        <v>283</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3202,16 +3221,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3237,31 +3256,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3275,25 +3294,25 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I5" s="4">
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -3301,25 +3320,25 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3327,25 +3346,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3353,25 +3372,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3379,25 +3398,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I9" s="4">
         <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3405,25 +3424,25 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="I10" s="4">
         <v>150</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3431,25 +3450,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I11" s="4">
         <v>200</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3457,36 +3476,36 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J13" s="4">
         <v>20</v>
@@ -3494,27 +3513,27 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3523,7 +3542,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J15" s="4">
         <v>30</v>
@@ -3531,19 +3550,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J16" s="4">
         <v>2</v>
@@ -3554,27 +3573,27 @@
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="I17" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
@@ -3583,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J18" s="4">
         <v>200</v>
@@ -3591,19 +3610,19 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>15</v>
+        <v>287</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J19" s="4">
         <v>100</v>
@@ -3611,36 +3630,36 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>57</v>
+        <v>286</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J21" s="4">
         <v>20</v>
@@ -3648,22 +3667,22 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>202</v>
-      </c>
       <c r="F22" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
@@ -3672,7 +3691,7 @@
         <v>25</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
@@ -3686,19 +3705,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="J23" s="4">
         <v>0.5</v>
@@ -3706,19 +3725,19 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J24" s="4">
         <v>2</v>
@@ -3726,22 +3745,42 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="J25" s="4">
-        <v>50</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J26" s="4">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3770,44 +3809,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>21</v>
@@ -3816,71 +3855,71 @@
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -3888,10 +3927,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -3899,10 +3938,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -3910,10 +3949,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -3921,13 +3960,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3952,10 +3994,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3963,39 +4005,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -4003,19 +4045,19 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4023,10 +4065,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4034,10 +4076,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4045,13 +4087,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4059,16 +4101,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="308">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -462,10 +462,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>데미지 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>체력 회복 효과</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -601,10 +597,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_PASSIVE_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -694,10 +686,6 @@
   </si>
   <si>
     <t>SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1236,10 +1224,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_TAKE_DAMAGE_101</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1257,10 +1241,6 @@
   </si>
   <si>
     <t>MATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1383,10 +1363,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>!bool</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1592,10 +1568,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SE_KNOCKBACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Self</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1616,27 +1588,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_KNOCKBACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_KNOCKBACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>짧은기간 넉백 효과</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1725,6 +1677,118 @@
   </si>
   <si>
     <t>SE_DECREASE_DAMAGETAKEN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DASH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2211,7 +2275,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2244,28 +2308,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2290,7 +2354,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -2317,76 +2381,76 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2401,14 +2465,14 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="13"/>
@@ -2417,7 +2481,7 @@
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2426,7 +2490,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2440,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="8" t="s">
@@ -2452,15 +2516,15 @@
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>27</v>
@@ -2504,7 +2568,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>36</v>
@@ -2521,18 +2585,18 @@
         <v>0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F35"/>
     </row>
@@ -2545,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2570,7 +2634,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2584,52 +2648,52 @@
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
@@ -2646,52 +2710,52 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>111</v>
+        <v>281</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="M3" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2717,22 +2781,22 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>4</v>
+        <v>288</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2741,7 +2805,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>174</v>
+        <v>293</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2750,157 +2814,163 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5">
-        <v>50</v>
+        <v>300</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>288</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="I5" s="4">
         <v>0.5</v>
       </c>
+      <c r="J5" s="4">
+        <v>180</v>
+      </c>
       <c r="K5" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>240</v>
+        <v>293</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M5" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>197</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>87</v>
+        <v>299</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>301</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>179</v>
+        <v>288</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>172</v>
+        <v>290</v>
       </c>
       <c r="I6" s="4">
-        <v>99999</v>
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="M6" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>60</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
+      </c>
+      <c r="F7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="I7" s="4">
-        <v>99999</v>
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>234</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>134</v>
+        <v>287</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>172</v>
+        <v>290</v>
       </c>
       <c r="I8" s="4">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M8" s="4" t="b">
-        <v>1</v>
+        <v>99999</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>151</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>4</v>
+        <v>176</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I9" s="4">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="L9" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M9" s="4" t="b">
-        <v>1</v>
+        <v>99999</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2909,13 +2979,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -2929,25 +2999,25 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D11" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L11" s="4">
         <v>0.3</v>
@@ -2956,15 +3026,15 @@
         <v>1</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -2973,13 +3043,13 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L12" s="4">
         <v>0.3</v>
@@ -2988,15 +3058,15 @@
         <v>1</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -3005,13 +3075,13 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L13" s="4">
         <v>0.3</v>
@@ -3020,117 +3090,242 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D14" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L14" s="4">
-        <v>0.1</v>
+        <v>0.3</v>
+      </c>
+      <c r="M14" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="D15" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I15" s="4">
-        <v>99999</v>
+        <v>1</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="M15" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>242</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>114</v>
+        <v>142</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>4</v>
+        <v>175</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="I16" s="4">
-        <v>99999</v>
+      <c r="L16" s="4">
+        <v>0.1</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>243</v>
+        <v>62</v>
+      </c>
+      <c r="D17" s="4">
+        <v>5</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="I17" s="4">
         <v>99999</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="R17" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>276</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="4">
+        <v>99999</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I19" s="4">
+        <v>99999</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I20" s="4">
+        <v>2</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="M20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3160,7 +3355,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -3174,40 +3369,40 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3221,16 +3416,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3256,22 +3451,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>303</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>47</v>
@@ -3280,7 +3475,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3294,16 +3489,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>139</v>
+        <v>304</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>47</v>
@@ -3312,24 +3513,36 @@
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>140</v>
+        <v>305</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>47</v>
@@ -3338,24 +3551,30 @@
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>47</v>
@@ -3364,7 +3583,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3372,16 +3591,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>47</v>
@@ -3390,7 +3609,7 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3398,16 +3617,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>47</v>
@@ -3416,7 +3635,7 @@
         <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3424,16 +3643,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>47</v>
@@ -3442,7 +3661,7 @@
         <v>150</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3450,25 +3669,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I11" s="4">
         <v>200</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3476,7 +3695,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -3485,15 +3704,15 @@
         <v>11</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>50</v>
@@ -3502,10 +3721,10 @@
         <v>11</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J13" s="4">
         <v>20</v>
@@ -3513,10 +3732,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
@@ -3525,15 +3744,15 @@
         <v>26</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -3542,7 +3761,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4">
         <v>30</v>
@@ -3550,10 +3769,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
@@ -3562,7 +3781,7 @@
         <v>26</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J16" s="4">
         <v>2</v>
@@ -3573,27 +3792,27 @@
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
@@ -3602,7 +3821,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J18" s="4">
         <v>200</v>
@@ -3610,19 +3829,19 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J19" s="4">
         <v>100</v>
@@ -3630,36 +3849,36 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J21" s="4">
         <v>20</v>
@@ -3667,22 +3886,22 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
@@ -3691,7 +3910,7 @@
         <v>25</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
@@ -3705,39 +3924,39 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="J23" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="J24" s="4">
         <v>2</v>
@@ -3745,42 +3964,39 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>245</v>
+        <v>11</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="J25" s="4">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>11</v>
+        <v>295</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>289</v>
+        <v>26</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="J26" s="4">
-        <v>30</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3809,44 +4025,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>21</v>
@@ -3855,40 +4071,40 @@
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>44</v>
@@ -3897,29 +4113,29 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -3927,10 +4143,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -3938,10 +4154,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -3949,10 +4165,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -3960,16 +4176,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -3994,10 +4210,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4005,39 +4221,39 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -4045,19 +4261,16 @@
         <v>1001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4065,10 +4278,10 @@
         <v>10001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4076,10 +4289,10 @@
         <v>10002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4087,13 +4300,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4101,16 +4314,16 @@
         <v>10004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -11,7 +11,7 @@
     <sheet name="#SkillInfo" sheetId="2" r:id="rId2"/>
     <sheet name="#SkillEffect" sheetId="6" r:id="rId3"/>
     <sheet name="#BuffInfo" sheetId="4" r:id="rId4"/>
-    <sheet name="#SkillSet" sheetId="7" r:id="rId5"/>
+    <sheet name="#SkillSet" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -34,119 +34,119 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="297">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillCastingTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>n초후 발동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!SkillCastingTypes</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillApplyTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Friendly</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!SkillApplyTarget</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>DecreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>아군에게 적용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>자신에게 적용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>적에게 적용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>모두에게 적용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!SkillEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Effect_2</t>
   </si>
   <si>
     <t>FinishEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_3</t>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>버프 생성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectType에 따라 EffectParam1~5에 넣을 값이 달라짐.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -227,15 +227,15 @@
       </rPr>
       <t xml:space="preserve"> : 버프 효과 발동 간격. 실수형</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Effect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>CooltimeSec</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Effect_3</t>
@@ -245,23 +245,23 @@
   </si>
   <si>
     <t>스탯 증가 (Target은 Self만 가능)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>스탯 감소(Target은 Self만 가능)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>오라 생성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>DeactivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>버프 삭제</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -286,7 +286,7 @@
       </rPr>
       <t xml:space="preserve"> : 버프 ID</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -333,7 +333,7 @@
       </rPr>
       <t xml:space="preserve"> : 지속 시간. 실수형(0이면 무한)</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -380,7 +380,7 @@
       </rPr>
       <t xml:space="preserve"> : 증가 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -427,395 +427,261 @@
       </rPr>
       <t xml:space="preserve"> : 감소 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>패시브1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>All</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>체력 회복 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>포션 사용 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_HP_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_MOVESPEED_01</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>패시브2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>포션1 사용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_HP_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_HP_INTERVAL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>IntervalEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>체력 회복 지속효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_HP_INTERVAL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 캐릭터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 몬스터 스킬세트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>데미지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>BuffInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!BuffInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_USE_POSTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_USE_SCROLL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스크롤1 사용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_SCROLL_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>스크롤 사용 버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>HpRecovery_Add</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MUSHROOM_ATTACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_GOBLIN_ATTACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
   </si>
   <si>
     <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_03</t>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MUSHROOM_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_GOBLIN_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DEMON_ATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>기본공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격2</t>
@@ -839,10 +705,6 @@
     <t>SE_TAKE_DAMAGE_06</t>
   </si>
   <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_TAKE_DAMAGE_07</t>
   </si>
   <si>
@@ -850,47 +712,43 @@
   </si>
   <si>
     <t>SkillScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>타겟팅스킬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>부채꼴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>원형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Donut</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>도넛 모양</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>직선 궤적</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -915,7 +773,7 @@
       </rPr>
       <t xml:space="preserve"> : 반지름</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -974,7 +832,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1033,7 +891,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1092,23 +950,23 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!SkillScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ScanParam1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ScanParam2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1133,318 +991,650 @@
       </rPr>
       <t xml:space="preserve"> : 사정거리</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시 적용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionEffectTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillDamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 데미지 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-blue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_hit_finisher_52</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>Root</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFXAnchor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillAnchorType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFXAnchor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAnchorType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraShake</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy-hit-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동불가 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDebuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_SILENCE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BINDING</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 데미지 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크(받는 데미지 증가)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_DAMAGETAKEN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>상시 적용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingParam</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DASH</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_MELEE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 근접공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골궁수 원거리공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 물리 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 마법 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골마법사 원거리 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_MATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉시발동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionEffectTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionName</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillDamageType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 데미지 효과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hit-blue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>Root</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFXAnchor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillAnchorType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillAnchorType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ApplyTarget</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CameraShake</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_POTION_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashy-hit-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateAura</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>스턴 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>침묵 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동불가 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDebuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseAttackSkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1557,251 +1747,27 @@
       </rPr>
       <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 디버프</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_KNOCKBACK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BREAK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 데미지 증가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크(받는 데미지 증가)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffectTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DecreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_DAMAGETAKEN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DASH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1870,6 +1836,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1897,7 +1870,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1958,14 +1931,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1988,24 +1977,46 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="40% - 강조색3" xfId="1" builtinId="39"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2275,7 +2286,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2308,28 +2319,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2354,7 +2365,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -2381,76 +2392,76 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="4" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2465,14 +2476,14 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="4" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="13"/>
@@ -2481,7 +2492,7 @@
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2490,7 +2501,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2504,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="8" t="s">
@@ -2516,15 +2527,15 @@
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>27</v>
@@ -2568,7 +2579,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>36</v>
@@ -2585,23 +2596,23 @@
         <v>0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="F35"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2609,12 +2620,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="36.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.75" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="15" style="4" customWidth="1"/>
     <col min="6" max="12" width="23.75" style="4" customWidth="1"/>
     <col min="13" max="13" width="14.25" style="4" bestFit="1" customWidth="1"/>
@@ -2634,7 +2645,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2648,52 +2659,52 @@
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
@@ -2710,52 +2721,52 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="L3" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>220</v>
-      </c>
       <c r="P3" s="4" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2781,10 +2792,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D4" s="4">
         <v>0.4</v>
@@ -2793,10 +2804,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2805,7 +2816,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2814,15 +2825,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="D5" s="4">
         <v>0.3</v>
@@ -2831,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="I5" s="4">
         <v>0.5</v>
@@ -2843,7 +2854,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -2852,15 +2863,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="D6" s="4">
         <v>0.2</v>
@@ -2869,16 +2880,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -2887,56 +2898,56 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="I7" s="4">
         <v>0.5</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>287</v>
+        <v>247</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="I8" s="4">
         <v>99999</v>
@@ -2953,39 +2964,42 @@
         <v>61</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="I9" s="4">
         <v>99999</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="I10" s="4">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -2994,342 +3008,232 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="I11" s="4">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="L11" s="4">
         <v>0.3</v>
       </c>
-      <c r="M11" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="R11" s="4" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I12" s="4">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="L12" s="4">
         <v>0.3</v>
       </c>
-      <c r="M12" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="R12" s="4" t="s">
-        <v>145</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>139</v>
+        <v>271</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
       </c>
+      <c r="E13" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F13" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="L13" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M13" s="4" t="b">
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>146</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>140</v>
+        <v>279</v>
       </c>
       <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>171</v>
+        <v>281</v>
       </c>
       <c r="L14" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M14" s="4" t="b">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>147</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="4">
-        <v>3</v>
+        <v>199</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="I15" s="4">
-        <v>1</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="L15" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M15" s="4" t="b">
-        <v>1</v>
+        <v>99999</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>149</v>
+        <v>224</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="4">
-        <v>5</v>
+        <v>245</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="4">
         <v>2</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" s="4">
-        <v>1</v>
-      </c>
       <c r="K16" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="N17" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="4">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I17" s="4">
-        <v>99999</v>
+      <c r="O17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I18" s="4">
-        <v>99999</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="I19" s="4">
-        <v>99999</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="I20" s="4">
-        <v>2</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="M20" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="I21" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3337,7 +3241,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3355,7 +3259,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -3369,40 +3273,40 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3416,16 +3320,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3451,22 +3355,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>47</v>
@@ -3475,7 +3379,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3489,22 +3393,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>47</v>
@@ -3513,7 +3417,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K5" s="4">
         <v>1</v>
@@ -3527,22 +3431,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>47</v>
@@ -3551,7 +3455,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3565,16 +3469,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>47</v>
@@ -3583,7 +3487,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3591,16 +3495,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>47</v>
@@ -3609,7 +3513,7 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3617,25 +3521,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>140</v>
+        <v>273</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="4">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3643,25 +3544,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>149</v>
+        <v>277</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>141</v>
+        <v>278</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="4">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3669,25 +3567,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>227</v>
+        <v>47</v>
       </c>
       <c r="I11" s="4">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3695,84 +3593,99 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>241</v>
+        <v>47</v>
+      </c>
+      <c r="I12" s="4">
+        <v>150</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J13" s="4">
-        <v>20</v>
+        <v>190</v>
+      </c>
+      <c r="I13" s="4">
+        <v>200</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="J15" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
@@ -3781,226 +3694,263 @@
         <v>26</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="4">
-        <v>2</v>
-      </c>
-      <c r="K16" s="4">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>118</v>
+        <v>98</v>
+      </c>
+      <c r="J17" s="4">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="J18" s="4">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>275</v>
+        <v>97</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" s="4">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>242</v>
+        <v>99</v>
+      </c>
+      <c r="J20" s="4">
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>269</v>
+        <v>67</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="J21" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>216</v>
+        <v>11</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="4">
-        <v>25</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="K22" s="4">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4">
-        <v>1</v>
-      </c>
-      <c r="M22" s="4">
-        <v>2</v>
+        <v>218</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>252</v>
+        <v>11</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>273</v>
+        <v>100</v>
       </c>
       <c r="J23" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>264</v>
+        <v>161</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>267</v>
+        <v>157</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>239</v>
+        <v>46</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="J24" s="4">
+        <v>14</v>
+      </c>
+      <c r="I24" s="4">
+        <v>25</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="K24" s="4">
+        <v>2</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>277</v>
+        <v>26</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="J25" s="4">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>295</v>
+        <v>228</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="J26" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J27" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="J28" s="4">
         <v>0.2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4025,44 +3975,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>21</v>
@@ -4071,18 +4021,18 @@
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>43</v>
@@ -4093,18 +4043,18 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>253</v>
+        <v>214</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>44</v>
@@ -4118,24 +4068,24 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>52</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>244</v>
+        <v>206</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4143,10 +4093,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4154,10 +4104,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -4165,10 +4115,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -4176,158 +4126,286 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T40"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="36.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="19.25" style="4" customWidth="1"/>
+    <col min="19" max="19" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+    <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>90</v>
+        <v>287</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>91</v>
+        <v>288</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
-        <v>97</v>
+        <v>290</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="17" t="s">
+        <v>283</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>291</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
-        <v>1001</v>
+        <v>291</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="16">
+        <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
+        <v>292</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="16">
+        <v>102</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="16">
+        <v>103</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="20">
         <v>10001</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+      <c r="C7" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="20">
         <v>10002</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
+      <c r="C8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="20">
         <v>10003</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
-        <v>10004</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="C9" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="20"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E12" s="16"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="298">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1597,10 +1597,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>BaseAttackSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1747,6 +1743,14 @@
       </rPr>
       <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseAttackSkill</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2428,7 +2432,7 @@
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
         <v>120</v>
@@ -2530,7 +2534,7 @@
         <v>86</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2798,7 +2802,7 @@
         <v>103</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E4" s="4" t="b">
         <v>1</v>
@@ -2836,7 +2840,7 @@
         <v>260</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="4" t="b">
         <v>1</v>
@@ -2996,7 +3000,7 @@
         <v>133</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>135</v>
@@ -3028,7 +3032,7 @@
         <v>133</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>135</v>
@@ -4175,7 +4179,7 @@
         <v>282</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4185,19 +4189,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>284</v>
@@ -4212,25 +4216,25 @@
         <v>283</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4250,7 +4254,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E4" s="18"/>
       <c r="G4" s="16"/>
@@ -4267,7 +4271,7 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
@@ -4284,7 +4288,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -1034,10 +1034,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>MotionEffectTime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>!float</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1751,6 +1747,10 @@
   </si>
   <si>
     <t>BaseAttackSkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionEffectTime</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2290,7 +2290,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -2419,7 +2419,7 @@
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>121</v>
@@ -2432,7 +2432,7 @@
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C16" t="s">
         <v>120</v>
@@ -2445,7 +2445,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>124</v>
@@ -2480,14 +2480,14 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="13"/>
@@ -2496,7 +2496,7 @@
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2505,7 +2505,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="8" t="s">
@@ -2534,12 +2534,12 @@
         <v>86</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>27</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>36</v>
@@ -2600,18 +2600,18 @@
         <v>0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F35"/>
     </row>
@@ -2663,16 +2663,16 @@
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>142</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>131</v>
@@ -2681,34 +2681,34 @@
         <v>132</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>145</v>
+        <v>297</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S2" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
@@ -2734,7 +2734,7 @@
         <v>79</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
@@ -2746,7 +2746,7 @@
         <v>130</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>79</v>
@@ -2755,22 +2755,22 @@
         <v>80</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>103</v>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>119</v>
@@ -2820,7 +2820,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2829,36 +2829,36 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>119</v>
       </c>
       <c r="I5" s="4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J5" s="4">
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -2867,15 +2867,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D6" s="4">
         <v>0.2</v>
@@ -2884,16 +2884,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -2902,47 +2902,47 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G7">
         <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I7" s="4">
         <v>0.5</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
@@ -2951,7 +2951,7 @@
         <v>139</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I8" s="4">
         <v>99999</v>
@@ -3038,7 +3038,7 @@
         <v>135</v>
       </c>
       <c r="L11" s="4">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>112</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -3070,18 +3070,18 @@
         <v>135</v>
       </c>
       <c r="L12" s="4">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -3105,15 +3105,15 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D14" s="4">
         <v>3</v>
@@ -3131,62 +3131,62 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R15" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="S15" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
@@ -3198,42 +3198,42 @@
         <v>1</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I17" s="4">
         <v>0.5</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3277,16 +3277,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>87</v>
@@ -3295,13 +3295,13 @@
         <v>24</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>76</v>
@@ -3324,16 +3324,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3362,19 +3362,19 @@
         <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>47</v>
@@ -3400,31 +3400,31 @@
         <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
       <c r="I5" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>88</v>
       </c>
       <c r="K5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4">
         <v>1</v>
@@ -3438,19 +3438,19 @@
         <v>110</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>47</v>
@@ -3482,7 +3482,7 @@
         <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>47</v>
@@ -3508,7 +3508,7 @@
         <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>47</v>
@@ -3525,22 +3525,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3548,22 +3548,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3580,7 +3580,7 @@
         <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>47</v>
@@ -3606,7 +3606,7 @@
         <v>46</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>47</v>
@@ -3632,10 +3632,10 @@
         <v>46</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
@@ -3658,10 +3658,10 @@
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -3792,7 +3792,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>99</v>
@@ -3812,15 +3812,15 @@
         <v>11</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>53</v>
@@ -3829,7 +3829,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>100</v>
@@ -3840,22 +3840,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>14</v>
@@ -3864,7 +3864,7 @@
         <v>25</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K24" s="4">
         <v>2</v>
@@ -3878,19 +3878,19 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
@@ -3898,19 +3898,19 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J26" s="4">
         <v>2</v>
@@ -3918,19 +3918,19 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="J27" s="4">
         <v>30</v>
@@ -3938,16 +3938,16 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J28" s="4">
         <v>0.2</v>
@@ -3990,7 +3990,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>30</v>
@@ -3999,13 +3999,13 @@
         <v>68</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4028,10 +4028,10 @@
         <v>82</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4058,7 +4058,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>44</v>
@@ -4086,10 +4086,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4108,10 +4108,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -4119,10 +4119,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -4130,16 +4130,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4176,10 +4176,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4189,52 +4189,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>289</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4254,15 +4254,15 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E4" s="18"/>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4271,15 +4271,15 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4288,15 +4288,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4305,7 +4305,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4316,7 +4316,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -4327,7 +4327,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="300">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1098,10 +1098,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Circle</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1751,6 +1747,17 @@
   </si>
   <si>
     <t>MotionEffectTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2290,7 +2297,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2419,7 +2426,7 @@
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>121</v>
@@ -2432,7 +2439,7 @@
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C16" t="s">
         <v>120</v>
@@ -2445,7 +2452,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>124</v>
@@ -2519,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="8" t="s">
@@ -2534,7 +2541,7 @@
         <v>86</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2583,7 +2590,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>36</v>
@@ -2600,18 +2607,18 @@
         <v>0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F35"/>
     </row>
@@ -2663,16 +2670,16 @@
         <v>31</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>142</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>131</v>
@@ -2684,31 +2691,31 @@
         <v>146</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S2" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
@@ -2725,7 +2732,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
@@ -2734,7 +2741,7 @@
         <v>79</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
@@ -2746,7 +2753,7 @@
         <v>130</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>79</v>
@@ -2761,16 +2768,16 @@
         <v>147</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2796,7 +2803,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>103</v>
@@ -2808,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>119</v>
@@ -2820,7 +2827,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2829,15 +2836,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -2846,7 +2853,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>119</v>
@@ -2858,7 +2865,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -2867,15 +2874,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D6" s="4">
         <v>0.2</v>
@@ -2884,16 +2891,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -2902,39 +2909,39 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>161</v>
+        <v>298</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I7" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>155</v>
@@ -2942,7 +2949,7 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
@@ -2951,7 +2958,7 @@
         <v>139</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I8" s="4">
         <v>99999</v>
@@ -3046,10 +3053,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -3073,15 +3080,15 @@
         <v>0.5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -3105,15 +3112,15 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D14" s="4">
         <v>3</v>
@@ -3131,62 +3138,62 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R15" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="S15" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
@@ -3198,39 +3205,39 @@
         <v>1</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I17" s="4">
         <v>0.5</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>155</v>
@@ -3277,16 +3284,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>87</v>
@@ -3295,13 +3302,13 @@
         <v>24</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>76</v>
@@ -3327,13 +3334,13 @@
         <v>154</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3362,7 +3369,7 @@
         <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>46</v>
@@ -3371,10 +3378,10 @@
         <v>150</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>47</v>
@@ -3400,7 +3407,7 @@
         <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>46</v>
@@ -3409,10 +3416,10 @@
         <v>150</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>47</v>
@@ -3438,7 +3445,7 @@
         <v>110</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>46</v>
@@ -3447,10 +3454,10 @@
         <v>150</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>47</v>
@@ -3525,22 +3532,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3548,10 +3555,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>46</v>
@@ -3635,7 +3642,7 @@
         <v>151</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
@@ -3658,10 +3665,10 @@
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -3792,7 +3799,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>99</v>
@@ -3812,15 +3819,15 @@
         <v>11</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>53</v>
@@ -3829,7 +3836,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>100</v>
@@ -3852,22 +3859,22 @@
         <v>158</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>159</v>
+        <v>299</v>
       </c>
       <c r="K24" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L24" s="4">
         <v>1</v>
@@ -3878,19 +3885,19 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
@@ -3898,19 +3905,19 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J26" s="4">
         <v>2</v>
@@ -3918,19 +3925,19 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="J27" s="4">
         <v>30</v>
@@ -3938,16 +3945,16 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J28" s="4">
         <v>0.2</v>
@@ -3990,7 +3997,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>30</v>
@@ -3999,13 +4006,13 @@
         <v>68</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4028,10 +4035,10 @@
         <v>82</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4058,7 +4065,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>44</v>
@@ -4086,10 +4093,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4097,10 +4104,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4108,10 +4115,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -4119,10 +4126,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -4130,16 +4137,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4156,7 +4163,7 @@
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="4" bestFit="1" customWidth="1"/>
@@ -4176,10 +4183,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4189,52 +4196,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>288</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4254,15 +4261,18 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>297</v>
       </c>
       <c r="E4" s="18"/>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4271,15 +4281,15 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4288,15 +4298,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4305,7 +4315,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4316,7 +4326,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -4327,7 +4337,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -2297,7 +2297,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="314">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -130,10 +130,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EffectParam_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>EffectParam_3</t>
   </si>
   <si>
@@ -529,1235 +525,1295 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>체력 회복 지속효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_HP_INTERVAL_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_POTION_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_POTION_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_ATTACKSPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_ATTACKSPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!BuffInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_POTION_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_SCROLL_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크롤 사용 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 몬스터 공격1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 몬스터 공격2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마 몬스터 공격1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마 몬스터 공격2</t>
+  </si>
+  <si>
+    <t>악마 몬스터 공격3</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_06</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_07</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_08</t>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타겟팅스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>부채꼴</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원형</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Donut</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도넛 모양</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>직선 궤적</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ScanParam_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 반지름</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ScanParam_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 반지름 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 각도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ScanParam_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 길이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 너비</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ScanParam_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 외경 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 내경</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillScanType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ScanParam_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 사정거리</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시 적용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillDamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 데미지 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-blue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_hit_finisher_52</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>Root</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFXAnchor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillAnchorType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFXAnchor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAnchorType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraShake</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy-hit-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동불가 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDebuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_SILENCE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BINDING</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 데미지 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크(받는 데미지 증가)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_DAMAGETAKEN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_MELEE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 근접공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골궁수 원거리공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 물리 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 마법 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골마법사 원거리 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_MATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 기본데미지 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 데미지 계수 속성 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 데미지 계수값  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_5]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseAttackSkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>IntervalEffect</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>체력 회복 지속효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_HP_INTERVAL_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_POTION_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_POTION_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!BuffInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_POTION_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_SCROLL_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스크롤 사용 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 몬스터 공격1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 몬스터 공격2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 몬스터 공격1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 몬스터 공격2</t>
-  </si>
-  <si>
-    <t>악마 몬스터 공격3</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_03</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_06</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_07</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_08</t>
+    <t>SKILL_DASH_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시공격 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시어택 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DASH</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DASH_ATTACK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시공격 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DASH_ATTACK_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시어택 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SkillScanType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타겟팅스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>부채꼴</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>원형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Donut</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>도넛 모양</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직선 궤적</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 반지름</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 반지름 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 각도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 길이 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 너비</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 외경 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 내경</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ScanParam1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ScanParam2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[ScanParam_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 사정거리</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상시 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉시발동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pure</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillDamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 데미지 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hit-blue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>Root</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFXAnchor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillAnchorType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillAnchorType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ApplyTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CameraShake</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashy-hit-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateAura</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스턴 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>침묵 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동불가 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDebuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_KNOCKBACK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 데미지 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크(받는 데미지 증가)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffectTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DecreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_DAMAGETAKEN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DASH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_ATK_MELEE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_ATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 근접공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골궁수 원거리공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 물리 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 마법 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골마법사 원거리 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 기본데미지 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 데미지 계수 속성 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_3]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 데미지 계수값  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_4]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_5]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseAttackSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MotionEffectTime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2330,28 +2386,28 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2376,7 +2432,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -2392,7 +2448,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>20</v>
@@ -2403,76 +2459,76 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>116</v>
+        <v>311</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2487,14 +2543,14 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="13"/>
@@ -2503,7 +2559,7 @@
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2512,7 +2568,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2526,11 +2582,11 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2538,32 +2594,32 @@
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="E28" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2571,10 +2627,10 @@
         <v>15</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2582,21 +2638,21 @@
         <v>16</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2607,18 +2663,18 @@
         <v>0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F35"/>
     </row>
@@ -2631,7 +2687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2656,7 +2712,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2667,64 +2723,64 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>146</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="V2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>23</v>
@@ -2732,52 +2788,52 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="O3" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2803,10 +2859,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D4" s="4">
         <v>0.3</v>
@@ -2815,10 +2871,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2827,7 +2883,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2836,15 +2892,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -2853,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I5" s="4">
         <v>0.8</v>
@@ -2865,7 +2921,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -2874,15 +2930,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D6" s="4">
         <v>0.2</v>
@@ -2891,16 +2947,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -2909,90 +2965,90 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I8" s="4">
         <v>99999</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I9" s="4">
         <v>99999</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -3004,13 +3060,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I10" s="4">
         <v>0.3</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -3019,15 +3075,15 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -3036,27 +3092,27 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I11" s="4">
         <v>0.3</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L11" s="4">
         <v>0.5</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -3068,27 +3124,27 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I12" s="4">
         <v>0.2</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L12" s="4">
         <v>0.5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -3100,27 +3156,27 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L13" s="4">
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D14" s="4">
         <v>3</v>
@@ -3132,115 +3188,182 @@
         <v>4</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="L14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I17" s="4">
         <v>0.5</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D18" s="4">
+        <v>5</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19" s="4">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3375,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3270,7 +3393,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>7</v>
@@ -3284,40 +3407,40 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3331,16 +3454,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3366,31 +3489,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3404,31 +3527,31 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I5" s="4">
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -3442,31 +3565,31 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3480,25 +3603,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3506,25 +3629,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3532,22 +3655,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3555,22 +3678,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3578,25 +3701,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I11" s="4">
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -3604,25 +3727,25 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="I12" s="4">
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -3630,25 +3753,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -3656,36 +3779,36 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -3693,27 +3816,27 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
@@ -3722,7 +3845,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -3730,19 +3853,19 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J18" s="4">
         <v>2</v>
@@ -3753,27 +3876,27 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="I19" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>11</v>
@@ -3782,7 +3905,7 @@
         <v>15</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J20" s="4">
         <v>200</v>
@@ -3790,19 +3913,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J21" s="4">
         <v>100</v>
@@ -3810,36 +3933,36 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J23" s="4">
         <v>20</v>
@@ -3847,22 +3970,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>14</v>
@@ -3871,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="K24" s="4">
         <v>5</v>
@@ -3885,19 +4008,19 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
@@ -3905,19 +4028,19 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="J26" s="4">
         <v>2</v>
@@ -3925,19 +4048,19 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J27" s="4">
         <v>30</v>
@@ -3945,19 +4068,80 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>253</v>
+        <v>299</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="J28" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="J29" s="4">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="4">
+        <v>100</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K30" s="4">
+        <v>3</v>
+      </c>
+      <c r="L30" s="4">
+        <v>1</v>
+      </c>
+      <c r="M30" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +4152,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3986,44 +4170,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>289</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>21</v>
@@ -4032,71 +4216,71 @@
         <v>21</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4104,10 +4288,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4115,10 +4299,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -4126,10 +4310,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -4137,16 +4321,35 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -4183,10 +4386,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4196,52 +4399,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4261,18 +4464,17 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="E4" s="18"/>
+        <v>287</v>
+      </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4281,15 +4483,18 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>290</v>
+        <v>281</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4298,15 +4503,18 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>291</v>
+        <v>282</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4315,7 +4523,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4326,7 +4534,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -4337,7 +4545,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="328">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -945,11 +945,602 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ScanParam2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시 적용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시발동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillDamageType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 데미지 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-blue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_hit_finisher_52</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>Root</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFXAnchor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillAnchorType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFXAnchor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAnchorType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraShake</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy-hit-1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동불가 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDebuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_SILENCE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BINDING</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_KNOCKBACK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 데미지 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크(받는 데미지 증가)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_DAMAGETAKEN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본공격3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_MELEE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 근접공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골궁수 원거리공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 물리 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 마법 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골마법사 원거리 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_MATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -963,7 +1554,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[ScanParam_1]</t>
+      <t>[Param_1]</t>
     </r>
     <r>
       <rPr>
@@ -973,633 +1564,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 사정거리</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상시 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉시발동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pure</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillDamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 데미지 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hit-blue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>Root</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFXAnchor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillAnchorType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillAnchorType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ApplyTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CameraShake</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashy-hit-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateAura</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스턴 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>침묵 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동불가 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDebuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_KNOCKBACK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 데미지 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크(받는 데미지 증가)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffectTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DecreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_DAMAGETAKEN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_ATK_MELEE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_ATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 근접공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골궁수 원거리공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 물리 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 마법 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골마법사 원거리 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> : 기본데미지 </t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
+        <color theme="4" tint="-0.249977111117893"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_1]</t>
+      <t>[Param_2]</t>
     </r>
     <r>
       <rPr>
@@ -1609,7 +1586,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 기본데미지 </t>
+      <t xml:space="preserve"> : 데미지 계수 속성 </t>
     </r>
     <r>
       <rPr>
@@ -1621,7 +1598,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_2]</t>
+      <t>[Param_3]</t>
     </r>
     <r>
       <rPr>
@@ -1631,19 +1608,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 데미지 계수 속성 </t>
+      <t xml:space="preserve"> : 데미지 계수값  </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
+        <color rgb="FF0070C0"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_3]</t>
+      <t>[Param_4]</t>
     </r>
     <r>
       <rPr>
@@ -1653,7 +1630,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 데미지 계수값  </t>
+      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
     </r>
     <r>
       <rPr>
@@ -1665,7 +1642,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_4]</t>
+      <t>[Param_5]</t>
     </r>
     <r>
       <rPr>
@@ -1675,19 +1652,160 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
-    </r>
+      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseAttackSkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시공격 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시어택 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DASH</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DASH_ATTACK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시공격 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DASH_ATTACK_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시어택 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillScanType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionEffectTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 단일 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 범위(직선) 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF0070C0"/>
+        <color theme="8"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_5]</t>
+      <t>[ScanParam_1]</t>
     </r>
     <r>
       <rPr>
@@ -1697,99 +1815,66 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseAttackSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시공격 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시어택 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DASH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DASH_ATTACK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시공격 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DASH_ATTACK_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시어택 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-  </si>
-  <si>
-    <t>Physical</t>
+      <t xml:space="preserve"> : 사정거리 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[ScanParam_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 타갯 수</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>발동확률 0~1 = 0~100%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 스킬 데미지1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 스킬 데미지2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1797,23 +1882,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EffectParam_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillScanType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>ScanParam1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>MotionEffectTime</t>
+    <t>CastingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2353,7 +2430,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2361,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2380,37 +2457,46 @@
         <v>3</v>
       </c>
       <c r="D1" s="6"/>
+      <c r="E1" s="5" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>136</v>
+      <c r="E3" s="4" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2432,7 +2518,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -2459,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
@@ -2476,13 +2562,13 @@
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
-        <v>130</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>118</v>
@@ -2495,7 +2581,7 @@
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C16" t="s">
         <v>117</v>
@@ -2508,7 +2594,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>121</v>
@@ -2534,32 +2620,29 @@
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
       <c r="D19" s="13"/>
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+    <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="9"/>
+      <c r="B21" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2567,116 +2650,125 @@
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
-      <c r="B23" t="s">
-        <v>148</v>
+      <c r="B23" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+    <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12"/>
+      <c r="B24" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="8" t="s">
+      <c r="B26" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="8" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>28</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>198</v>
+        <v>16</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E32" s="9"/>
-    </row>
-    <row r="33" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="4" t="s">
-        <v>174</v>
-      </c>
+      <c r="B34" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F35"/>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2687,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2726,52 +2818,52 @@
         <v>30</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>161</v>
+        <v>326</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="R2" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>22</v>
@@ -2788,7 +2880,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>6</v>
@@ -2797,19 +2889,19 @@
         <v>77</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>127</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>77</v>
@@ -2818,22 +2910,22 @@
         <v>78</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>21</v>
@@ -2859,7 +2951,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>101</v>
@@ -2871,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>116</v>
@@ -2883,7 +2975,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2892,24 +2984,24 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>116</v>
@@ -2921,7 +3013,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -2930,33 +3022,36 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
       </c>
+      <c r="J6" s="4">
+        <v>3</v>
+      </c>
       <c r="K6" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -2965,62 +3060,65 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I8" s="4">
         <v>99999</v>
       </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
       <c r="R8" s="4" t="s">
-        <v>58</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -3031,13 +3129,16 @@
         <v>60</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I9" s="4">
         <v>99999</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>61</v>
@@ -3060,13 +3161,16 @@
         <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I10" s="4">
         <v>0.3</v>
       </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
       <c r="K10" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -3092,13 +3196,16 @@
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I11" s="4">
         <v>0.3</v>
       </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
       <c r="K11" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L11" s="4">
         <v>0.5</v>
@@ -3109,10 +3216,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -3129,22 +3236,25 @@
       <c r="I12" s="4">
         <v>0.2</v>
       </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
       <c r="K12" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L12" s="4">
         <v>0.5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D13" s="4">
         <v>3</v>
@@ -3161,22 +3271,25 @@
       <c r="I13" s="4">
         <v>1</v>
       </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
       <c r="K13" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L13" s="4">
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D14" s="4">
         <v>3</v>
@@ -3193,153 +3306,159 @@
       <c r="I14" s="4">
         <v>1</v>
       </c>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
       <c r="K14" s="4" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="L14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
       </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
       <c r="N15" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I17" s="4">
         <v>0.5</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D18" s="4">
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I18" s="4">
         <v>2</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D19" s="4">
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -3348,22 +3467,116 @@
         <v>0.2</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D20" s="4">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="4">
+        <v>9</v>
+      </c>
+      <c r="J20" s="4">
+        <v>5</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L20" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D21" s="4">
+        <v>5</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="I21" s="4">
+        <v>2</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L21" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3588,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3407,31 +3620,31 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>85</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>74</v>
@@ -3454,16 +3667,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>6</v>
@@ -3492,19 +3705,19 @@
         <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>46</v>
@@ -3530,19 +3743,19 @@
         <v>107</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>46</v>
@@ -3568,19 +3781,19 @@
         <v>108</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>46</v>
@@ -3612,7 +3825,7 @@
         <v>45</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>46</v>
@@ -3638,7 +3851,7 @@
         <v>45</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>46</v>
@@ -3655,22 +3868,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3678,22 +3891,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3710,7 +3923,7 @@
         <v>45</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>46</v>
@@ -3736,7 +3949,7 @@
         <v>45</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>46</v>
@@ -3762,10 +3975,10 @@
         <v>45</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
@@ -3788,15 +4001,15 @@
         <v>11</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>55</v>
+        <v>310</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>49</v>
@@ -3922,7 +4135,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>97</v>
@@ -3942,15 +4155,15 @@
         <v>11</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>52</v>
@@ -3959,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>98</v>
@@ -3970,22 +4183,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>14</v>
@@ -3994,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="K24" s="4">
         <v>5</v>
@@ -4008,19 +4221,19 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
@@ -4028,19 +4241,19 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J26" s="4">
         <v>2</v>
@@ -4048,19 +4261,19 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J27" s="4">
         <v>30</v>
@@ -4068,10 +4281,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>11</v>
@@ -4080,7 +4293,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="J28" s="4">
         <v>0.1</v>
@@ -4088,10 +4301,10 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>11</v>
@@ -4100,7 +4313,7 @@
         <v>25</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="J29" s="4">
         <v>0.2</v>
@@ -4108,22 +4321,22 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>14</v>
@@ -4141,6 +4354,82 @@
         <v>1</v>
       </c>
       <c r="M30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="4">
+        <v>200</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="K31" s="4">
+        <v>1</v>
+      </c>
+      <c r="L31" s="4">
+        <v>1</v>
+      </c>
+      <c r="M31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="4">
+        <v>400</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="K32" s="4">
+        <v>1</v>
+      </c>
+      <c r="L32" s="4">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4">
         <v>1</v>
       </c>
     </row>
@@ -4181,22 +4470,22 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4219,10 +4508,10 @@
         <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4249,7 +4538,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>43</v>
@@ -4277,10 +4566,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4288,10 +4577,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4299,10 +4588,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
@@ -4310,10 +4599,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D11" s="4" t="b">
         <v>1</v>
@@ -4321,35 +4610,35 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4367,8 +4656,7 @@
     <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="26.375" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="21.75" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.75" style="4" bestFit="1" customWidth="1"/>
@@ -4386,10 +4674,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4399,52 +4687,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4464,17 +4752,20 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>306</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4483,18 +4774,18 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4503,18 +4794,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4523,7 +4811,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4534,7 +4822,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -4545,7 +4833,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="330">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -573,10 +573,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>IncreaseAttribute</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1228,10 +1224,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>DecreaseAttribute</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1249,10 +1241,6 @@
   </si>
   <si>
     <t>IsBasicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1557,10 +1545,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>BaseAttackSkill</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1859,6 +1843,60 @@
   </si>
   <si>
     <t>SKILL_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DAMAGE_IMMUNITY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DAMAGE_IMMUNITY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood_bat_finisher_05</t>
+  </si>
+  <si>
+    <t>Sector</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2398,7 +2436,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2422,11 +2460,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2434,37 +2472,37 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2486,7 +2524,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>18</v>
@@ -2513,76 +2551,76 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
         <v>103</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2603,14 +2641,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -2619,7 +2657,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2628,7 +2666,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2642,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
@@ -2657,12 +2695,12 @@
         <v>74</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>25</v>
@@ -2706,7 +2744,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>34</v>
@@ -2723,18 +2761,18 @@
         <v>0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F36"/>
     </row>
@@ -2747,7 +2785,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2760,7 +2798,7 @@
     <col min="15" max="15" width="16.25" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="34.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.375" style="4" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="36.5" style="4" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="28.75" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="24" width="22" style="4" customWidth="1"/>
@@ -2772,7 +2810,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>79</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2786,52 +2824,52 @@
         <v>29</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>21</v>
@@ -2848,7 +2886,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -2857,19 +2895,19 @@
         <v>67</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>67</v>
@@ -2878,22 +2916,22 @@
         <v>68</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="N3" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>20</v>
@@ -2919,10 +2957,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" s="4">
         <v>0.3</v>
@@ -2931,10 +2969,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2943,7 +2981,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2952,15 +2990,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -2969,10 +3007,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I5" s="4">
         <v>0.8</v>
@@ -2981,7 +3019,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -2990,15 +3028,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3007,10 +3045,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
@@ -3019,7 +3057,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -3028,56 +3066,56 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I8" s="4">
         <v>99999</v>
@@ -3086,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -3097,10 +3135,10 @@
         <v>56</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I9" s="4">
         <v>99999</v>
@@ -3114,10 +3152,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -3129,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I10" s="4">
         <v>0.3</v>
@@ -3138,7 +3176,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L10" s="4">
         <v>0.3</v>
@@ -3147,15 +3185,15 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -3164,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I11" s="4">
         <v>0.3</v>
@@ -3173,21 +3211,21 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L11" s="4">
         <v>0.5</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D12" s="4">
         <v>3</v>
@@ -3199,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I12" s="4">
         <v>0.2</v>
@@ -3208,21 +3246,21 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L12" s="4">
         <v>0.5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -3234,7 +3272,7 @@
         <v>3</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -3243,21 +3281,21 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L13" s="4">
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D14" s="4">
         <v>3</v>
@@ -3269,7 +3307,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -3278,27 +3316,27 @@
         <v>1</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="L14" s="4">
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I15" s="4">
         <v>99999</v>
@@ -3307,126 +3345,126 @@
         <v>1</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R15" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="S15" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I16" s="4">
         <v>2</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I17" s="4">
         <v>0.5</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D18" s="4">
         <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I18" s="4">
         <v>2</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D19" s="4">
         <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -3435,42 +3473,42 @@
         <v>0.2</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D20" s="4">
         <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G20" s="4">
         <v>2</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -3479,45 +3517,45 @@
         <v>5</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="L20" s="4">
         <v>0.2</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D21" s="4">
         <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G21" s="4">
         <v>2</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I21" s="4">
         <v>1.5</v>
@@ -3526,69 +3564,118 @@
         <v>0.5</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L21" s="4">
         <v>0.2</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D22" s="4">
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G22" s="4">
         <v>2</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I22" s="4">
         <v>2</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L22" s="4">
         <v>0.2</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="I23" s="4">
+        <v>99999</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="N24" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3600,7 +3687,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3632,31 +3719,31 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>75</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>64</v>
@@ -3679,16 +3766,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -3717,19 +3804,19 @@
         <v>61</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>45</v>
@@ -3752,22 +3839,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>45</v>
@@ -3790,22 +3877,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>45</v>
@@ -3828,16 +3915,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>45</v>
@@ -3854,16 +3941,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>45</v>
@@ -3880,22 +3967,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3903,22 +3990,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -3926,16 +4013,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>45</v>
@@ -3952,16 +4039,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>45</v>
@@ -3978,19 +4065,19 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
@@ -4013,15 +4100,15 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>48</v>
@@ -4030,10 +4117,10 @@
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -4070,7 +4157,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -4087,15 +4174,15 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>49</v>
@@ -4104,10 +4191,10 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -4115,22 +4202,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4139,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4153,19 +4240,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>199</v>
+        <v>327</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4173,19 +4260,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4193,19 +4280,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -4213,10 +4300,10 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>10</v>
@@ -4225,7 +4312,7 @@
         <v>24</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J24" s="4">
         <v>0.1</v>
@@ -4233,10 +4320,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>10</v>
@@ -4245,7 +4332,7 @@
         <v>24</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J25" s="4">
         <v>0.2</v>
@@ -4253,22 +4340,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -4291,22 +4378,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -4315,7 +4402,7 @@
         <v>200</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4329,22 +4416,22 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>13</v>
@@ -4353,7 +4440,7 @@
         <v>400</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
@@ -4367,22 +4454,22 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>13</v>
@@ -4391,13 +4478,33 @@
         <v>300</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="K29" s="4">
         <v>1</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="J30" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4408,7 +4515,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -4437,22 +4544,22 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4475,10 +4582,10 @@
         <v>70</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4505,7 +4612,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>42</v>
@@ -4519,10 +4626,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -4530,10 +4637,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4541,10 +4648,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4552,35 +4659,43 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -4616,10 +4731,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4629,52 +4744,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4694,14 +4809,14 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4710,18 +4825,18 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4730,15 +4845,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4747,7 +4862,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4758,7 +4873,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -4769,7 +4884,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -4780,10 +4895,10 @@
         <v>10004</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="345">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -276,31 +276,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 버프 ID</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Param_1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> : 오라 ID </t>
     </r>
     <r>
@@ -885,19 +860,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Passive</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -978,14 +941,6 @@
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHit</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1549,10 +1504,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ATK</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1897,6 +1848,111 @@
   </si>
   <si>
     <t>Sector</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 버프 ID</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitCaster</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동(시전자)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동(피격자)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_03</t>
+  </si>
+  <si>
+    <t>특수 스킬1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 스킬2</t>
+  </si>
+  <si>
+    <t>특수 스킬3</t>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2436,7 +2492,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2444,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2460,11 +2516,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2472,192 +2528,194 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>116</v>
+        <v>333</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>332</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>117</v>
+        <v>334</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>293</v>
+        <v>112</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="E6" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+    <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="9" t="s">
-        <v>282</v>
+      <c r="B14" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>106</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>104</v>
+        <v>322</v>
+      </c>
+      <c r="C17" t="s">
+        <v>99</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
-      <c r="B19" s="4"/>
+      <c r="B19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
       <c r="D19" s="13"/>
-      <c r="E19" s="9"/>
+      <c r="E19" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
       <c r="D20" s="13"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="9"/>
+      <c r="B22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2665,116 +2723,125 @@
     </row>
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
-      <c r="B24" t="s">
-        <v>126</v>
+      <c r="B24" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+    <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12"/>
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="8" t="s">
+      <c r="B27" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="8" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>39</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+      <c r="E33" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="B35" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F36"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2785,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2810,7 +2877,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2824,52 +2891,52 @@
         <v>29</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>298</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="R2" s="4" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>21</v>
@@ -2886,52 +2953,52 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="Q3" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>20</v>
@@ -2957,10 +3024,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" s="4">
         <v>0.3</v>
@@ -2969,10 +3036,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -2981,7 +3048,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -2990,15 +3057,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -3007,10 +3074,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I5" s="4">
         <v>0.8</v>
@@ -3019,7 +3086,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -3028,15 +3095,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3045,10 +3112,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
@@ -3057,7 +3124,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -3066,616 +3133,791 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>252</v>
+        <v>323</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>113</v>
+        <v>339</v>
       </c>
       <c r="F7" t="s">
+        <v>331</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="N7" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="O7" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>167</v>
+        <v>328</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>115</v>
+        <v>325</v>
+      </c>
+      <c r="F8" t="s">
+        <v>331</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="I8" s="4">
-        <v>99999</v>
+        <v>0.8</v>
       </c>
       <c r="J8" s="4">
-        <v>1</v>
+        <v>0.2</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>279</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>326</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>115</v>
+        <v>327</v>
+      </c>
+      <c r="F9" t="s">
+        <v>331</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="I9" s="4">
-        <v>99999</v>
-      </c>
-      <c r="J9" s="4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>57</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="b">
-        <v>1</v>
+        <v>338</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>3</v>
+        <v>332</v>
+      </c>
+      <c r="G10">
+        <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="J10" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L10" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="M10" s="4" t="b">
-        <v>1</v>
+        <v>204</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="4">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>3</v>
+        <v>332</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="J11" s="4">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0.5</v>
+        <v>204</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>225</v>
+        <v>337</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="4">
-        <v>3</v>
-      </c>
-      <c r="E12" s="4" t="b">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>3</v>
+        <v>332</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="J12" s="4">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L12" s="4">
-        <v>0.5</v>
+        <v>204</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>232</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="b">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="I13" s="4">
-        <v>1</v>
+        <v>99999</v>
       </c>
       <c r="J13" s="4">
         <v>1</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L13" s="4">
-        <v>1</v>
-      </c>
       <c r="R13" s="4" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>236</v>
+        <v>54</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D14" s="4">
-        <v>3</v>
-      </c>
-      <c r="E14" s="4" t="b">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="I14" s="4">
-        <v>1</v>
+        <v>99999</v>
       </c>
       <c r="J14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="L14" s="4">
-        <v>1</v>
-      </c>
       <c r="R14" s="4" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>169</v>
+        <v>84</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="I15" s="4">
-        <v>99999</v>
+        <v>0.3</v>
       </c>
       <c r="J15" s="4">
         <v>1</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>168</v>
+      <c r="K15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="M15" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>190</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>205</v>
+        <v>85</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="I16" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
+      <c r="E19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" s="4">
+        <v>99999</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="4">
         <v>2</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="K21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" s="4">
         <v>0.5</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="N17" s="4" t="s">
+      <c r="K22" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="4">
+        <v>5</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="4">
+        <v>2</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" s="4">
+        <v>5</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P24" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="O17" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q17" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="Q24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D25" s="4">
         <v>5</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I18" s="4">
+      <c r="F25" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G25" s="4">
         <v>2</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="H25" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
         <v>5</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="I19" s="4">
-        <v>1</v>
-      </c>
-      <c r="J19" s="4">
+      <c r="K25" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="L25" s="4">
         <v>0.2</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="N19" s="4" t="s">
+      <c r="N25" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="O19" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="Q25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" s="4">
         <v>5</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F26" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G26" s="4">
+        <v>2</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="L26" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R26" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="G20" s="4">
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="4">
+        <v>5</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G27" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H27" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="I27" s="4">
+        <v>2</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R27" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4">
-        <v>5</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="L20" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D21" s="4">
-        <v>5</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G21" s="4">
-        <v>2</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="I21" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="J21" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="L21" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="D22" s="4">
-        <v>5</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G22" s="4">
-        <v>2</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="I22" s="4">
-        <v>2</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="L22" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="I23" s="4">
+      <c r="I28" s="4">
         <v>99999</v>
       </c>
-      <c r="N23" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="N24" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>324</v>
+      <c r="N28" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q28" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="N29" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3705,7 +3947,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>6</v>
@@ -3719,40 +3961,40 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3766,16 +4008,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -3801,31 +4043,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -3839,31 +4081,31 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I5" s="4">
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -3877,31 +4119,31 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -3915,25 +4157,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -3941,25 +4183,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -3967,22 +4209,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3990,22 +4232,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -4013,25 +4255,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I11" s="4">
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -4039,25 +4281,25 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="I12" s="4">
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -4065,25 +4307,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -4091,36 +4333,36 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -4128,10 +4370,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>10</v>
@@ -4140,15 +4382,15 @@
         <v>24</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>10</v>
@@ -4157,7 +4399,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -4165,36 +4407,36 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -4202,22 +4444,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4226,7 +4468,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4240,19 +4482,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4260,19 +4502,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4280,19 +4522,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -4300,10 +4542,10 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>10</v>
@@ -4312,7 +4554,7 @@
         <v>24</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="J24" s="4">
         <v>0.1</v>
@@ -4320,10 +4562,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>10</v>
@@ -4332,7 +4574,7 @@
         <v>24</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J25" s="4">
         <v>0.2</v>
@@ -4340,22 +4582,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -4364,7 +4606,7 @@
         <v>100</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K26" s="4">
         <v>3</v>
@@ -4378,22 +4620,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -4402,7 +4644,7 @@
         <v>200</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4416,22 +4658,22 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>13</v>
@@ -4440,7 +4682,7 @@
         <v>400</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="K28" s="4">
         <v>1</v>
@@ -4454,22 +4696,22 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>13</v>
@@ -4478,7 +4720,7 @@
         <v>300</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="K29" s="4">
         <v>1</v>
@@ -4489,10 +4731,10 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>10</v>
@@ -4501,7 +4743,7 @@
         <v>24</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="J30" s="4">
         <v>2</v>
@@ -4533,44 +4775,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>20</v>
@@ -4579,57 +4821,57 @@
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -4637,10 +4879,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4648,10 +4890,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4659,43 +4901,43 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4731,10 +4973,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4744,52 +4986,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4809,14 +5051,17 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>335</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4825,18 +5070,18 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>252</v>
+        <v>344</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4845,15 +5090,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4862,7 +5107,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -4873,7 +5118,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -4884,7 +5129,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -4895,10 +5140,10 @@
         <v>10004</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="336">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1516,10 +1516,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>대시 스킬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1533,42 +1529,6 @@
   </si>
   <si>
     <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시어택 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DASH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DASH_ATTACK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시공격 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DASH_ATTACK_DAMAGE_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1825,10 +1785,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_ACTIVATE_BUFF_DASH_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
   </si>
   <si>
@@ -1953,6 +1909,14 @@
   </si>
   <si>
     <t>SKILL_SPECIALATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DASH_ATTACK_DAMAGE_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2492,7 +2456,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2516,11 +2480,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2533,24 +2497,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2563,13 +2527,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2618,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
@@ -2635,7 +2599,7 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2654,7 +2618,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C17" t="s">
         <v>99</v>
@@ -2667,7 +2631,7 @@
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>103</v>
@@ -2784,7 +2748,7 @@
         <v>36</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2877,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2894,28 +2858,28 @@
         <v>196</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>151</v>
@@ -2953,7 +2917,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -3138,19 +3102,19 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="F7" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="G7">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3165,7 +3129,7 @@
         <v>146</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>125</v>
@@ -3173,19 +3137,19 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="F8" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="G8">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I8" s="4">
         <v>0.8</v>
@@ -3203,7 +3167,7 @@
         <v>146</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>125</v>
@@ -3211,13 +3175,13 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="F9" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="G9">
         <v>20</v>
@@ -3238,21 +3202,21 @@
         <v>146</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="G10">
         <v>20</v>
@@ -3273,7 +3237,7 @@
         <v>146</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>125</v>
@@ -3281,19 +3245,19 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I11" s="4">
         <v>0.4</v>
@@ -3308,7 +3272,7 @@
         <v>146</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>125</v>
@@ -3316,13 +3280,13 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="G12">
         <v>20</v>
@@ -3340,7 +3304,7 @@
         <v>146</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>125</v>
@@ -3348,7 +3312,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>42</v>
@@ -3366,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -3569,7 +3533,7 @@
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>163</v>
@@ -3671,7 +3635,7 @@
         <v>248</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D23" s="4">
         <v>5</v>
@@ -3688,16 +3652,13 @@
       <c r="K23" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="R23" s="4" t="s">
-        <v>255</v>
-      </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>249</v>
+        <v>334</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
@@ -3706,7 +3667,7 @@
         <v>202</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I24" s="4">
         <v>1</v>
@@ -3730,27 +3691,27 @@
         <v>162</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>254</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D25" s="4">
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="G25" s="4">
         <v>2</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="I25" s="4">
         <v>1</v>
@@ -3759,7 +3720,7 @@
         <v>5</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="L25" s="4">
         <v>0.2</v>
@@ -3777,27 +3738,27 @@
         <v>162</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I26" s="4">
         <v>1.5</v>
@@ -3806,7 +3767,7 @@
         <v>0.5</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="L26" s="4">
         <v>0.2</v>
@@ -3824,33 +3785,33 @@
         <v>162</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="I27" s="4">
         <v>2</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="L27" s="4">
         <v>0.2</v>
@@ -3868,21 +3829,21 @@
         <v>162</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>201</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I28" s="4">
         <v>99999</v>
@@ -3894,13 +3855,13 @@
         <v>146</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="Q28" s="4" t="s">
         <v>162</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
@@ -3911,13 +3872,13 @@
         <v>146</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="Q29" s="4" t="s">
         <v>162</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -3929,7 +3890,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3976,10 +3937,10 @@
         <v>74</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>23</v>
@@ -4290,7 +4251,7 @@
         <v>43</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>44</v>
@@ -4350,7 +4311,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>47</v>
@@ -4494,7 +4455,7 @@
         <v>24</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4542,56 +4503,92 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>10</v>
+        <v>43</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="J24" s="4">
-        <v>0.1</v>
+        <v>13</v>
+      </c>
+      <c r="I24" s="4">
+        <v>100</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="4">
+        <v>3</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1</v>
+      </c>
+      <c r="M24" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>10</v>
+        <v>43</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="J25" s="4">
-        <v>0.2</v>
+        <v>13</v>
+      </c>
+      <c r="I25" s="4">
+        <v>200</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>135</v>
@@ -4603,13 +4600,13 @@
         <v>13</v>
       </c>
       <c r="I26" s="4">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="K26" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" s="4">
         <v>1</v>
@@ -4620,10 +4617,10 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>43</v>
@@ -4641,111 +4638,35 @@
         <v>13</v>
       </c>
       <c r="I27" s="4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
       </c>
       <c r="L27" s="4">
-        <v>1</v>
-      </c>
-      <c r="M27" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="4">
-        <v>400</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K28" s="4">
-        <v>1</v>
-      </c>
-      <c r="L28" s="4">
-        <v>1</v>
-      </c>
-      <c r="M28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B29" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="4">
-        <v>300</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K29" s="4">
-        <v>1</v>
-      </c>
-      <c r="L29" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H30" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="J30" s="4">
+      <c r="I28" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="J28" s="4">
         <v>2</v>
       </c>
     </row>
@@ -4757,7 +4678,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -4868,7 +4789,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>170</v>
@@ -4879,7 +4800,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>171</v>
@@ -4901,7 +4822,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>188</v>
@@ -4915,29 +4836,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -5054,7 +4956,7 @@
         <v>241</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
@@ -5073,7 +4975,7 @@
         <v>242</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
@@ -5090,7 +4992,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
@@ -5129,7 +5031,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -5143,7 +5045,7 @@
         <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="337">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -120,10 +120,6 @@
   </si>
   <si>
     <t>Effect_2</t>
-  </si>
-  <si>
-    <t>FinishEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_3</t>
@@ -1131,15 +1127,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Effect_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1917,6 +1905,22 @@
   </si>
   <si>
     <t>SE_DASH_ATTACK_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FinishEffect</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2480,11 +2484,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2492,48 +2496,48 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2555,7 +2559,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>18</v>
@@ -2571,7 +2575,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>19</v>
@@ -2582,76 +2586,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
         <v>101</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2672,14 +2676,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2688,7 +2692,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2697,7 +2701,7 @@
     <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="13"/>
@@ -2711,11 +2715,11 @@
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -2723,32 +2727,32 @@
         <v>13</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E30" s="9" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2756,10 +2760,10 @@
         <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2767,21 +2771,21 @@
         <v>15</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2792,18 +2796,18 @@
         <v>0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37"/>
     </row>
@@ -2816,7 +2820,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2841,7 +2845,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2852,117 +2856,117 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>281</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>182</v>
+        <v>334</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="V2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="W2" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="X2" s="4" t="s">
-        <v>22</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="O3" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>20</v>
@@ -2988,10 +2992,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="4">
         <v>0.3</v>
@@ -3000,10 +3004,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I4" s="4">
         <v>0.5</v>
@@ -3012,7 +3016,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -3021,15 +3025,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -3038,10 +3042,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="4">
         <v>0.8</v>
@@ -3050,7 +3054,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -3059,15 +3063,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3076,10 +3080,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
@@ -3088,7 +3092,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -3097,59 +3101,59 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G7">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G8">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I8" s="4">
         <v>0.8</v>
@@ -3158,170 +3162,170 @@
         <v>0.2</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G9">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I9" s="4">
         <v>2</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>327</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G10">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I10" s="4">
         <v>0.5</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I11" s="4">
         <v>0.4</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G12">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I13" s="4">
         <v>99999</v>
@@ -3330,21 +3334,21 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I14" s="4">
         <v>99999</v>
@@ -3353,15 +3357,15 @@
         <v>1</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -3373,7 +3377,7 @@
         <v>3</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I15" s="4">
         <v>0.3</v>
@@ -3382,7 +3386,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L15" s="4">
         <v>0.3</v>
@@ -3391,15 +3395,15 @@
         <v>1</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" s="4">
         <v>3</v>
@@ -3408,7 +3412,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I16" s="4">
         <v>0.3</v>
@@ -3417,21 +3421,21 @@
         <v>1</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L16" s="4">
         <v>0.5</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D17" s="4">
         <v>3</v>
@@ -3443,7 +3447,7 @@
         <v>3</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I17" s="4">
         <v>0.2</v>
@@ -3452,21 +3456,21 @@
         <v>1</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L17" s="4">
         <v>0.5</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -3478,7 +3482,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -3487,21 +3491,21 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L18" s="4">
         <v>1</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D19" s="4">
         <v>3</v>
@@ -3513,7 +3517,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -3522,27 +3526,27 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L19" s="4">
         <v>1</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I20" s="4">
         <v>99999</v>
@@ -3551,123 +3555,123 @@
         <v>1</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I21" s="4">
         <v>2</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M21" s="4" t="b">
         <v>1</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I22" s="4">
         <v>0.5</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D23" s="4">
         <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I23" s="4">
         <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I24" s="4">
         <v>1</v>
@@ -3676,42 +3680,42 @@
         <v>0.2</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D25" s="4">
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G25" s="4">
         <v>2</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I25" s="4">
         <v>1</v>
@@ -3720,45 +3724,45 @@
         <v>5</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="L25" s="4">
         <v>0.2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I26" s="4">
         <v>1.5</v>
@@ -3767,118 +3771,101 @@
         <v>0.5</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L26" s="4">
         <v>0.2</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>279</v>
+        <v>333</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I27" s="4">
         <v>2</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L27" s="4">
         <v>0.2</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I28" s="4">
         <v>99999</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="N29" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q29" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -3908,7 +3895,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>6</v>
@@ -3922,40 +3909,40 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -3969,16 +3956,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -4004,31 +3991,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -4042,31 +4029,31 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I5" s="4">
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -4080,31 +4067,31 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -4118,25 +4105,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -4144,25 +4131,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -4170,22 +4157,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4193,22 +4180,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -4216,25 +4203,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I11" s="4">
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -4242,25 +4229,25 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I12" s="4">
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -4268,25 +4255,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -4294,36 +4281,36 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -4331,27 +4318,27 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>10</v>
@@ -4360,7 +4347,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -4368,36 +4355,36 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -4405,22 +4392,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4429,7 +4416,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4443,19 +4430,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4463,19 +4450,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4483,19 +4470,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -4503,22 +4490,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>13</v>
@@ -4527,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K24" s="4">
         <v>3</v>
@@ -4541,22 +4528,22 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>13</v>
@@ -4565,7 +4552,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4579,22 +4566,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -4603,7 +4590,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4617,22 +4604,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -4641,7 +4628,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4652,19 +4639,19 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4696,44 +4683,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>20</v>
@@ -4742,57 +4729,57 @@
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -4800,10 +4787,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4811,10 +4798,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4822,24 +4809,24 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4875,10 +4862,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4888,52 +4875,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>239</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4953,17 +4940,17 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4972,18 +4959,18 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4992,15 +4979,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -5009,7 +4996,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -5020,7 +5007,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -5031,7 +5018,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -5042,10 +5029,10 @@
         <v>10004</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="350">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -952,10 +952,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>EffectVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>horizontal-slash</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1375,6 +1371,84 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>BaseAttackSkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시공격 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시어택 데미지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillScanType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionEffectTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 단일 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_INCREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+  </si>
+  <si>
+    <t>캐스팅 범위(직선) 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1385,7 +1459,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_1]</t>
+      <t>[ScanParam_1]</t>
     </r>
     <r>
       <rPr>
@@ -1395,7 +1469,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 기본데미지 </t>
+      <t xml:space="preserve"> : 사정거리 </t>
     </r>
     <r>
       <rPr>
@@ -1407,7 +1481,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_2]</t>
+      <t>[ScanParam_2]</t>
     </r>
     <r>
       <rPr>
@@ -1417,19 +1491,224 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 데미지 계수 속성 </t>
-    </r>
+      <t xml:space="preserve"> : 타갯 수</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>발동확률 0~1 = 0~100%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 스킬 데미지1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 스킬 데미지2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCastingTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting;Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionNames</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_SILENCE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_MATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 범위(원형) 공격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting;Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BREAK</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_DAMAGE_IMMUNITY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적 버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무적 효과</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_STUN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood_bat_finisher_05</t>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
+        <color theme="8"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_3]</t>
+      <t>[Param_1]</t>
     </r>
     <r>
       <rPr>
@@ -1439,19 +1718,106 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 데미지 계수값  </t>
-    </r>
+      <t xml:space="preserve"> : 버프 ID</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitCaster</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동(시전자)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타격시 n% 확률로 발동(피격자)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_03</t>
+  </si>
+  <si>
+    <t>특수 스킬1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수 스킬2</t>
+  </si>
+  <si>
+    <t>특수 스킬3</t>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsOnHitTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DASH_ATTACK_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FinishEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>발사체 생성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF0070C0"/>
+        <color theme="8"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_4]</t>
+      <t>[Param_1]</t>
     </r>
     <r>
       <rPr>
@@ -1461,19 +1827,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
+      <t xml:space="preserve"> : 기본데미지 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF0070C0"/>
+        <color theme="4" tint="-0.249977111117893"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[Param_5]</t>
+      <t>[Param_2]</t>
     </r>
     <r>
       <rPr>
@@ -1483,100 +1849,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseAttackSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시공격 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시어택 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillScanType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionEffectTime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 단일 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-  </si>
-  <si>
-    <t>캐스팅 범위(직선) 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> : 데미지 계수 속성 </t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
+        <color theme="4" tint="-0.249977111117893"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[ScanParam_1]</t>
+      <t>[Param_3]</t>
     </r>
     <r>
       <rPr>
@@ -1586,19 +1871,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 사정거리 </t>
+      <t xml:space="preserve"> : 데미지 계수값  </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="4" tint="-0.249977111117893"/>
+        <color rgb="FF0070C0"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[ScanParam_2]</t>
+      <t>[Param_4]</t>
     </r>
     <r>
       <rPr>
@@ -1608,227 +1893,75 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 타갯 수</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>발동확률 0~1 = 0~100%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CASTING_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CASTING_DAMAGE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 스킬 데미지1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 스킬 데미지2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillCastingTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting;Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MotionNames</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 범위(원형) 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting;Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무적 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무적 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무적 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wood_bat_finisher_05</t>
-  </si>
-  <si>
-    <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
+      <t xml:space="preserve"> : 브레이크데미지 배율 </t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
+        <color rgb="FF0070C0"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>[Param_5]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DAMAGE_IMMUNITY</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 발사체 공격1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnProjectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Projectile_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_PROJECTILE_DAMAGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 발사1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 데미지1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>[Param_1]</t>
     </r>
     <r>
@@ -1836,91 +1969,101 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> : 버프 ID</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHitCaster</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHitTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동(시전자)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>타격시 n% 확률로 발동(피격자)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SPECIALATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SPECIALATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_SPECIALATTACK_03</t>
-  </si>
-  <si>
-    <t>특수 스킬1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>특수 스킬2</t>
-  </si>
-  <si>
-    <t>특수 스킬3</t>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SPECIALATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DASH_ATTACK_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FinishEffect</t>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 발사체 개수 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 발사 각도 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 발사체 프리펩 이름 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 발사체 효과(SkillEffcetID)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnProjectile</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2468,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2484,11 +2627,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2501,24 +2644,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2531,13 +2674,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2586,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
@@ -2603,7 +2746,7 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2622,7 +2765,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C17" t="s">
         <v>98</v>
@@ -2635,7 +2778,7 @@
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>102</v>
@@ -2715,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="8" t="s">
@@ -2730,7 +2873,7 @@
         <v>72</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>241</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2752,7 +2895,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2779,37 +2922,48 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>168</v>
+        <v>339</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="B36" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F37"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2820,7 +2974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -2845,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -2859,52 +3013,52 @@
         <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>21</v>
@@ -2916,12 +3070,12 @@
         <v>30</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -2930,7 +3084,7 @@
         <v>65</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>8</v>
@@ -2960,13 +3114,13 @@
         <v>132</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>20</v>
@@ -2992,7 +3146,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>82</v>
@@ -3004,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>97</v>
@@ -3016,7 +3170,7 @@
         <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L4" s="4">
         <v>0.1</v>
@@ -3025,15 +3179,15 @@
         <v>1</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -3042,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>97</v>
@@ -3054,7 +3208,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L5" s="4">
         <v>0.1</v>
@@ -3063,15 +3217,15 @@
         <v>1</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3080,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I6" s="4">
         <v>2</v>
@@ -3092,7 +3246,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L6" s="4">
         <v>0.1</v>
@@ -3101,39 +3255,39 @@
         <v>1</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G7">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>124</v>
@@ -3141,19 +3295,19 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G8">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I8" s="4">
         <v>0.8</v>
@@ -3162,16 +3316,16 @@
         <v>0.2</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>124</v>
@@ -3179,48 +3333,48 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G9">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I9" s="4">
         <v>2</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G10">
         <v>20</v>
@@ -3232,16 +3386,16 @@
         <v>0.5</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>124</v>
@@ -3249,34 +3403,34 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I11" s="4">
         <v>0.4</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>124</v>
@@ -3284,31 +3438,31 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G12">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>124</v>
@@ -3316,7 +3470,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>41</v>
@@ -3325,7 +3479,7 @@
         <v>111</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I13" s="4">
         <v>99999</v>
@@ -3334,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -3432,10 +3586,10 @@
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D17" s="4">
         <v>3</v>
@@ -3462,15 +3616,15 @@
         <v>0.5</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -3497,15 +3651,15 @@
         <v>1</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D19" s="4">
         <v>3</v>
@@ -3526,27 +3680,27 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L19" s="4">
         <v>1</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I20" s="4">
         <v>99999</v>
@@ -3555,30 +3709,30 @@
         <v>1</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="S20" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>3</v>
@@ -3596,21 +3750,21 @@
         <v>1</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>130</v>
@@ -3619,16 +3773,16 @@
         <v>0.5</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R22" s="4" t="s">
         <v>124</v>
@@ -3636,16 +3790,16 @@
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D23" s="4">
         <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>130</v>
@@ -3654,24 +3808,24 @@
         <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I24" s="4">
         <v>1</v>
@@ -3680,42 +3834,42 @@
         <v>0.2</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D25" s="4">
         <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G25" s="4">
         <v>2</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I25" s="4">
         <v>1</v>
@@ -3724,45 +3878,45 @@
         <v>5</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L25" s="4">
         <v>0.2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I26" s="4">
         <v>1.5</v>
@@ -3771,101 +3925,133 @@
         <v>0.5</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L26" s="4">
         <v>0.2</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I27" s="4">
         <v>2</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L27" s="4">
         <v>0.2</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I28" s="4">
         <v>99999</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L29" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -3877,7 +4063,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3888,7 +4074,9 @@
     <col min="8" max="8" width="23.125" style="4" customWidth="1"/>
     <col min="9" max="9" width="32.25" style="4" customWidth="1"/>
     <col min="10" max="10" width="29.375" style="4" customWidth="1"/>
-    <col min="11" max="13" width="13.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.875" style="4" customWidth="1"/>
     <col min="14" max="15" width="13.75" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="4"/>
   </cols>
@@ -3909,31 +4097,31 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>122</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>135</v>
+        <v>347</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>62</v>
@@ -3962,10 +4150,10 @@
         <v>132</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -3994,7 +4182,7 @@
         <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>42</v>
@@ -4006,7 +4194,7 @@
         <v>133</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>43</v>
@@ -4032,7 +4220,7 @@
         <v>88</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>42</v>
@@ -4044,7 +4232,7 @@
         <v>133</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>43</v>
@@ -4070,7 +4258,7 @@
         <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>42</v>
@@ -4082,7 +4270,7 @@
         <v>133</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>43</v>
@@ -4157,22 +4345,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4180,10 +4368,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>42</v>
@@ -4238,7 +4426,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>43</v>
@@ -4267,7 +4455,7 @@
         <v>120</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
@@ -4290,15 +4478,15 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>46</v>
@@ -4364,15 +4552,15 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>47</v>
@@ -4381,7 +4569,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>79</v>
@@ -4407,7 +4595,7 @@
         <v>134</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4416,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4430,19 +4618,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4450,19 +4638,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4470,19 +4658,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -4490,22 +4678,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>134</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>13</v>
@@ -4528,10 +4716,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>42</v>
@@ -4543,7 +4731,7 @@
         <v>134</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>13</v>
@@ -4552,7 +4740,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4566,10 +4754,10 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>42</v>
@@ -4581,7 +4769,7 @@
         <v>134</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -4590,7 +4778,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4604,10 +4792,10 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>42</v>
@@ -4619,7 +4807,7 @@
         <v>134</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -4628,7 +4816,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4639,10 +4827,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4651,10 +4839,68 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="4">
+        <v>150</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4694,22 +4940,22 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4732,10 +4978,10 @@
         <v>68</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4762,7 +5008,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>40</v>
@@ -4776,10 +5022,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -4787,10 +5033,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -4798,10 +5044,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -4809,24 +5055,24 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4862,10 +5108,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -4875,52 +5121,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>236</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -4940,17 +5186,17 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -4959,18 +5205,18 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="16"/>
       <c r="H5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -4979,15 +5225,15 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E6" s="18"/>
       <c r="G6" s="16"/>
       <c r="H6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -4996,7 +5242,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -5007,7 +5253,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>217</v>
+        <v>345</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -5018,7 +5264,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -5029,10 +5275,10 @@
         <v>10004</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="364">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1952,6 +1952,22 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>SE_SPAWNPOJECTILE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectVFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnProjectile</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2042,8 +2058,73 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> : 발사체 효과(SkillEffcetID)</t>
-    </r>
+      <t xml:space="preserve"> : 발사체 효과(SkillEffcetID) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[Param_5]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 발사체 효과 반경(0이면 단일)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_02</t>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_03</t>
+  </si>
+  <si>
+    <t>투사체 발사2</t>
+  </si>
+  <si>
+    <t>투사체 발사3</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_02</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_03</t>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 발사체 공격2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 발사체 공격3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2051,19 +2132,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnProjectile</t>
+    <t>SKILL_PROJECTILE_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2928,7 +3001,7 @@
         <v>334</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2974,7 +3047,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -4024,13 +4097,13 @@
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>337</v>
       </c>
       <c r="D29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4" t="b">
         <v>1</v>
@@ -4051,7 +4124,65 @@
         <v>0.1</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -4063,7 +4194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -4103,7 +4234,7 @@
         <v>122</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>136</v>
@@ -4847,7 +4978,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>342</v>
@@ -4856,13 +4987,10 @@
         <v>42</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
-      </c>
-      <c r="J29" s="4">
-        <v>0</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>340</v>
@@ -4873,33 +5001,85 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="H30" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I30" s="4">
+        <v>3</v>
+      </c>
+      <c r="J30" s="4">
+        <v>30</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I32" s="4">
         <v>150</v>
       </c>
-      <c r="J30" s="4" t="s">
+      <c r="J32" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K30" s="4">
+      <c r="K32" s="4">
         <v>1</v>
       </c>
     </row>
@@ -5089,7 +5269,7 @@
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.875" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="26.375" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="21.75" style="4" bestFit="1" customWidth="1"/>
@@ -5253,7 +5433,13 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>345</v>
+        <v>362</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>356</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="364">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2676,7 +2676,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4986,6 +4986,15 @@
       <c r="D29" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="E29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="H29" s="4" t="s">
         <v>347</v>
       </c>
@@ -5009,6 +5018,15 @@
       <c r="D30" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="E30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="H30" s="4" t="s">
         <v>339</v>
       </c>
@@ -5034,6 +5052,15 @@
       </c>
       <c r="D31" s="4" t="s">
         <v>42</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>339</v>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="365">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1315,10 +1315,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1568,22 +1564,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>캐스팅 범위(원형) 공격</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1674,19 +1654,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_POWERATTACK_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>강타 스킬2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1775,14 +1747,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_SPECIALATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_DASH_ATTACK_DAMAGE_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2129,14 +2093,49 @@
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_PROJECTILE_ATTACK_02</t>
+    <t>SKILL_CASTING_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_ATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_MATK_RANGE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_03</t>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2344,7 +2343,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2391,9 +2390,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
@@ -2676,7 +2672,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2700,11 +2696,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2717,24 +2713,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2747,13 +2743,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2802,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
@@ -2819,7 +2815,7 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2838,7 +2834,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
         <v>98</v>
@@ -2851,7 +2847,7 @@
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>102</v>
@@ -2946,7 +2942,7 @@
         <v>72</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2968,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2995,13 +2991,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3072,7 +3068,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -3089,28 +3085,28 @@
         <v>192</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="K2" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>149</v>
@@ -3125,10 +3121,10 @@
         <v>155</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>178</v>
@@ -3143,12 +3139,12 @@
         <v>30</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -3333,19 +3329,19 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F7" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G7">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -3360,7 +3356,7 @@
         <v>144</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>124</v>
@@ -3368,19 +3364,19 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" t="s">
         <v>307</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F8" t="s">
-        <v>314</v>
       </c>
       <c r="G8">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I8" s="4">
         <v>0.8</v>
@@ -3398,7 +3394,7 @@
         <v>144</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>124</v>
@@ -3406,13 +3402,13 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F9" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G9">
         <v>20</v>
@@ -3433,21 +3429,21 @@
         <v>144</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G10">
         <v>20</v>
@@ -3468,7 +3464,7 @@
         <v>144</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>124</v>
@@ -3476,19 +3472,19 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G11">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I11" s="4">
         <v>0.4</v>
@@ -3503,7 +3499,7 @@
         <v>144</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>124</v>
@@ -3511,13 +3507,13 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G12">
         <v>20</v>
@@ -3535,7 +3531,7 @@
         <v>144</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>124</v>
@@ -3543,7 +3539,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>41</v>
@@ -3561,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -3729,7 +3725,7 @@
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>226</v>
+        <v>358</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>225</v>
@@ -3753,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L19" s="4">
         <v>1</v>
@@ -3764,7 +3760,7 @@
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>161</v>
@@ -3863,10 +3859,10 @@
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="D23" s="4">
         <v>5</v>
@@ -3886,10 +3882,10 @@
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
@@ -3898,7 +3894,7 @@
         <v>198</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I24" s="4">
         <v>1</v>
@@ -3922,27 +3918,27 @@
         <v>160</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D25" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G25" s="4">
         <v>2</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="I25" s="4">
         <v>1</v>
@@ -3951,7 +3947,7 @@
         <v>5</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="L25" s="4">
         <v>0.2</v>
@@ -3969,27 +3965,27 @@
         <v>160</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>280</v>
+        <v>357</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D26" s="4">
         <v>5</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G26" s="4">
         <v>2</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I26" s="4">
         <v>1.5</v>
@@ -3998,7 +3994,7 @@
         <v>0.5</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L26" s="4">
         <v>0.2</v>
@@ -4016,33 +4012,33 @@
         <v>160</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>282</v>
+        <v>360</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="G27" s="4">
         <v>2</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I27" s="4">
         <v>2</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L27" s="4">
         <v>0.2</v>
@@ -4060,21 +4056,21 @@
         <v>160</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>197</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I28" s="4">
         <v>99999</v>
@@ -4086,24 +4082,24 @@
         <v>144</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="Q28" s="4" t="s">
         <v>160</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D29" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E29" s="4" t="b">
         <v>1</v>
@@ -4112,7 +4108,7 @@
         <v>3</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
@@ -4124,24 +4120,24 @@
         <v>0.1</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D30" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -4153,24 +4149,24 @@
         <v>0.1</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D31" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
@@ -4182,7 +4178,7 @@
         <v>0.1</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -4234,7 +4230,7 @@
         <v>122</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>136</v>
@@ -4243,10 +4239,10 @@
         <v>73</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4557,7 +4553,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>43</v>
@@ -4617,7 +4613,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>46</v>
@@ -4735,7 +4731,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4761,7 +4757,7 @@
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4809,16 +4805,16 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>134</v>
@@ -4847,10 +4843,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>42</v>
@@ -4871,7 +4867,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4885,10 +4881,10 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>42</v>
@@ -4909,7 +4905,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4923,10 +4919,10 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>42</v>
@@ -4947,7 +4943,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4958,10 +4954,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4970,7 +4966,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4978,10 +4974,10 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>42</v>
@@ -4996,24 +4992,24 @@
         <v>142</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>42</v>
@@ -5028,7 +5024,7 @@
         <v>142</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -5037,18 +5033,18 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>42</v>
@@ -5063,16 +5059,16 @@
         <v>142</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5080,16 +5076,16 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>134</v>
@@ -5101,7 +5097,7 @@
         <v>13</v>
       </c>
       <c r="I32" s="4">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>74</v>
@@ -5153,7 +5149,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>148</v>
@@ -5229,7 +5225,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>168</v>
@@ -5240,7 +5236,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>169</v>
@@ -5262,7 +5258,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>184</v>
@@ -5276,10 +5272,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5290,7 +5286,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -5314,11 +5310,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>228</v>
+      <c r="A1" s="18" t="s">
+        <v>227</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -5328,52 +5324,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -5393,18 +5389,15 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>328</v>
+        <v>361</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="G4" s="16"/>
-      <c r="H4" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>194</v>
-      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
@@ -5412,19 +5405,15 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="E5" s="18"/>
+        <v>361</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>363</v>
+      </c>
       <c r="G5" s="16"/>
-      <c r="H5" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>194</v>
-      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
@@ -5432,20 +5421,19 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="E6" s="18"/>
+        <v>284</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>363</v>
+      </c>
       <c r="G6" s="16"/>
-      <c r="H6" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>194</v>
-      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -5456,89 +5444,116 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="20">
-        <v>10004</v>
+      <c r="B10">
+        <v>20001</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E11" s="16"/>
+      <c r="B11">
+        <v>30001</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E12" s="16"/>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>100001</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C17"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C19"/>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D20"/>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D21"/>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D22"/>
     </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D23"/>
     </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D24"/>
     </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D25"/>
     </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D26"/>
     </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D27"/>
     </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D28"/>
     </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D29"/>
     </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D30"/>
     </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D31"/>
     </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D32"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
@@ -5561,9 +5576,6 @@
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="367">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2136,6 +2136,14 @@
   </si>
   <si>
     <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaCost</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3043,27 +3051,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="36.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="22.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15" style="4" customWidth="1"/>
-    <col min="6" max="12" width="23.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" style="4" customWidth="1"/>
-    <col min="15" max="15" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="39.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="36.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="22" style="4" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="4"/>
+    <col min="4" max="6" width="15" style="4" customWidth="1"/>
+    <col min="7" max="13" width="23.75" style="4" customWidth="1"/>
+    <col min="14" max="14" width="14.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.25" style="4" customWidth="1"/>
+    <col min="16" max="16" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.375" style="4" customWidth="1"/>
+    <col min="19" max="19" width="39.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="36.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="22" style="4" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3071,7 +3079,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3085,64 +3093,67 @@
         <v>192</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>290</v>
       </c>
@@ -3156,43 +3167,43 @@
         <v>154</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>20</v>
@@ -3212,8 +3223,11 @@
       <c r="X3" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>177</v>
       </c>
@@ -3226,32 +3240,35 @@
       <c r="E4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>0.5</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>120</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <v>0.1</v>
       </c>
-      <c r="M4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4" t="s">
+      <c r="N4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" s="4" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>205</v>
       </c>
@@ -3264,32 +3281,35 @@
       <c r="E5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="4">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="4">
+      <c r="J5" s="4">
         <v>0.8</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <v>180</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>0.1</v>
       </c>
-      <c r="M5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="s">
+      <c r="N5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>206</v>
       </c>
@@ -3302,288 +3322,291 @@
       <c r="E6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="4">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>2</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>3</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>0.1</v>
       </c>
-      <c r="M6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4" t="s">
+      <c r="N6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>307</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>20</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="R7" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="S7" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>301</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>307</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>20</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>0.8</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>0.2</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="R8" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="S8" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>364</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>307</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>20</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>2</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="R9" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="S9" s="4" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>311</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>20</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I10" s="4">
+      <c r="J10" s="4">
         <v>0.5</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="O10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="R10" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>312</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>20</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>0.4</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="R11" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>313</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>20</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="O12" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="P12" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="R12" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="S12" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>255</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="I13" s="4">
+      <c r="J13" s="4">
         <v>99999</v>
       </c>
-      <c r="J13" s="4">
-        <v>1</v>
-      </c>
-      <c r="R13" s="4" t="s">
+      <c r="K13" s="4">
+        <v>1</v>
+      </c>
+      <c r="S13" s="4" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I14" s="4">
+      <c r="J14" s="4">
         <v>99999</v>
       </c>
-      <c r="J14" s="4">
-        <v>1</v>
-      </c>
-      <c r="R14" s="4" t="s">
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="S14" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>81</v>
       </c>
@@ -3596,32 +3619,32 @@
       <c r="E15" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>0.3</v>
       </c>
-      <c r="J15" s="4">
-        <v>1</v>
-      </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="4">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <v>0.3</v>
       </c>
-      <c r="M15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" s="4" t="s">
+      <c r="N15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>80</v>
       </c>
@@ -3631,29 +3654,29 @@
       <c r="D16" s="4">
         <v>3</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>0.3</v>
       </c>
-      <c r="J16" s="4">
-        <v>1</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="4">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L16" s="4">
+      <c r="M16" s="4">
         <v>0.5</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="S16" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>215</v>
       </c>
@@ -3666,29 +3689,29 @@
       <c r="E17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="4">
+      <c r="J17" s="4">
         <v>0.2</v>
       </c>
-      <c r="J17" s="4">
-        <v>1</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="4">
         <v>0.5</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="S17" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>216</v>
       </c>
@@ -3701,29 +3724,29 @@
       <c r="E18" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="4">
-        <v>1</v>
-      </c>
       <c r="J18" s="4">
         <v>1</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="4">
+        <v>1</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L18" s="4">
-        <v>1</v>
-      </c>
-      <c r="R18" s="4" t="s">
+      <c r="M18" s="4">
+        <v>1</v>
+      </c>
+      <c r="S18" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>358</v>
       </c>
@@ -3736,93 +3759,93 @@
       <c r="E19" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="4">
-        <v>1</v>
-      </c>
       <c r="J19" s="4">
         <v>1</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="L19" s="4">
-        <v>1</v>
-      </c>
-      <c r="R19" s="4" t="s">
+      <c r="M19" s="4">
+        <v>1</v>
+      </c>
+      <c r="S19" s="4" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>288</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="I20" s="4">
+      <c r="J20" s="4">
         <v>99999</v>
       </c>
-      <c r="J20" s="4">
-        <v>1</v>
-      </c>
-      <c r="N20" s="4" t="s">
+      <c r="K20" s="4">
+        <v>1</v>
+      </c>
+      <c r="O20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="P20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="Q20" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="R20" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R20" s="4" t="s">
+      <c r="S20" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="S20" s="4" t="s">
+      <c r="T20" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>193</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I21" s="4">
+      <c r="J21" s="4">
         <v>2</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="L21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="M21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" s="4" t="s">
+      <c r="N21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>194</v>
       </c>
@@ -3832,32 +3855,32 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I22" s="4">
+      <c r="J22" s="4">
         <v>0.5</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="L22" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="O22" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="P22" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="R22" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="S22" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>242</v>
       </c>
@@ -3867,20 +3890,20 @@
       <c r="D23" s="4">
         <v>5</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="I23" s="4">
+      <c r="J23" s="4">
         <v>2</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="L23" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>355</v>
       </c>
@@ -3890,38 +3913,38 @@
       <c r="D24" s="4">
         <v>5</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="I24" s="4">
-        <v>1</v>
-      </c>
       <c r="J24" s="4">
+        <v>1</v>
+      </c>
+      <c r="K24" s="4">
         <v>0.2</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="L24" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="O24" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="P24" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P24" s="4" t="s">
+      <c r="Q24" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q24" s="4" t="s">
+      <c r="R24" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R24" s="4" t="s">
+      <c r="S24" s="4" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>354</v>
       </c>
@@ -3931,44 +3954,44 @@
       <c r="D25" s="4">
         <v>2</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="G25" s="4">
+      <c r="H25" s="4">
         <v>2</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="I25" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="I25" s="4">
-        <v>1</v>
-      </c>
       <c r="J25" s="4">
+        <v>1</v>
+      </c>
+      <c r="K25" s="4">
         <v>5</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="L25" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="L25" s="4">
+      <c r="M25" s="4">
         <v>0.2</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="O25" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="P25" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="Q25" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q25" s="4" t="s">
+      <c r="R25" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R25" s="4" t="s">
+      <c r="S25" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>357</v>
       </c>
@@ -3978,44 +4001,44 @@
       <c r="D26" s="4">
         <v>5</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="G26" s="4">
+      <c r="H26" s="4">
         <v>2</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="I26" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="I26" s="4">
+      <c r="J26" s="4">
         <v>1.5</v>
       </c>
-      <c r="J26" s="4">
+      <c r="K26" s="4">
         <v>0.5</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="L26" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="L26" s="4">
+      <c r="M26" s="4">
         <v>0.2</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="O26" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="P26" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P26" s="4" t="s">
+      <c r="Q26" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q26" s="4" t="s">
+      <c r="R26" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R26" s="4" t="s">
+      <c r="S26" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>360</v>
       </c>
@@ -4025,73 +4048,73 @@
       <c r="D27" s="4">
         <v>5</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="G27" s="4">
+      <c r="H27" s="4">
         <v>2</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="I27" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="I27" s="4">
+      <c r="J27" s="4">
         <v>2</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="L27" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="L27" s="4">
+      <c r="M27" s="4">
         <v>0.2</v>
       </c>
-      <c r="N27" s="4" t="s">
+      <c r="O27" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="O27" s="4" t="s">
+      <c r="P27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P27" s="4" t="s">
+      <c r="Q27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q27" s="4" t="s">
+      <c r="R27" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R27" s="4" t="s">
+      <c r="S27" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>327</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="I28" s="4">
+      <c r="J28" s="4">
         <v>99999</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="O28" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="O28" s="4" t="s">
+      <c r="P28" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P28" s="4" t="s">
+      <c r="Q28" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="Q28" s="4" t="s">
+      <c r="R28" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R28" s="4" t="s">
+      <c r="S28" s="4" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>353</v>
       </c>
@@ -4104,26 +4127,26 @@
       <c r="E29" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="I29" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="I29" s="4">
-        <v>1</v>
-      </c>
-      <c r="K29" s="4" t="s">
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L29" s="4">
+      <c r="M29" s="4">
         <v>0.1</v>
       </c>
-      <c r="R29" s="4" t="s">
+      <c r="S29" s="4" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>346</v>
       </c>
@@ -4133,26 +4156,26 @@
       <c r="D30" s="4">
         <v>5</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="I30" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="I30" s="4">
-        <v>1</v>
-      </c>
-      <c r="K30" s="4" t="s">
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L30" s="4">
+      <c r="M30" s="4">
         <v>0.1</v>
       </c>
-      <c r="R30" s="4" t="s">
+      <c r="S30" s="4" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>347</v>
       </c>
@@ -4162,22 +4185,22 @@
       <c r="D31" s="4">
         <v>5</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="I31" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="I31" s="4">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4" t="s">
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L31" s="4">
+      <c r="M31" s="4">
         <v>0.1</v>
       </c>
-      <c r="R31" s="4" t="s">
+      <c r="S31" s="4" t="s">
         <v>351</v>
       </c>
     </row>

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="365">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -553,13 +553,6 @@
   </si>
   <si>
     <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_SKELETONWARRIOR_ATTACK_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2680,7 +2673,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2704,11 +2697,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2716,48 +2709,48 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>309</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>310</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2779,7 +2772,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>18</v>
@@ -2806,76 +2799,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2896,14 +2889,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2912,7 +2905,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2921,7 +2914,7 @@
     <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="13"/>
@@ -2935,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="8" t="s">
@@ -2950,12 +2943,12 @@
         <v>72</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>24</v>
@@ -2972,7 +2965,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2999,18 +2992,18 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>33</v>
@@ -3027,18 +3020,18 @@
         <v>0</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F38"/>
     </row>
@@ -3051,7 +3044,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3076,7 +3069,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -3090,55 +3083,55 @@
         <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="V2" s="4" t="s">
         <v>21</v>
@@ -3150,12 +3143,12 @@
         <v>30</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -3164,22 +3157,22 @@
         <v>65</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>65</v>
@@ -3188,22 +3181,22 @@
         <v>66</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>20</v>
@@ -3229,10 +3222,10 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4">
         <v>0.3</v>
@@ -3244,10 +3237,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J4" s="4">
         <v>0.5</v>
@@ -3256,7 +3249,7 @@
         <v>120</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M4" s="4">
         <v>0.1</v>
@@ -3265,15 +3258,15 @@
         <v>1</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>207</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -3285,10 +3278,10 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J5" s="4">
         <v>0.8</v>
@@ -3297,7 +3290,7 @@
         <v>180</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M5" s="4">
         <v>0.1</v>
@@ -3306,15 +3299,15 @@
         <v>1</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3326,10 +3319,10 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="J6" s="4">
         <v>2</v>
@@ -3338,7 +3331,7 @@
         <v>3</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M6" s="4">
         <v>0.1</v>
@@ -3347,59 +3340,59 @@
         <v>1</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H8">
         <v>20</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J8" s="4">
         <v>0.8</v>
@@ -3408,170 +3401,176 @@
         <v>0.2</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H9">
         <v>20</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J9" s="4">
         <v>2</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R9" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="S9" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H10">
         <v>20</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J10" s="4">
         <v>0.5</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H11">
         <v>20</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J11" s="4">
         <v>0.4</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J13" s="4">
         <v>99999</v>
@@ -3580,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -3591,10 +3590,10 @@
         <v>54</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J14" s="4">
         <v>99999</v>
@@ -3608,13 +3607,13 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="D15" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="b">
         <v>1</v>
@@ -3623,65 +3622,65 @@
         <v>3</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="J15" s="4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K15" s="4">
         <v>1</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M15" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="N15" s="4" t="b">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>90</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="D16" s="4">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="J16" s="4">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K16" s="4">
         <v>1</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M16" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>215</v>
+        <v>356</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D17" s="4">
         <v>3</v>
@@ -3693,214 +3692,232 @@
         <v>3</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="4">
         <v>1</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="M17" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="b">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="J18" s="4">
-        <v>1</v>
+        <v>99999</v>
       </c>
       <c r="K18" s="4">
         <v>1</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M18" s="4">
-        <v>1</v>
+      <c r="O18" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>222</v>
+        <v>177</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>358</v>
+        <v>191</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D19" s="4">
-        <v>3</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="J19" s="4">
-        <v>1</v>
-      </c>
-      <c r="K19" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="M19" s="4">
+        <v>108</v>
+      </c>
+      <c r="N19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>161</v>
+        <v>194</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="I20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R20" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J20" s="4">
-        <v>99999</v>
-      </c>
-      <c r="K20" s="4">
-        <v>1</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="S20" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>195</v>
+        <v>241</v>
+      </c>
+      <c r="D21" s="4">
+        <v>5</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="N21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>194</v>
+        <v>353</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" s="4">
+        <v>5</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="I22" s="4" t="s">
-        <v>130</v>
+        <v>244</v>
       </c>
       <c r="J22" s="4">
-        <v>0.5</v>
+        <v>1</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0.2</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>124</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>242</v>
+        <v>352</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H23" s="4">
+        <v>2</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="J23" s="4">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4">
         <v>5</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J23" s="4">
-        <v>2</v>
-      </c>
       <c r="L23" s="4" t="s">
-        <v>201</v>
+        <v>283</v>
+      </c>
+      <c r="M23" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
@@ -3908,300 +3925,212 @@
         <v>355</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>198</v>
+        <v>271</v>
+      </c>
+      <c r="H24" s="4">
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J24" s="4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K24" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="M24" s="4">
         <v>0.2</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="O24" s="4" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>320</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="D25" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>257</v>
+        <v>319</v>
       </c>
       <c r="H25" s="4">
         <v>2</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="J25" s="4">
-        <v>1</v>
-      </c>
-      <c r="K25" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="M25" s="4">
         <v>0.2</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D26" s="4">
-        <v>5</v>
+        <v>289</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26" s="4">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="J26" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="K26" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="M26" s="4">
-        <v>0.2</v>
+        <v>99999</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>141</v>
+        <v>297</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
       </c>
+      <c r="E27" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G27" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H27" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J27" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="M27" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="R27" s="4" t="s">
-        <v>160</v>
+        <v>0.1</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>291</v>
+        <v>346</v>
+      </c>
+      <c r="D28" s="4">
+        <v>5</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>197</v>
+        <v>3</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="J28" s="4">
-        <v>99999</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q28" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>160</v>
+        <v>1</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M28" s="4">
+        <v>0.1</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>295</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="D29" s="4">
         <v>5</v>
       </c>
-      <c r="E29" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="G29" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J29" s="4">
         <v>1</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M29" s="4">
         <v>0.1</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B30" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="D30" s="4">
-        <v>5</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="J30" s="4">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M30" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="S30" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B31" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="D31" s="4">
-        <v>5</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="J31" s="4">
-        <v>1</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="M31" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="S31" s="4" t="s">
-        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -4247,31 +4176,31 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>62</v>
@@ -4294,16 +4223,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -4332,19 +4261,19 @@
         <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>43</v>
@@ -4367,22 +4296,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>43</v>
@@ -4405,22 +4334,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>43</v>
@@ -4443,16 +4372,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>43</v>
@@ -4469,16 +4398,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>43</v>
@@ -4495,22 +4424,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4518,22 +4447,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -4541,16 +4470,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>43</v>
@@ -4567,16 +4496,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>43</v>
@@ -4593,19 +4522,19 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
@@ -4628,15 +4557,15 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>46</v>
@@ -4702,15 +4631,15 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>47</v>
@@ -4719,7 +4648,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>79</v>
@@ -4730,22 +4659,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4754,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4768,19 +4697,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4788,19 +4717,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4808,19 +4737,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -4828,22 +4757,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>13</v>
@@ -4866,22 +4795,22 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>13</v>
@@ -4890,7 +4819,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4904,22 +4833,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -4928,7 +4857,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4942,22 +4871,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -4966,7 +4895,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4977,10 +4906,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4989,7 +4918,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4997,57 +4926,57 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -5056,42 +4985,42 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H31" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="I31" s="4">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5099,22 +5028,22 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>13</v>
@@ -5166,22 +5095,22 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -5204,10 +5133,10 @@
         <v>68</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -5234,7 +5163,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>40</v>
@@ -5248,10 +5177,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -5259,10 +5188,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -5270,10 +5199,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -5281,24 +5210,24 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5334,10 +5263,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -5347,52 +5276,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -5412,13 +5341,13 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="G4" s="16"/>
     </row>
@@ -5428,13 +5357,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="G5" s="16"/>
     </row>
@@ -5444,13 +5373,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -5460,7 +5389,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -5471,7 +5400,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -5482,7 +5411,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -5492,7 +5421,7 @@
         <v>20001</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -5501,13 +5430,13 @@
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -5515,10 +5444,10 @@
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="366">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1525,10 +1525,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SkillCastingTypes</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2137,6 +2133,14 @@
   </si>
   <si>
     <t>StaminaCost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2697,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
@@ -2706,7 +2710,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>3</v>
+        <v>365</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>112</v>
@@ -2714,10 +2718,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>260</v>
@@ -2725,10 +2729,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>260</v>
@@ -2744,7 +2748,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>268</v>
+        <v>364</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
@@ -2835,7 +2839,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
         <v>96</v>
@@ -2943,7 +2947,7 @@
         <v>72</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2965,7 +2969,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2992,13 +2996,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3069,7 +3073,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -3086,16 +3090,16 @@
         <v>190</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>266</v>
@@ -3104,13 +3108,13 @@
         <v>267</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>251</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>147</v>
@@ -3125,10 +3129,10 @@
         <v>153</v>
       </c>
       <c r="S2" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="U2" s="4" t="s">
         <v>176</v>
@@ -3143,12 +3147,12 @@
         <v>30</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -3160,7 +3164,7 @@
         <v>152</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
@@ -3345,19 +3349,19 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
@@ -3372,7 +3376,7 @@
         <v>142</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S7" s="4" t="s">
         <v>122</v>
@@ -3380,13 +3384,13 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="G8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H8">
         <v>20</v>
@@ -3410,7 +3414,7 @@
         <v>142</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>122</v>
@@ -3418,13 +3422,13 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H9">
         <v>20</v>
@@ -3445,21 +3449,21 @@
         <v>142</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H10">
         <v>20</v>
@@ -3480,7 +3484,7 @@
         <v>142</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S10" s="4" t="s">
         <v>122</v>
@@ -3488,13 +3492,13 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H11">
         <v>20</v>
@@ -3515,7 +3519,7 @@
         <v>142</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S11" s="4" t="s">
         <v>122</v>
@@ -3523,13 +3527,13 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H12">
         <v>20</v>
@@ -3553,7 +3557,7 @@
         <v>142</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S12" s="4" t="s">
         <v>122</v>
@@ -3677,7 +3681,7 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>223</v>
@@ -3712,7 +3716,7 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>159</v>
@@ -3834,7 +3838,7 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>242</v>
@@ -3870,12 +3874,12 @@
         <v>158</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>252</v>
@@ -3890,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J23" s="4">
         <v>1</v>
@@ -3899,7 +3903,7 @@
         <v>5</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M23" s="4">
         <v>0.2</v>
@@ -3922,7 +3926,7 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>256</v>
@@ -3931,7 +3935,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H24" s="4">
         <v>2</v>
@@ -3946,7 +3950,7 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M24" s="4">
         <v>0.2</v>
@@ -3969,28 +3973,28 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D25" s="4">
         <v>5</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H25" s="4">
         <v>2</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M25" s="4">
         <v>0.2</v>
@@ -4008,21 +4012,21 @@
         <v>158</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>195</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J26" s="4">
         <v>99999</v>
@@ -4034,21 +4038,21 @@
         <v>142</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R26" s="4" t="s">
         <v>158</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
@@ -4060,7 +4064,7 @@
         <v>3</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J27" s="4">
         <v>1</v>
@@ -4072,15 +4076,15 @@
         <v>0.1</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D28" s="4">
         <v>5</v>
@@ -4089,7 +4093,7 @@
         <v>3</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J28" s="4">
         <v>1</v>
@@ -4101,15 +4105,15 @@
         <v>0.1</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D29" s="4">
         <v>5</v>
@@ -4118,7 +4122,7 @@
         <v>3</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J29" s="4">
         <v>1</v>
@@ -4130,7 +4134,7 @@
         <v>0.1</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4182,7 +4186,7 @@
         <v>120</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>134</v>
@@ -4709,7 +4713,7 @@
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4757,7 +4761,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>245</v>
@@ -4871,7 +4875,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>264</v>
@@ -4906,10 +4910,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4918,7 +4922,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4926,10 +4930,10 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>42</v>
@@ -4944,24 +4948,24 @@
         <v>140</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>42</v>
@@ -4976,7 +4980,7 @@
         <v>140</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -4985,18 +4989,18 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>42</v>
@@ -5011,16 +5015,16 @@
         <v>140</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5028,16 +5032,16 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>132</v>
@@ -5177,7 +5181,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>166</v>
@@ -5188,7 +5192,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>167</v>
@@ -5210,7 +5214,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>182</v>
@@ -5224,10 +5228,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -5344,10 +5348,10 @@
         <v>234</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G4" s="16"/>
     </row>
@@ -5360,10 +5364,10 @@
         <v>235</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G5" s="16"/>
     </row>
@@ -5373,13 +5377,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -5400,7 +5404,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -5411,7 +5415,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -5430,13 +5434,13 @@
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -5444,10 +5448,10 @@
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="360">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -401,10 +401,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>패시브1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Enemy</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -452,10 +448,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>패시브2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -553,10 +545,6 @@
   </si>
   <si>
     <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1232,14 +1220,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>기본공격2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본공격3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_TAKE_DAMAGE_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1647,14 +1627,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>강타 스킬2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>shake_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1714,20 +1686,6 @@
     <t>SKILL_SPECIALATTACK_03</t>
   </si>
   <si>
-    <t>특수 스킬1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>특수 스킬2</t>
-  </si>
-  <si>
-    <t>특수 스킬3</t>
-  </si>
-  <si>
     <t>Circle</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2141,6 +2099,26 @@
   </si>
   <si>
     <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAttack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2677,7 +2655,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2701,60 +2679,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2776,7 +2754,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>18</v>
@@ -2792,7 +2770,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>19</v>
@@ -2803,76 +2781,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2893,14 +2871,14 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2909,7 +2887,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -2918,7 +2896,7 @@
     <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="13"/>
@@ -2932,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="8" t="s">
@@ -2944,15 +2922,15 @@
         <v>13</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>24</v>
@@ -2969,7 +2947,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2996,18 +2974,18 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>33</v>
@@ -3024,18 +3002,18 @@
         <v>0</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F38"/>
     </row>
@@ -3073,7 +3051,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -3087,55 +3065,55 @@
         <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>272</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="V2" s="4" t="s">
         <v>21</v>
@@ -3147,60 +3125,60 @@
         <v>30</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="O3" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>20</v>
@@ -3226,10 +3204,10 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="D4" s="4">
         <v>0.3</v>
@@ -3241,10 +3219,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J4" s="4">
         <v>0.5</v>
@@ -3253,7 +3231,7 @@
         <v>120</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M4" s="4">
         <v>0.1</v>
@@ -3262,15 +3240,15 @@
         <v>1</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>205</v>
+        <v>356</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -3282,10 +3260,10 @@
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J5" s="4">
         <v>0.8</v>
@@ -3294,7 +3272,7 @@
         <v>180</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M5" s="4">
         <v>0.1</v>
@@ -3303,15 +3281,15 @@
         <v>1</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>206</v>
+        <v>356</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -3323,10 +3301,10 @@
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J6" s="4">
         <v>2</v>
@@ -3335,7 +3313,7 @@
         <v>3</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M6" s="4">
         <v>0.1</v>
@@ -3344,59 +3322,59 @@
         <v>1</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="G7" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H7">
         <v>20</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="G8" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H8">
         <v>20</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J8" s="4">
         <v>0.8</v>
@@ -3405,141 +3383,141 @@
         <v>0.2</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="G9" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H9">
         <v>20</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J9" s="4">
         <v>2</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H10">
         <v>20</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J10" s="4">
         <v>0.5</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H11">
         <v>20</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J11" s="4">
         <v>0.4</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J12" s="4">
         <v>2</v>
@@ -3548,33 +3526,33 @@
         <v>1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>41</v>
+        <v>358</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J13" s="4">
         <v>99999</v>
@@ -3583,21 +3561,21 @@
         <v>1</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>54</v>
+        <v>359</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J14" s="4">
         <v>99999</v>
@@ -3606,15 +3584,15 @@
         <v>1</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D15" s="4">
         <v>3</v>
@@ -3626,7 +3604,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J15" s="4">
         <v>0.4</v>
@@ -3635,21 +3613,21 @@
         <v>1</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M15" s="4">
         <v>0.5</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -3661,7 +3639,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J16" s="4">
         <v>1</v>
@@ -3670,21 +3648,21 @@
         <v>1</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M16" s="4">
         <v>1</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D17" s="4">
         <v>3</v>
@@ -3696,7 +3674,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
@@ -3705,27 +3683,27 @@
         <v>1</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M17" s="4">
         <v>1</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J18" s="4">
         <v>99999</v>
@@ -3734,123 +3712,123 @@
         <v>1</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J19" s="4">
         <v>2</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J20" s="4">
         <v>0.5</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D21" s="4">
         <v>5</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D22" s="4">
         <v>5</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J22" s="4">
         <v>1</v>
@@ -3859,42 +3837,42 @@
         <v>0.2</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D23" s="4">
         <v>2</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H23" s="4">
         <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J23" s="4">
         <v>1</v>
@@ -3903,45 +3881,45 @@
         <v>5</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="M23" s="4">
         <v>0.2</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H24" s="4">
         <v>2</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J24" s="4">
         <v>1.5</v>
@@ -3950,109 +3928,109 @@
         <v>0.5</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M24" s="4">
         <v>0.2</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D25" s="4">
         <v>5</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="H25" s="4">
         <v>2</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M25" s="4">
         <v>0.2</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J26" s="4">
         <v>99999</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D27" s="4">
         <v>5</v>
@@ -4064,27 +4042,27 @@
         <v>3</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J27" s="4">
         <v>1</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M27" s="4">
         <v>0.1</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="D28" s="4">
         <v>5</v>
@@ -4093,27 +4071,27 @@
         <v>3</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J28" s="4">
         <v>1</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M28" s="4">
         <v>0.1</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D29" s="4">
         <v>5</v>
@@ -4122,19 +4100,19 @@
         <v>3</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J29" s="4">
         <v>1</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M29" s="4">
         <v>0.1</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4166,7 +4144,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>6</v>
@@ -4180,40 +4158,40 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -4227,16 +4205,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -4262,31 +4240,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -4300,31 +4278,31 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I5" s="4">
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -4338,31 +4316,31 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -4376,25 +4354,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -4402,25 +4380,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -4428,22 +4406,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4451,22 +4429,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -4474,25 +4452,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I11" s="4">
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -4500,25 +4478,25 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="I12" s="4">
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -4526,25 +4504,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -4552,36 +4530,36 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -4589,10 +4567,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>10</v>
@@ -4601,15 +4579,15 @@
         <v>23</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>10</v>
@@ -4618,7 +4596,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -4626,36 +4604,36 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -4663,22 +4641,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4687,7 +4665,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4701,19 +4679,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>180</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4721,19 +4699,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4741,19 +4719,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -4761,22 +4739,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>13</v>
@@ -4785,7 +4763,7 @@
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K24" s="4">
         <v>3</v>
@@ -4799,22 +4777,22 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>13</v>
@@ -4823,7 +4801,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4837,22 +4815,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -4861,7 +4839,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4875,22 +4853,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -4899,7 +4877,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4910,10 +4888,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4922,7 +4900,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4930,57 +4908,57 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -4989,42 +4967,42 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5032,22 +5010,22 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>13</v>
@@ -5056,7 +5034,7 @@
         <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K32" s="4">
         <v>1</v>
@@ -5088,44 +5066,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>20</v>
@@ -5134,40 +5112,40 @@
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>40</v>
@@ -5176,15 +5154,15 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -5192,10 +5170,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -5203,10 +5181,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -5214,24 +5192,24 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -5267,10 +5245,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -5280,52 +5258,52 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
@@ -5345,13 +5323,13 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="G4" s="16"/>
     </row>
@@ -5361,13 +5339,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="G5" s="16"/>
     </row>
@@ -5377,13 +5355,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -5393,7 +5371,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -5404,7 +5382,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -5415,7 +5393,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -5425,7 +5403,7 @@
         <v>20001</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -5434,13 +5412,13 @@
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -5448,10 +5426,10 @@
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="361">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1164,10 +1164,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_CLASS_BASIC_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1297,14 +1293,6 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1403,10 +1391,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1581,10 +1565,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>무적 스킬</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1676,10 +1656,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_SPECIALATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_SPECIALATTACK_02</t>
   </si>
   <si>
@@ -2075,50 +2051,78 @@
     <t>SKILL_POWERATTACK_01</t>
   </si>
   <si>
+    <t>SKILL_POWERATTACK_03</t>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaCost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAttack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Attack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>SKILL_POWERATTACK_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_POWERATTACK_03</t>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaCost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive2</t>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2655,7 +2659,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2679,16 +2683,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>109</v>
@@ -2696,24 +2700,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2726,13 +2730,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2781,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
@@ -2798,7 +2802,7 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2817,7 +2821,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
         <v>93</v>
@@ -2830,7 +2834,7 @@
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>97</v>
@@ -2925,7 +2929,7 @@
         <v>70</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2947,7 +2951,7 @@
         <v>35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2974,13 +2978,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3026,35 +3030,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y29"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="36.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="22.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15" style="4" customWidth="1"/>
-    <col min="7" max="13" width="23.75" style="4" customWidth="1"/>
-    <col min="14" max="14" width="14.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.25" style="4" customWidth="1"/>
-    <col min="16" max="16" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.375" style="4" customWidth="1"/>
-    <col min="19" max="19" width="39.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="36.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="22" style="4" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="4"/>
+    <col min="4" max="5" width="22.75" style="4" customWidth="1"/>
+    <col min="6" max="8" width="15" style="4" customWidth="1"/>
+    <col min="9" max="15" width="23.75" style="4" customWidth="1"/>
+    <col min="16" max="16" width="14.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.25" style="4" customWidth="1"/>
+    <col min="18" max="18" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="39.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="36.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="22" style="4" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3062,129 +3067,135 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>275</v>
+        <v>345</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>309</v>
-      </c>
       <c r="U2" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AA2" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>282</v>
+        <v>357</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="U3" s="4" t="s">
         <v>20</v>
@@ -3201,918 +3212,924 @@
       <c r="Y3" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M4" s="4">
+        <v>120</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M5" s="4">
+        <v>180</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
+        <v>10</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="L6" s="4">
+        <v>2</v>
+      </c>
+      <c r="M6" s="4">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="I7" t="s">
+        <v>292</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="L7" s="4">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="I8" t="s">
+        <v>292</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" t="s">
+        <v>292</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="L9" s="4">
+        <v>2</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="L12" s="4">
+        <v>2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D4" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="E4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="K4" s="4">
-        <v>120</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="N4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="K5" s="4">
-        <v>180</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="N5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="J6" s="4">
-        <v>2</v>
-      </c>
-      <c r="K6" s="4">
-        <v>3</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="N6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G7" t="s">
-        <v>297</v>
-      </c>
-      <c r="H7">
-        <v>20</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="J7" s="4">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G8" t="s">
-        <v>297</v>
-      </c>
-      <c r="H8">
-        <v>20</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="G9" t="s">
-        <v>297</v>
-      </c>
-      <c r="H9">
-        <v>20</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J9" s="4">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H10">
-        <v>20</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H12">
-        <v>20</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J12" s="4">
-        <v>2</v>
-      </c>
-      <c r="K12" s="4">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B13" s="4" t="s">
-        <v>248</v>
-      </c>
       <c r="C13" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="G13" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="L13" s="4">
         <v>99999</v>
       </c>
-      <c r="K13" s="4">
-        <v>1</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="M13" s="4">
+        <v>1</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="G14" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J14" s="4">
+      <c r="L14" s="4">
         <v>99999</v>
       </c>
-      <c r="K14" s="4">
-        <v>1</v>
-      </c>
-      <c r="S14" s="4" t="s">
+      <c r="M14" s="4">
+        <v>1</v>
+      </c>
+      <c r="U14" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="4">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="M15" s="4">
+        <v>1</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D15" s="4">
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="K16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" s="4">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4">
+        <v>1</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O16" s="4">
+        <v>1</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" s="4">
         <v>3</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="G17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="J15" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="K15" s="4">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M15" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S15" s="4" t="s">
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="O17" s="4">
+        <v>1</v>
+      </c>
+      <c r="U17" s="4" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J16" s="4">
-        <v>1</v>
-      </c>
-      <c r="K16" s="4">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M16" s="4">
-        <v>1</v>
-      </c>
-      <c r="S16" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D17" s="4">
-        <v>3</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J17" s="4">
-        <v>1</v>
-      </c>
-      <c r="K17" s="4">
-        <v>1</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="M17" s="4">
-        <v>1</v>
-      </c>
-      <c r="S17" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="J18" s="4">
+      <c r="L18" s="4">
         <v>99999</v>
       </c>
-      <c r="K18" s="4">
-        <v>1</v>
-      </c>
-      <c r="O18" s="4" t="s">
+      <c r="M18" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="R18" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="S18" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="T18" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="U18" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="T18" s="4" t="s">
+      <c r="V18" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" s="4">
+        <v>2</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="P19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I19" s="4" t="s">
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="4">
+      <c r="L20" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" s="4">
+        <v>5</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L21" s="4">
         <v>2</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S19" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J20" s="4">
+      <c r="N21" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="J23" s="4">
+        <v>2</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="L23" s="4">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4">
+        <v>5</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="O23" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="4">
+        <v>5</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="J24" s="4">
+        <v>2</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L24" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="M24" s="4">
         <v>0.5</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P20" s="4" t="s">
+      <c r="N24" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="O24" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="R24" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="R20" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="S24" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F25" s="4">
         <v>5</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="J21" s="4">
-        <v>2</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D22" s="4">
-        <v>5</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="J22" s="4">
-        <v>1</v>
-      </c>
-      <c r="K22" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q22" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="H23" s="4">
-        <v>2</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="J23" s="4">
-        <v>1</v>
-      </c>
-      <c r="K23" s="4">
-        <v>5</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="M23" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B24" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D24" s="4">
-        <v>5</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="H24" s="4">
-        <v>2</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="J24" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="K24" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="M24" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D25" s="4">
-        <v>5</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="H25" s="4">
-        <v>2</v>
-      </c>
       <c r="I25" s="4" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="M25" s="4">
+      <c r="K25" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L25" s="4">
+        <v>2</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="O25" s="4">
         <v>0.2</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="Q25" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="R25" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Q25" s="4" t="s">
+      <c r="S25" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="R25" s="4" t="s">
+      <c r="T25" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="S25" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="U25" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="J26" s="4">
+        <v>191</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="L26" s="4">
         <v>99999</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="Q26" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="P26" s="4" t="s">
+      <c r="R26" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Q26" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="R26" s="4" t="s">
+      <c r="S26" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="T26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="S26" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="U26" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="D27" s="4">
+        <v>308</v>
+      </c>
+      <c r="F27" s="4">
         <v>5</v>
       </c>
-      <c r="E27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="J27" s="4">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="s">
+      <c r="K27" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L27" s="4">
+        <v>1</v>
+      </c>
+      <c r="N27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="M27" s="4">
+      <c r="O27" s="4">
         <v>0.1</v>
       </c>
-      <c r="S27" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="U27" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D28" s="4">
+        <v>328</v>
+      </c>
+      <c r="F28" s="4">
         <v>5</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="J28" s="4">
-        <v>1</v>
-      </c>
-      <c r="L28" s="4" t="s">
+      <c r="K28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L28" s="4">
+        <v>1</v>
+      </c>
+      <c r="N28" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="M28" s="4">
+      <c r="O28" s="4">
         <v>0.1</v>
       </c>
-      <c r="S28" s="4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="U28" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="4">
+        <v>329</v>
+      </c>
+      <c r="F29" s="4">
         <v>5</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="I29" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="J29" s="4">
-        <v>1</v>
-      </c>
-      <c r="L29" s="4" t="s">
+      <c r="K29" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="L29" s="4">
+        <v>1</v>
+      </c>
+      <c r="N29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="M29" s="4">
+      <c r="O29" s="4">
         <v>0.1</v>
       </c>
-      <c r="S29" s="4" t="s">
-        <v>337</v>
+      <c r="U29" s="4" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4164,7 +4181,7 @@
         <v>117</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>131</v>
@@ -4173,10 +4190,10 @@
         <v>71</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4243,7 +4260,7 @@
         <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>41</v>
@@ -4281,7 +4298,7 @@
         <v>83</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>41</v>
@@ -4319,7 +4336,7 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>41</v>
@@ -4406,22 +4423,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4429,10 +4446,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>41</v>
@@ -4487,7 +4504,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>42</v>
@@ -4547,7 +4564,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -4665,7 +4682,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4691,7 +4708,7 @@
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4711,7 +4728,7 @@
         <v>23</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4739,16 +4756,16 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>129</v>
@@ -4777,10 +4794,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>41</v>
@@ -4801,7 +4818,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4815,10 +4832,10 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>41</v>
@@ -4839,7 +4856,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4853,10 +4870,10 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>41</v>
@@ -4877,7 +4894,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4888,10 +4905,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4900,7 +4917,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4908,10 +4925,10 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>41</v>
@@ -4926,24 +4943,24 @@
         <v>137</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>41</v>
@@ -4958,7 +4975,7 @@
         <v>137</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -4967,18 +4984,18 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>41</v>
@@ -4993,16 +5010,16 @@
         <v>137</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5010,16 +5027,16 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>129</v>
@@ -5083,7 +5100,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>143</v>
@@ -5159,7 +5176,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>163</v>
@@ -5170,7 +5187,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>164</v>
@@ -5192,7 +5209,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>179</v>
@@ -5206,10 +5223,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -5220,7 +5237,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -5229,82 +5246,71 @@
     <col min="4" max="4" width="28.875" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="26.375" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19.25" style="4" customWidth="1"/>
-    <col min="19" max="19" width="12.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="4"/>
+    <col min="11" max="11" width="14" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="19.25" style="4" customWidth="1"/>
+    <col min="17" max="17" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C1" s="14"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
       <c r="B2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>228</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -5314,131 +5320,126 @@
       <c r="P3" s="17"/>
       <c r="Q3" s="17"/>
       <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="16">
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G4" s="16"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="16">
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G5" s="16"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="16">
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G6" s="16"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="19">
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8" s="19">
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="19">
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>20001</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E10" s="16"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C15"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C16"/>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,8 @@
     <sheet name="#SkillEffect" sheetId="6" r:id="rId3"/>
     <sheet name="#BuffInfo" sheetId="4" r:id="rId4"/>
     <sheet name="#SkillSet" sheetId="8" r:id="rId5"/>
+    <sheet name="#SkillCard" sheetId="9" r:id="rId6"/>
+    <sheet name="#SkillCardUpgrade" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -34,89 +36,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="392">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>n초후 발동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillCastingTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillApplyTarget</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Friendly</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillApplyTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DecreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아군에게 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>자신에게 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>적에게 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>모두에게 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_2</t>
@@ -126,15 +128,15 @@
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>버프 생성</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectType에 따라 EffectParam1~5에 넣을 값이 달라짐.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -215,15 +217,15 @@
       </rPr>
       <t xml:space="preserve"> : 버프 효과 발동 간격. 실수형</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CooltimeSec</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_3</t>
@@ -233,23 +235,23 @@
   </si>
   <si>
     <t>스탯 증가 (Target은 Self만 가능)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>스탯 감소(Target은 Self만 가능)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>오라 생성</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DeactivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>버프 삭제</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -296,7 +298,7 @@
       </rPr>
       <t xml:space="preserve"> : 지속 시간. 실수형(0이면 무한)</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -343,7 +345,7 @@
       </rPr>
       <t xml:space="preserve"> : 증가 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -390,174 +392,174 @@
       </rPr>
       <t xml:space="preserve"> : 감소 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>All</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_MOVESPEED_01</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_ATTACKSPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BuffInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!BuffInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격2</t>
@@ -588,39 +590,39 @@
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>타겟팅스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>부채꼴</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>원형</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Donut</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>도넛 모양</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>직선 궤적</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -645,7 +647,7 @@
       </rPr>
       <t xml:space="preserve"> : 반지름</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -704,7 +706,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -763,7 +765,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -822,584 +824,580 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Passive</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>상시 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>즉시발동</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillDamageType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Magical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Pure</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillDamageType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>강타 데미지 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Magical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>hit-blue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>focus-hit-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>horizontal-slash</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectSFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillSFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>blade_hit_07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>metal_punch_06</t>
   </si>
   <si>
     <t>Root</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Center</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>VFXAnchor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillAnchorType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>VFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillAnchorType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ApplyTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CameraShake</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Center</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>shake_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>shake_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>브레이크</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>flashy-hit-1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ActivateAura</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>스턴 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>침묵 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동불가 디버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IsDebuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillEffectTypes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>받는 데미지 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>브레이크 상태 효과1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>브레이크 상태 효과2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>브레이크(받는 데미지 증가)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffectTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DecreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_DAMAGETAKEN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IsBasicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>기본직업 고유스킬1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>기본직업 고유스킬2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DASH</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>데미지 효과1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>데미지 효과2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>데미지 효과3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_MONSTER_ATK_MELEE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_MONSTER_ATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 근접공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수 원거리공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>몬스터 물리 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>몬스터 마법 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사 원거리 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BaseAttackSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IntervalEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DASH_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>대시 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>대시공격 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>대시어택 데미지</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillScanType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MotionEffectTime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 단일 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
   </si>
   <si>
     <t>캐스팅 범위(직선) 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1446,169 +1444,169 @@
       </rPr>
       <t xml:space="preserve"> : 타갯 수</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>발동확률 0~1 = 0~100%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 스킬 데미지1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 스킬 데미지2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MATK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ScanParam1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ScanParam2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillCastingTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CastingType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting;Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MotionNames</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 범위(원형) 공격</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ScanType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CastingParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting;Skill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BREAK</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>무적 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>무적 버프</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>무적 효과</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>wood_bat_finisher_05</t>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_POWERATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>shake_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1633,27 +1631,27 @@
       </rPr>
       <t xml:space="preserve"> : 버프 ID</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>OnHitCaster</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>OnHitTarget</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>타격시 n% 확률로 발동(시전자)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>타격시 n% 확률로 발동(피격자)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_SPECIALATTACK_02</t>
@@ -1663,35 +1661,35 @@
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_DASH_ATTACK_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>StartEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>FinishEffect</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>발사체 생성</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1804,55 +1802,55 @@
       </rPr>
       <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SpawnProjectile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Projectile_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_PROJECTILE_DAMAGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>투사체 발사1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>투사체 데미지1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectVFX</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SpawnProjectile</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1970,7 +1968,7 @@
       </rPr>
       <t xml:space="preserve"> : 발사체 효과 반경(0이면 단일)</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_02</t>
@@ -1992,60 +1990,60 @@
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_01</t>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_02</t>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_03</t>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_POWERATTACK_01</t>
@@ -2055,87 +2053,267 @@
   </si>
   <si>
     <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>StaminaCost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Power Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BasicAttack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target Attack</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Passive1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Passive2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_SPECIALATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_01_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_02_5</t>
+  </si>
+  <si>
+    <t>SampleSkill_02_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_02_1</t>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ame</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>esc</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_5</t>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_01</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillGroupGrade</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillGroupGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SourceGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequiredCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCard</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UltimateSkill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCardUpgrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2325,12 +2503,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2353,36 +2531,42 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2667,7 +2851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2683,16 +2867,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>109</v>
@@ -2700,24 +2884,24 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2730,13 +2914,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2785,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
@@ -2802,7 +2986,7 @@
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2821,7 +3005,7 @@
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C17" t="s">
         <v>93</v>
@@ -2834,7 +3018,7 @@
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>97</v>
@@ -2860,29 +3044,32 @@
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
       <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="13"/>
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+    <row r="21" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -2890,139 +3077,164 @@
     </row>
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
-      <c r="B24" s="4" t="s">
-        <v>115</v>
+      <c r="B24" t="s">
+        <v>116</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="8" t="s">
+      <c r="D26" s="6"/>
+      <c r="E26" s="8" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>26</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>290</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>15</v>
+        <v>309</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>32</v>
+        <v>304</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>38</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>310</v>
+        <v>162</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>305</v>
+        <v>33</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>319</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E35" s="9"/>
-    </row>
-    <row r="36" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B35" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D36" s="6"/>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F38"/>
+      <c r="F37"/>
+    </row>
+    <row r="39" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="21" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="21" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="21" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="21" t="s">
+        <v>377</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3056,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -3067,10 +3279,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>360</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>28</v>
@@ -3079,31 +3291,31 @@
         <v>187</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>258</v>
-      </c>
       <c r="N2" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>144</v>
@@ -3118,10 +3330,10 @@
         <v>150</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="V2" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>173</v>
@@ -3136,21 +3348,21 @@
         <v>30</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>63</v>
@@ -3159,7 +3371,7 @@
         <v>149</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>8</v>
@@ -3224,7 +3436,10 @@
         <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="F4" s="4">
         <v>0.3</v>
@@ -3265,7 +3480,10 @@
         <v>199</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="F5" s="4">
         <v>0.5</v>
@@ -3306,7 +3524,10 @@
         <v>200</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -3344,19 +3565,22 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>360</v>
       </c>
       <c r="I7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L7" s="4">
         <v>1</v>
@@ -3371,7 +3595,7 @@
         <v>139</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U7" s="4" t="s">
         <v>119</v>
@@ -3379,19 +3603,22 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>360</v>
       </c>
       <c r="I8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J8">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L8" s="4">
         <v>0.8</v>
@@ -3409,7 +3636,7 @@
         <v>139</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U8" s="4" t="s">
         <v>119</v>
@@ -3417,13 +3644,16 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>360</v>
       </c>
       <c r="I9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J9">
         <v>20</v>
@@ -3444,21 +3674,24 @@
         <v>139</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J10">
         <v>20</v>
@@ -3479,7 +3712,7 @@
         <v>139</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U10" s="4" t="s">
         <v>119</v>
@@ -3487,19 +3720,22 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J11">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L11" s="4">
         <v>0.4</v>
@@ -3514,7 +3750,7 @@
         <v>139</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U11" s="4" t="s">
         <v>119</v>
@@ -3522,13 +3758,16 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J12">
         <v>20</v>
@@ -3552,7 +3791,7 @@
         <v>139</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="U12" s="4" t="s">
         <v>119</v>
@@ -3560,10 +3799,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>362</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>106</v>
@@ -3578,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -3586,7 +3828,10 @@
         <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>362</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>106</v>
@@ -3676,7 +3921,7 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>217</v>
@@ -3711,7 +3956,7 @@
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>156</v>
@@ -3749,7 +3994,7 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>189</v>
@@ -3810,10 +4055,10 @@
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="F21" s="4">
         <v>5</v>
@@ -3833,10 +4078,10 @@
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F22" s="4">
         <v>5</v>
@@ -3845,7 +4090,7 @@
         <v>192</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L22" s="4">
         <v>1</v>
@@ -3869,27 +4114,27 @@
         <v>155</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J23" s="4">
         <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L23" s="4">
         <v>1</v>
@@ -3898,7 +4143,7 @@
         <v>5</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O23" s="4">
         <v>0.2</v>
@@ -3916,27 +4161,27 @@
         <v>155</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F24" s="4">
         <v>5</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J24" s="4">
         <v>2</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L24" s="4">
         <v>1.5</v>
@@ -3945,7 +4190,7 @@
         <v>0.5</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O24" s="4">
         <v>0.2</v>
@@ -3963,33 +4208,33 @@
         <v>155</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F25" s="4">
         <v>5</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L25" s="4">
         <v>2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O25" s="4">
         <v>0.2</v>
@@ -4007,21 +4252,21 @@
         <v>155</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>191</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L26" s="4">
         <v>99999</v>
@@ -4033,21 +4278,21 @@
         <v>139</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T26" s="4" t="s">
         <v>155</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F27" s="4">
         <v>5</v>
@@ -4059,7 +4304,7 @@
         <v>3</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L27" s="4">
         <v>1</v>
@@ -4071,15 +4316,15 @@
         <v>0.1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F28" s="4">
         <v>5</v>
@@ -4088,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L28" s="4">
         <v>1</v>
@@ -4100,15 +4345,15 @@
         <v>0.1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F29" s="4">
         <v>5</v>
@@ -4117,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
@@ -4129,11 +4374,11 @@
         <v>0.1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4181,7 +4426,7 @@
         <v>117</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>131</v>
@@ -4190,10 +4435,10 @@
         <v>71</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4504,7 +4749,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>42</v>
@@ -4564,7 +4809,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -4682,7 +4927,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4708,7 +4953,7 @@
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4756,16 +5001,16 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>129</v>
@@ -4794,10 +5039,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>41</v>
@@ -4818,7 +5063,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -4832,10 +5077,10 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>41</v>
@@ -4856,7 +5101,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -4870,10 +5115,10 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>41</v>
@@ -4894,7 +5139,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -4905,10 +5150,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -4917,7 +5162,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -4925,10 +5170,10 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>41</v>
@@ -4943,24 +5188,24 @@
         <v>137</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>41</v>
@@ -4975,7 +5220,7 @@
         <v>137</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -4984,18 +5229,18 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>41</v>
@@ -5010,16 +5255,16 @@
         <v>137</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5027,16 +5272,16 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>129</v>
@@ -5058,7 +5303,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5100,7 +5345,7 @@
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>143</v>
@@ -5176,7 +5421,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>163</v>
@@ -5187,7 +5432,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>164</v>
@@ -5209,7 +5454,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>179</v>
@@ -5223,14 +5468,14 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>281</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5263,8 +5508,8 @@
       <c r="A1" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>228</v>
+      <c r="B1" s="20" t="s">
+        <v>386</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -5274,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>221</v>
@@ -5330,10 +5575,10 @@
         <v>226</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="G4" s="16"/>
     </row>
@@ -5346,10 +5591,10 @@
         <v>227</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="G5" s="16"/>
     </row>
@@ -5359,13 +5604,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -5385,7 +5630,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G8" s="16"/>
     </row>
@@ -5395,7 +5640,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G9" s="16"/>
     </row>
@@ -5413,13 +5658,13 @@
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -5427,10 +5672,10 @@
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -5513,8 +5758,467 @@
       <c r="D39"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U39"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="15.375" style="4" customWidth="1"/>
+    <col min="7" max="8" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15" style="4" customWidth="1"/>
+    <col min="11" max="11" width="17" style="4" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="19.25" style="4" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="J4" s="16"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="J5" s="16"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G19"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G20"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G23"/>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G24"/>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G25"/>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G26"/>
+    </row>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G27"/>
+    </row>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G28"/>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G29"/>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G30"/>
+    </row>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G31"/>
+    </row>
+    <row r="32" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G32"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G33"/>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G34"/>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G35"/>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G36"/>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G37"/>
+    </row>
+    <row r="38" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G38"/>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G39"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="4" customWidth="1"/>
+    <col min="3" max="4" width="16.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" style="4" customWidth="1"/>
+    <col min="6" max="7" width="15.375" style="4" customWidth="1"/>
+    <col min="8" max="11" width="6.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="19.25" style="4" customWidth="1"/>
+    <col min="16" max="16" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="E4" s="21">
+        <v>10</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="16">
+        <v>2</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="E5" s="16">
+        <v>15</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="16">
+        <v>3</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="16">
+        <v>30</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="19">
+        <v>4</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="E7" s="19">
+        <v>50</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,6 @@
     <sheet name="#SkillEffect" sheetId="6" r:id="rId3"/>
     <sheet name="#BuffInfo" sheetId="4" r:id="rId4"/>
     <sheet name="#SkillSet" sheetId="8" r:id="rId5"/>
-    <sheet name="#SkillCard" sheetId="9" r:id="rId6"/>
-    <sheet name="#SkillCardUpgrade" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="404">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -466,10 +464,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>BUFF_ATTACKSPEED_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1528,10 +1522,6 @@
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2134,141 +2124,7 @@
     <t>SampleSkill_02_1</t>
   </si>
   <si>
-    <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ame</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>esc</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>con</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_5</t>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>kill_01</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_PASSIVE_01</t>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillGroupGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Epic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillGroupGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>TargetGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SourceGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>RequiredCount</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2276,24 +2132,139 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>SkillCard</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>UltimateSkill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillCardUpgrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>ScanType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV5</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지5</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지5</t>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv2</t>
+  </si>
+  <si>
+    <t>Lv3</t>
+  </si>
+  <si>
+    <t>Lv4</t>
+  </si>
+  <si>
+    <t>Lv5</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2479,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2564,9 +2535,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2843,7 +2811,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2851,7 +2819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
@@ -2867,60 +2835,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>294</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2942,7 +2910,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>18</v>
@@ -2969,76 +2937,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
         <v>95</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3053,14 +3021,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -3069,7 +3037,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -3078,7 +3046,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -3092,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
@@ -3104,15 +3072,15 @@
         <v>13</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>24</v>
@@ -3129,7 +3097,7 @@
         <v>35</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3156,18 +3124,18 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>33</v>
@@ -3184,54 +3152,20 @@
         <v>0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37"/>
-    </row>
-    <row r="39" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="21" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="21" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="21" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="21" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="21" t="s">
-        <v>377</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3242,13 +3176,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="36.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="22.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="22.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="39.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="4" customWidth="1"/>
     <col min="6" max="8" width="15" style="4" customWidth="1"/>
     <col min="9" max="15" width="23.75" style="4" customWidth="1"/>
     <col min="16" max="16" width="14.25" style="4" bestFit="1" customWidth="1"/>
@@ -3268,7 +3203,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -3279,64 +3214,64 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="N2" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Q2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="S2" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>21</v>
@@ -3348,66 +3283,66 @@
         <v>30</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="R3" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U3" s="4" t="s">
         <v>20</v>
@@ -3433,13 +3368,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F4" s="4">
         <v>0.3</v>
@@ -3451,10 +3386,10 @@
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" s="4">
         <v>0.5</v>
@@ -3463,7 +3398,7 @@
         <v>120</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O4" s="4">
         <v>0.1</v>
@@ -3472,18 +3407,18 @@
         <v>1</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F5" s="4">
         <v>0.5</v>
@@ -3495,10 +3430,10 @@
         <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L5" s="4">
         <v>0.8</v>
@@ -3507,7 +3442,7 @@
         <v>180</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O5" s="4">
         <v>0.1</v>
@@ -3516,18 +3451,18 @@
         <v>1</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -3539,10 +3474,10 @@
         <v>10</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L6" s="4">
         <v>2</v>
@@ -3551,7 +3486,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O6" s="4">
         <v>0.1</v>
@@ -3560,65 +3495,65 @@
         <v>1</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L7" s="4">
         <v>1</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J8">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L8" s="4">
         <v>0.8</v>
@@ -3627,153 +3562,153 @@
         <v>0.2</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I9" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L9" s="4">
         <v>2</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T9" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="U9" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J10">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L10" s="4">
         <v>0.5</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J11">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L11" s="4">
         <v>0.4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J12">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L12" s="4">
         <v>2</v>
@@ -3782,36 +3717,36 @@
         <v>1</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L13" s="4">
         <v>99999</v>
@@ -3820,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
@@ -3828,16 +3763,16 @@
         <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L14" s="4">
         <v>99999</v>
@@ -3851,10 +3786,10 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F15" s="4">
         <v>3</v>
@@ -3866,7 +3801,7 @@
         <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L15" s="4">
         <v>0.4</v>
@@ -3875,21 +3810,21 @@
         <v>1</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O15" s="4">
         <v>0.5</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -3901,7 +3836,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L16" s="4">
         <v>1</v>
@@ -3910,21 +3845,21 @@
         <v>1</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -3936,7 +3871,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L17" s="4">
         <v>1</v>
@@ -3945,27 +3880,27 @@
         <v>1</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O17" s="4">
         <v>1</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L18" s="4">
         <v>99999</v>
@@ -3974,123 +3909,123 @@
         <v>1</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U18" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="V18" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="V18" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L19" s="4">
         <v>2</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F20" s="4">
         <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L20" s="4">
         <v>0.5</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="F21" s="4">
         <v>5</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L21" s="4">
         <v>2</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F22" s="4">
         <v>5</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L22" s="4">
         <v>1</v>
@@ -4099,42 +4034,42 @@
         <v>0.2</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J23" s="4">
         <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L23" s="4">
         <v>1</v>
@@ -4143,45 +4078,45 @@
         <v>5</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O23" s="4">
         <v>0.2</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F24" s="4">
         <v>5</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J24" s="4">
         <v>2</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L24" s="4">
         <v>1.5</v>
@@ -4190,109 +4125,109 @@
         <v>0.5</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O24" s="4">
         <v>0.2</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F25" s="4">
         <v>5</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L25" s="4">
         <v>2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O25" s="4">
         <v>0.2</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L26" s="4">
         <v>99999</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F27" s="4">
         <v>5</v>
@@ -4304,27 +4239,27 @@
         <v>3</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L27" s="4">
         <v>1</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O27" s="4">
         <v>0.1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="F28" s="4">
         <v>5</v>
@@ -4333,27 +4268,27 @@
         <v>3</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L28" s="4">
         <v>1</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O28" s="4">
         <v>0.1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="F29" s="4">
         <v>5</v>
@@ -4362,19 +4297,414 @@
         <v>3</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O29" s="4">
         <v>0.1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4">
+        <v>10</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M30" s="4">
+        <v>120</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P30" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4">
+        <v>10</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L31" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="4">
+        <v>130</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="O31" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" s="4">
+        <v>3</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <v>8</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L32" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="4">
+        <v>140</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="O32" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P32" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C33" s="4">
+        <v>4</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4">
+        <v>8</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L33" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M33" s="4">
+        <v>140</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="O33" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C34" s="4">
+        <v>5</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <v>5</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L34" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="4">
+        <v>150</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="O34" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="P34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J35">
+        <v>15</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L35" s="4">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4">
+        <v>1</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C36" s="4">
+        <v>2</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J36">
+        <v>20</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L36" s="4">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4">
+        <v>1</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C37" s="4">
+        <v>3</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J37">
+        <v>25</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L37" s="4">
+        <v>1</v>
+      </c>
+      <c r="M37" s="4">
+        <v>1</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B38" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C38" s="4">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J38">
+        <v>30</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L38" s="4">
+        <v>1</v>
+      </c>
+      <c r="M38" s="4">
+        <v>1</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C39" s="4">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J39">
+        <v>35</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L39" s="4">
+        <v>1</v>
+      </c>
+      <c r="M39" s="4">
+        <v>1</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4386,7 +4716,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -4406,7 +4736,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>6</v>
@@ -4420,40 +4750,40 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -4467,16 +4797,16 @@
         <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -4502,22 +4832,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>374</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>42</v>
@@ -4526,7 +4856,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -4540,22 +4870,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>42</v>
@@ -4564,7 +4894,7 @@
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -4578,22 +4908,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>42</v>
@@ -4602,7 +4932,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -4616,16 +4946,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>42</v>
@@ -4634,7 +4964,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -4642,16 +4972,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>42</v>
@@ -4660,7 +4990,7 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -4668,22 +4998,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4691,22 +5021,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>216</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -4714,16 +5044,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>42</v>
@@ -4732,7 +5062,7 @@
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -4740,16 +5070,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>42</v>
@@ -4758,7 +5088,7 @@
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -4766,25 +5096,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -4801,15 +5131,15 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -4818,10 +5148,10 @@
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -4841,7 +5171,7 @@
         <v>23</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
@@ -4858,7 +5188,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -4875,15 +5205,15 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>46</v>
@@ -4892,10 +5222,10 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -4903,22 +5233,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>13</v>
@@ -4927,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -4941,19 +5271,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -4961,19 +5291,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -4981,19 +5311,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -5001,22 +5331,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>13</v>
@@ -5025,7 +5355,7 @@
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K24" s="4">
         <v>3</v>
@@ -5039,22 +5369,22 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>13</v>
@@ -5063,7 +5393,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -5077,22 +5407,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -5101,7 +5431,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -5115,22 +5445,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -5139,7 +5469,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -5150,10 +5480,10 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -5162,7 +5492,7 @@
         <v>23</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -5170,57 +5500,57 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -5229,42 +5559,42 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H31" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="I31" s="4">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>311</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5272,22 +5602,22 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>129</v>
+        <v>396</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>137</v>
+        <v>397</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>13</v>
@@ -5296,10 +5626,330 @@
         <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K32" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K33" s="4">
+        <v>1</v>
+      </c>
+      <c r="L33" s="4">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K34" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K35" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="L35" s="4">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B36" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K36" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="L36" s="4">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37" s="4">
+        <v>2</v>
+      </c>
+      <c r="L37" s="4">
+        <v>1</v>
+      </c>
+      <c r="M37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B38" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K38" s="4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K39" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B40" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K40" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K41" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K42" s="4">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -5328,44 +5978,44 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>20</v>
@@ -5374,18 +6024,18 @@
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>39</v>
@@ -5396,7 +6046,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>55</v>
@@ -5407,7 +6057,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>40</v>
@@ -5421,10 +6071,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -5432,10 +6082,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -5443,10 +6093,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -5454,24 +6104,24 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -5506,10 +6156,10 @@
   <sheetData>
     <row r="1" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -5519,40 +6169,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -5572,13 +6222,13 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G4" s="16"/>
     </row>
@@ -5588,13 +6238,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G5" s="16"/>
     </row>
@@ -5604,13 +6254,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -5620,7 +6270,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G7" s="16"/>
     </row>
@@ -5630,7 +6280,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G8" s="16"/>
     </row>
@@ -5640,7 +6290,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G9" s="16"/>
     </row>
@@ -5649,7 +6299,7 @@
         <v>20001</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -5658,13 +6308,13 @@
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -5672,10 +6322,10 @@
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -5762,463 +6412,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="15.375" style="4" customWidth="1"/>
-    <col min="7" max="8" width="17.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="15" style="4" customWidth="1"/>
-    <col min="11" max="11" width="17" style="4" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="6.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="19.25" style="4" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="J4" s="16"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="J5" s="16"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="J6" s="16"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="J7" s="16"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="J9" s="16"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G19"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G20"/>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G21"/>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G22"/>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G23"/>
-    </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G24"/>
-    </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G25"/>
-    </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G26"/>
-    </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G27"/>
-    </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G28"/>
-    </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G29"/>
-    </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G30"/>
-    </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G31"/>
-    </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G32"/>
-    </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G33"/>
-    </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G34"/>
-    </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G35"/>
-    </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G36"/>
-    </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G37"/>
-    </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G38"/>
-    </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G39"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="4" customWidth="1"/>
-    <col min="3" max="4" width="16.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="4" customWidth="1"/>
-    <col min="6" max="7" width="15.375" style="4" customWidth="1"/>
-    <col min="8" max="11" width="6.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="19.25" style="4" customWidth="1"/>
-    <col min="16" max="16" width="12.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="E4" s="21">
-        <v>10</v>
-      </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="16">
-        <v>2</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="E5" s="16">
-        <v>15</v>
-      </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="16">
-        <v>3</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="E6" s="16">
-        <v>30</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="19">
-        <v>4</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="E7" s="19">
-        <v>50</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="#SkillEffect" sheetId="6" r:id="rId3"/>
     <sheet name="#BuffInfo" sheetId="4" r:id="rId4"/>
     <sheet name="#SkillSet" sheetId="8" r:id="rId5"/>
+    <sheet name="#SkillGroup" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -34,89 +35,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="422">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>n초후 발동</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillCastingTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillApplyTarget</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Friendly</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillApplyTarget</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DecreaseAttribute</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>아군에게 적용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>자신에게 적용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>적에게 적용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>모두에게 적용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillEffect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_2</t>
@@ -126,15 +123,15 @@
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>버프 생성</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EffectType에 따라 EffectParam1~5에 넣을 값이 달라짐.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -215,15 +212,11 @@
       </rPr>
       <t xml:space="preserve"> : 버프 효과 발동 간격. 실수형</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooltimeSec</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_3</t>
@@ -233,23 +226,23 @@
   </si>
   <si>
     <t>스탯 증가 (Target은 Self만 가능)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>스탯 감소(Target은 Self만 가능)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>오라 생성</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DeactivateBuff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>버프 삭제</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -296,7 +289,7 @@
       </rPr>
       <t xml:space="preserve"> : 지속 시간. 실수형(0이면 무한)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -343,7 +336,7 @@
       </rPr>
       <t xml:space="preserve"> : 증가 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -390,170 +383,166 @@
       </rPr>
       <t xml:space="preserve"> : 감소 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>All</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_MOVESPEED_01</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_ATTACKSPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_6</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_7</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>데미지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BuffInfo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!BuffInfo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격2</t>
@@ -584,39 +573,39 @@
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>타겟팅스킬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부채꼴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>원형</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Donut</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>도넛 모양</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>직선 궤적</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -641,7 +630,7 @@
       </rPr>
       <t xml:space="preserve"> : 반지름</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -700,7 +689,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -759,7 +748,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -818,580 +807,556 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillScanType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Passive</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>상시 적용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>즉시발동</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageType</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Magical</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Pure</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillDamageType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>강타 데미지 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Magical</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MATK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>hit-blue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>focus-hit-1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>horizontal-slash</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectSFX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillSFX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>blade_hit_07</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>metal_punch_06</t>
   </si>
   <si>
     <t>Root</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Center</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>VFXAnchor</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillAnchorType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SFX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>VFX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillVFX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillAnchorType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ApplyTarget</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CameraShake</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Center</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>shake_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>shake_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>브레이크</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>flashy-hit-1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ActivateAura</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>스턴 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>침묵 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>이동불가 디버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IsDebuff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillEffectTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>받는 데미지 증가</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>브레이크 상태 효과1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>브레이크 상태 효과2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>브레이크(받는 데미지 증가)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillEffectTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DecreaseAttribute</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_DAMAGETAKEN</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IsBasicAttack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>기본직업 고유스킬1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>기본직업 고유스킬2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Instant</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DASH</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>데미지 효과1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>데미지 효과2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>데미지 효과3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_MONSTER_ATK_MELEE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_MONSTER_ATK_RANGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 근접공격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수 원거리공격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>몬스터 물리 데미지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>몬스터 마법 데미지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사 원거리 공격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill_2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill_4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BaseAttackSkill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IntervalEffect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DASH_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>대시 스킬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>대시공격 스킬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Line</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Line</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>대시어택 데미지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillScanType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MotionEffectTime</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 단일 공격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
   </si>
   <si>
     <t>캐스팅 범위(직선) 공격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1438,165 +1403,157 @@
       </rPr>
       <t xml:space="preserve"> : 타갯 수</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>발동확률 0~1 = 0~100%</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 스킬 데미지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 스킬 데미지2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MATK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ScanParam2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillCastingTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Casting;Skill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MotionNames</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 범위(원형) 공격</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>CastingParam</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Casting;Skill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BREAK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SkillInfo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>무적 스킬</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>무적 버프</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>무적 효과</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>wood_bat_finisher_05</t>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_POWERATTACK_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>shake_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1621,27 +1578,27 @@
       </rPr>
       <t xml:space="preserve"> : 버프 ID</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>OnHitCaster</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>OnHitTarget</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>타격시 n% 확률로 발동(시전자)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>타격시 n% 확률로 발동(피격자)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_SPECIALATTACK_02</t>
@@ -1651,35 +1608,31 @@
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_DASH_ATTACK_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartEffect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_0</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>FinishEffect</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>발사체 생성</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1792,55 +1745,55 @@
       </rPr>
       <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SpawnProjectile</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Projectile_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_PROJECTILE_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>투사체 발사1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>투사체 데미지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EffectVFX</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SpawnProjectile</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1958,7 +1911,7 @@
       </rPr>
       <t xml:space="preserve"> : 발사체 효과 반경(0이면 단일)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_02</t>
@@ -1980,60 +1933,60 @@
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_01</t>
   </si>
   <si>
     <t>SKILL_PROJECTILE_ATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_02</t>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_03</t>
   </si>
   <si>
     <t>SKILL_CASTING_ATTACK_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_POWERATTACK_01</t>
@@ -2043,240 +1996,380 @@
   </si>
   <si>
     <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Attack</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAttack</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Attack</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_01_3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_02_5</t>
+  </si>
+  <si>
+    <t>SampleSkill_02_4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_02_1</t>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV1</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV5</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지5</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지5</t>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitCaster</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CooltimeSec</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>StaminaCost</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicAttack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SPECIALATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ApplyTarget</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillApplyTarget</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSFX</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sector</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Skill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_4</t>
+  </si>
+  <si>
+    <t>SkillID_5</t>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SampleSkill_01_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SampleSkill_02_5</t>
-  </si>
-  <si>
-    <t>SampleSkill_02_4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SampleSkill_02_1</t>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV2</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV3</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV4</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV5</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV2</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV3</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV4</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV5</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_02</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_03</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지2</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지3</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지4</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지5</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_02</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_03</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지2</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지3</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지4</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지5</t>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv2</t>
-  </si>
-  <si>
-    <t>Lv3</t>
-  </si>
-  <si>
-    <t>Lv4</t>
-  </si>
-  <si>
-    <t>Lv5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+  </si>
+  <si>
+    <t>기본공격</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스 블레이드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률로 적에게 포스로 데미지를 입힌다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방 부채꼴 범위의 적에게 데미지를 입힌다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2474,12 +2567,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2502,40 +2595,46 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2835,60 +2934,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2905,15 +3004,15 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2921,15 +3020,15 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2937,76 +3036,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3021,14 +3120,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>112</v>
+        <v>393</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -3037,7 +3136,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -3046,7 +3145,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -3060,88 +3159,88 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -3152,23 +3251,23 @@
         <v>0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F37"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3203,7 +3302,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -3214,167 +3313,167 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="AA2" s="4" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="T3" s="4" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F4" s="4">
         <v>0.3</v>
@@ -3386,10 +3485,10 @@
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L4" s="4">
         <v>0.5</v>
@@ -3398,7 +3497,7 @@
         <v>120</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O4" s="4">
         <v>0.1</v>
@@ -3407,18 +3506,18 @@
         <v>1</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F5" s="4">
         <v>0.5</v>
@@ -3430,10 +3529,10 @@
         <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L5" s="4">
         <v>0.8</v>
@@ -3442,7 +3541,7 @@
         <v>180</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O5" s="4">
         <v>0.1</v>
@@ -3451,18 +3550,18 @@
         <v>1</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -3474,10 +3573,10 @@
         <v>10</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L6" s="4">
         <v>2</v>
@@ -3486,7 +3585,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O6" s="4">
         <v>0.1</v>
@@ -3495,65 +3594,65 @@
         <v>1</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>358</v>
-      </c>
       <c r="I7" t="s">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="L7" s="4">
         <v>1</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>358</v>
-      </c>
       <c r="I8" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="J8">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="L8" s="4">
         <v>0.8</v>
@@ -3562,153 +3661,156 @@
         <v>0.2</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>358</v>
-      </c>
       <c r="I9" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L9" s="4">
         <v>2</v>
       </c>
+      <c r="M9" s="4">
+        <v>1</v>
+      </c>
       <c r="N9" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J10">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L10" s="4">
         <v>0.5</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J11">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="L11" s="4">
         <v>0.4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J12">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L12" s="4">
         <v>2</v>
@@ -3717,36 +3819,36 @@
         <v>1</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="L13" s="4">
         <v>99999</v>
@@ -3755,24 +3857,24 @@
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L14" s="4">
         <v>99999</v>
@@ -3781,15 +3883,15 @@
         <v>1</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F15" s="4">
         <v>3</v>
@@ -3801,7 +3903,7 @@
         <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L15" s="4">
         <v>0.4</v>
@@ -3810,21 +3912,21 @@
         <v>1</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O15" s="4">
         <v>0.5</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -3836,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L16" s="4">
         <v>1</v>
@@ -3845,21 +3947,21 @@
         <v>1</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -3871,7 +3973,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L17" s="4">
         <v>1</v>
@@ -3880,27 +3982,27 @@
         <v>1</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O17" s="4">
         <v>1</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L18" s="4">
         <v>99999</v>
@@ -3909,123 +4011,123 @@
         <v>1</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L19" s="4">
         <v>2</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F20" s="4">
         <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L20" s="4">
         <v>0.5</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F21" s="4">
         <v>5</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>191</v>
+        <v>388</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L21" s="4">
         <v>2</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F22" s="4">
         <v>5</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L22" s="4">
         <v>1</v>
@@ -4034,42 +4136,42 @@
         <v>0.2</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Q22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="R22" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="T22" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J23" s="4">
         <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="L23" s="4">
         <v>1</v>
@@ -4078,45 +4180,45 @@
         <v>5</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="O23" s="4">
         <v>0.2</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="F24" s="4">
         <v>5</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="J24" s="4">
         <v>2</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="L24" s="4">
         <v>1.5</v>
@@ -4125,109 +4227,109 @@
         <v>0.5</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="O24" s="4">
         <v>0.2</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="F25" s="4">
         <v>5</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="L25" s="4">
         <v>2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="O25" s="4">
         <v>0.2</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="L26" s="4">
         <v>99999</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="F27" s="4">
         <v>5</v>
@@ -4239,27 +4341,27 @@
         <v>3</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="L27" s="4">
         <v>1</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O27" s="4">
         <v>0.1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="F28" s="4">
         <v>5</v>
@@ -4268,27 +4370,27 @@
         <v>3</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="L28" s="4">
         <v>1</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O28" s="4">
         <v>0.1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="F29" s="4">
         <v>5</v>
@@ -4297,33 +4399,27 @@
         <v>3</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O29" s="4">
         <v>0.1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C30" s="4">
-        <v>1</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F30" s="4">
         <v>1</v>
@@ -4335,10 +4431,10 @@
         <v>10</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>91</v>
+        <v>401</v>
       </c>
       <c r="L30" s="4">
         <v>0.5</v>
@@ -4347,7 +4443,7 @@
         <v>120</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O30" s="4">
         <v>0.1</v>
@@ -4356,21 +4452,15 @@
         <v>1</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C31" s="4">
-        <v>2</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F31" s="4">
         <v>1</v>
@@ -4382,10 +4472,10 @@
         <v>10</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L31" s="4">
         <v>0.5</v>
@@ -4394,7 +4484,7 @@
         <v>130</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O31" s="4">
         <v>0.1</v>
@@ -4403,21 +4493,15 @@
         <v>1</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C32" s="4">
-        <v>3</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>401</v>
+        <v>354</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F32" s="4">
         <v>1</v>
@@ -4429,10 +4513,10 @@
         <v>8</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L32" s="4">
         <v>0.5</v>
@@ -4441,7 +4525,7 @@
         <v>140</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O32" s="4">
         <v>0.1</v>
@@ -4450,21 +4534,15 @@
         <v>1</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C33" s="4">
-        <v>4</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>402</v>
+        <v>355</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F33" s="4">
         <v>1</v>
@@ -4476,10 +4554,10 @@
         <v>8</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L33" s="4">
         <v>0.5</v>
@@ -4488,7 +4566,7 @@
         <v>140</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O33" s="4">
         <v>0.1</v>
@@ -4497,21 +4575,15 @@
         <v>1</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="34" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C34" s="4">
-        <v>5</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="F34" s="4">
         <v>1</v>
@@ -4523,10 +4595,10 @@
         <v>5</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L34" s="4">
         <v>0.5</v>
@@ -4535,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O34" s="4">
         <v>0.1</v>
@@ -4544,30 +4616,24 @@
         <v>1</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="C35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J35">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L35" s="4">
         <v>1</v>
@@ -4576,30 +4642,24 @@
         <v>1</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>118</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C36" s="4">
-        <v>2</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>400</v>
+        <v>359</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J36">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L36" s="4">
         <v>1</v>
@@ -4608,30 +4668,24 @@
         <v>1</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>118</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C37" s="4">
-        <v>3</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J37">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L37" s="4">
         <v>1</v>
@@ -4640,30 +4694,24 @@
         <v>1</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>118</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="C38" s="4">
-        <v>4</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J38">
         <v>30</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L38" s="4">
         <v>1</v>
@@ -4672,30 +4720,24 @@
         <v>1</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>118</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C39" s="4">
-        <v>5</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J39">
         <v>35</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L39" s="4">
         <v>1</v>
@@ -4704,11 +4746,11 @@
         <v>1</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>118</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4736,7 +4778,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>6</v>
@@ -4750,63 +4792,63 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>146</v>
+        <v>394</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>116</v>
+        <v>397</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>130</v>
+        <v>398</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>399</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>238</v>
+        <v>400</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>239</v>
+        <v>406</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>396</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -4832,31 +4874,31 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I4" s="4">
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -4870,31 +4912,31 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4">
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -4908,31 +4950,31 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4">
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -4946,25 +4988,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="4">
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -4972,25 +5014,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I8" s="4">
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -4998,22 +5040,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -5021,22 +5063,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -5044,25 +5086,25 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I11" s="4">
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -5070,25 +5112,25 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I12" s="4">
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -5096,25 +5138,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -5122,36 +5164,36 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -5159,36 +5201,36 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -5196,36 +5238,36 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -5233,31 +5275,31 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I20" s="4">
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -5271,19 +5313,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -5291,19 +5333,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -5311,19 +5353,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -5331,31 +5373,31 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I24" s="4">
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K24" s="4">
         <v>3</v>
@@ -5369,31 +5411,31 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I25" s="4">
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -5407,31 +5449,31 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I26" s="4">
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -5445,31 +5487,31 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I27" s="4">
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -5480,19 +5522,19 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>10</v>
+        <v>395</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -5500,57 +5542,57 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -5559,42 +5601,42 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5602,31 +5644,31 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I32" s="4">
         <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K32" s="4">
         <v>1</v>
@@ -5634,28 +5676,28 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K33" s="4">
         <v>1</v>
@@ -5669,28 +5711,28 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K34" s="4">
         <v>1.25</v>
@@ -5704,28 +5746,28 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K35" s="4">
         <v>1.5</v>
@@ -5739,28 +5781,28 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K36" s="4">
         <v>1.75</v>
@@ -5774,28 +5816,28 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K37" s="4">
         <v>2</v>
@@ -5809,28 +5851,28 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>13</v>
+        <v>405</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K38" s="4">
         <v>2.5</v>
@@ -5838,28 +5880,28 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>398</v>
-      </c>
       <c r="H39" s="4" t="s">
-        <v>13</v>
+        <v>405</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K39" s="4">
         <v>3</v>
@@ -5867,28 +5909,28 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K40" s="4">
         <v>3.5</v>
@@ -5896,28 +5938,28 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K41" s="4">
         <v>4</v>
@@ -5925,35 +5967,35 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>41</v>
+        <v>404</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K42" s="4">
         <v>4.5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5978,103 +6020,103 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -6082,10 +6124,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -6093,10 +6135,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -6104,28 +6146,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="D10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6156,10 +6198,10 @@
   <sheetData>
     <row r="1" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C1" s="14"/>
     </row>
@@ -6169,40 +6211,40 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="17" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
@@ -6222,13 +6264,13 @@
         <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="G4" s="16"/>
     </row>
@@ -6238,13 +6280,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="G5" s="16"/>
     </row>
@@ -6254,13 +6296,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="G6" s="16"/>
     </row>
@@ -6270,7 +6312,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G7" s="16"/>
     </row>
@@ -6280,7 +6322,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="G8" s="16"/>
     </row>
@@ -6290,7 +6332,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="G9" s="16"/>
     </row>
@@ -6299,7 +6341,7 @@
         <v>20001</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -6308,13 +6350,13 @@
         <v>30001</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -6322,11 +6364,275 @@
         <v>100001</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>333</v>
-      </c>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C17"/>
+    </row>
+    <row r="18" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C19"/>
+      <c r="D19"/>
+    </row>
+    <row r="20" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D20"/>
+    </row>
+    <row r="21" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D21"/>
+    </row>
+    <row r="22" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D22"/>
+    </row>
+    <row r="23" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D23"/>
+    </row>
+    <row r="24" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D24"/>
+    </row>
+    <row r="25" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D25"/>
+    </row>
+    <row r="26" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D27"/>
+    </row>
+    <row r="28" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D28"/>
+    </row>
+    <row r="29" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D29"/>
+    </row>
+    <row r="30" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D30"/>
+    </row>
+    <row r="31" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D31"/>
+    </row>
+    <row r="32" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R39"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="26" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="19.25" style="4" customWidth="1"/>
+    <col min="17" max="17" width="12.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="12"/>
+      <c r="B3" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="16">
+        <v>101</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="12"/>
+      <c r="B5" s="16">
+        <v>102</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="19"/>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="19"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="19"/>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B10"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B12"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14"/>
@@ -6408,8 +6714,7 @@
       <c r="D39"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,6 @@
     <sheet name="#SkillEffect" sheetId="6" r:id="rId3"/>
     <sheet name="#BuffInfo" sheetId="4" r:id="rId4"/>
     <sheet name="#SkillSet" sheetId="8" r:id="rId5"/>
-    <sheet name="#SkillGroup" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -35,85 +34,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="405">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
   </si>
   <si>
     <t>!EnumTable</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffect</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>n초후 발동</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillCastingTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillApplyTarget</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Instant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffect</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>n초후 발동</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillCastingTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillApplyTarget</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>Self</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Friendly</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DecreaseAttribute</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아군에게 적용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>자신에게 적용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>적에게 적용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>모두에게 적용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillEffect</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_2</t>
@@ -123,15 +122,15 @@
   </si>
   <si>
     <t>ActivateBuff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>버프 생성</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectType에 따라 EffectParam1~5에 넣을 값이 달라짐.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -212,11 +211,11 @@
       </rPr>
       <t xml:space="preserve"> : 버프 효과 발동 간격. 실수형</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_3</t>
@@ -226,23 +225,23 @@
   </si>
   <si>
     <t>스탯 증가 (Target은 Self만 가능)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>스탯 감소(Target은 Self만 가능)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>오라 생성</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DeactivateBuff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>버프 삭제</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -289,7 +288,7 @@
       </rPr>
       <t xml:space="preserve"> : 지속 시간. 실수형(0이면 무한)</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -336,7 +335,7 @@
       </rPr>
       <t xml:space="preserve"> : 증가 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -383,166 +382,166 @@
       </rPr>
       <t xml:space="preserve"> : 감소 수치. 실수형</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>All</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 증가 효과</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 효과</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이동속도 감소 디버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_DECREASE_MOVESPEED_01</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_ATTACKSPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>공격속도 증가 효과</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_ATTACKSPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_6</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>데미지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ATK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BuffInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!BuffInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해골전사 몬스터 공격2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>악마 몬스터 공격2</t>
@@ -573,39 +572,39 @@
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>타겟팅스킬</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>부채꼴</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>원형</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Donut</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>도넛 모양</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>직선 궤적</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ScanType에 따라 ScanParam1~2에 넣을 값이 달라짐</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -630,7 +629,7 @@
       </rPr>
       <t xml:space="preserve"> : 반지름</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -689,7 +688,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -748,7 +747,7 @@
       </rPr>
       <t/>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -807,556 +806,556 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillScanType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시 적용</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>즉시발동</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillDamageType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타 데미지 효과</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magical</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_101</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Circle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit-blue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal-slash</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSFX</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>blade_hit_07</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>body_hit_finisher_52</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+  </si>
+  <si>
+    <t>Root</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFXAnchor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillAnchorType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>VFX</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFX</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillVFXAnchor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAnchorType</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>!SkillScanType</t>
+    <t>Damage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CameraShake</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Center</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>shake_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>flashy-hit-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스턴 디버프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>침묵 디버프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동불가 디버프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDebuff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillEffectTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_MOVESPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BINDING</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivateBuff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 데미지 증가</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 상태 효과2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크(받는 데미지 증가)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillEffectTypes</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>EffectParam_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecreaseAttribute</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IncreaseAttribute</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_DECREASE_DAMAGETAKEN</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsBasicAttack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본직업 고유스킬2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Target</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEBUFF_BREAK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지 효과3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_MELEE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_ATK_RANGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사 근접공격</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골궁수 원거리공격</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 물리 데미지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 마법 데미지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골마법사 원거리 공격</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseAttackSkill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalEffect</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시 스킬</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시공격 스킬</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시어택 데미지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Physical</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillScanType</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Attack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>상시 적용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>즉시발동</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pure</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillDamageType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>강타 데미지 효과</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magical</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Circle</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>hit-blue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>horizontal-slash</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSFX</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>blade_hit_07</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>body_hit_finisher_52</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-  </si>
-  <si>
-    <t>Root</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFXAnchor</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillAnchorType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SFX</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>VFX</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFX</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillVFXAnchor</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillAnchorType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CameraShake</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Center</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>shake_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>flashy-hit-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateAura</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>스턴 디버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>침묵 디버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동불가 디버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDebuff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillEffectTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BINDING</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActivateBuff</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_DEBUFF_BREAK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 데미지 증가</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 상태 효과2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크(받는 데미지 증가)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillEffectTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>EffectParam_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DecreaseAttribute</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IncreaseAttribute</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_DECREASE_DAMAGETAKEN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsBasicAttack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본직업 고유스킬2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>데미지 효과3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_ATK_MELEE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_ATK_RANGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사 근접공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골궁수 원거리공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 물리 데미지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_MONSTER_PHYSICAL_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_MONSTER_MAGICAL_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 마법 데미지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골마법사 원거리 공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseAttackSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalEffect</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시 스킬</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시공격 스킬</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>대시어택 데미지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Physical</t>
-  </si>
-  <si>
-    <t>Physical</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillScanType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>MotionEffectTime</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 단일 공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
   </si>
   <si>
     <t>캐스팅 범위(직선) 공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1403,157 +1402,157 @@
       </rPr>
       <t xml:space="preserve"> : 타갯 수</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>발동확률 0~1 = 0~100%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_CASTING_DAMAGE_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 스킬 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐스팅 스킬 데미지2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanParam2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillCastingTypes</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>CastingTypes 에 따라 CastingParam 에 값이 다르다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 시간 (초) : 캐스팅중 넉백시 취소</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>발동확률 0~1 = 0~100%</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CASTING_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_CASTING_DAMAGE_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 스킬 데미지1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐스팅 스킬 데미지2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanParam2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillCastingTypes</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>Casting</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting;Skill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MotionNames</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_SILENCE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>캐스팅 범위(원형) 공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_CASTING_DAMAGE_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CastingParam</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting;Skill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_BREAK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_BREAK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>무적 스킬</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Target</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>무적 버프</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
   </si>
   <si>
     <t>SE_ACTIVATE_BUFF_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>무적 효과</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DEBUFF_STUN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>wood_bat_finisher_05</t>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_POWERATTACK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>shake_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1578,27 +1577,27 @@
       </rPr>
       <t xml:space="preserve"> : 버프 ID</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_TAKE_DAMAGE_101</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>OnHitCaster</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>OnHitTarget</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>타격시 n% 확률로 발동(시전자)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>타격시 n% 확률로 발동(피격자)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_SPECIALATTACK_02</t>
@@ -1608,31 +1607,31 @@
   </si>
   <si>
     <t>Circle</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IsOnHitTrigger</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_DASH_ATTACK_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Casting</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_0</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>FinishEffect</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>발사체 생성</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1745,55 +1744,55 @@
       </rPr>
       <t xml:space="preserve"> : 넉백 힘 방향 및 비율(-,+)</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_DAMAGE_IMMUNITY</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>원거리 발사체 공격1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Physical</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SpawnProjectile</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Projectile_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_PROJECTILE_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>투사체 발사1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>투사체 데미지1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectVFX</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SE_SPAWNPOJECTILE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SpawnProjectile</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1911,465 +1910,381 @@
       </rPr>
       <t xml:space="preserve"> : 발사체 효과 반경(0이면 단일)</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_02</t>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_03</t>
+  </si>
+  <si>
+    <t>투사체 발사2</t>
+  </si>
+  <si>
+    <t>투사체 발사3</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_02</t>
+  </si>
+  <si>
+    <t>Prefab_Projectile_03</t>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 발사체 공격2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 발사체 공격3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_SPAWNPOJECTILE_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_01</t>
+  </si>
+  <si>
+    <t>SKILL_PROJECTILE_ATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_DASH_ATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_02</t>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_MONSTER_MATK_RANGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_03</t>
+  </si>
+  <si>
+    <t>SKILL_CASTING_ATTACK_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casting</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAttack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Attack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_SPECIALATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_01_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_02_5</t>
+  </si>
+  <si>
+    <t>SampleSkill_02_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_02_1</t>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillSet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV5</t>
+  </si>
+  <si>
+    <t>SE_TAKE_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT1_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 기본공격 데미지5</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 확률발동 데미지5</t>
+  </si>
+  <si>
+    <t>focus-hit-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>metal_punch_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CastingType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHitCaster</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CooltimeSec</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaCost</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillDamageType</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>SE_SPAWNPOJECTILE_02</t>
-  </si>
-  <si>
-    <t>SE_SPAWNPOJECTILE_03</t>
-  </si>
-  <si>
-    <t>투사체 발사2</t>
-  </si>
-  <si>
-    <t>투사체 발사3</t>
-  </si>
-  <si>
-    <t>Prefab_Projectile_02</t>
-  </si>
-  <si>
-    <t>Prefab_Projectile_03</t>
-  </si>
-  <si>
-    <t>SKILL_PROJECTILE_ATTACK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PROJECTILE_ATTACK_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 발사체 공격2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 발사체 공격3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_SPAWNPOJECTILE_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_SPAWNPOJECTILE_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PROJECTILE_ATTACK_01</t>
-  </si>
-  <si>
-    <t>SKILL_PROJECTILE_ATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_DASH_ATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_02</t>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_MONSTER_MATK_RANGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_03</t>
-  </si>
-  <si>
-    <t>SKILL_CASTING_ATTACK_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Casting</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Attack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicAttack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Attack</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_SPECIALATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SampleSkill_01_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SampleSkill_02_5</t>
-  </si>
-  <si>
-    <t>SampleSkill_02_4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SampleSkill_02_1</t>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSet</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV1</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV2</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV3</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV4</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV5</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV1</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV2</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV3</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV4</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV5</t>
-  </si>
-  <si>
-    <t>SE_TAKE_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_02</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_03</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT1_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지2</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지3</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지4</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지5</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_02</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_03</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지2</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지3</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지4</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지5</t>
-  </si>
-  <si>
-    <t>focus-hit-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>metal_punch_06</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Instant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CastingType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OnHitCaster</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooltimeSec</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaCost</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillDamageType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>ApplyTarget</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Self</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillApplyTarget</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DamageType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectSFX</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Sector</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ScanParam1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>StartEffect</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Enemy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>EffectParam_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Skill</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Group</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_4</t>
-  </si>
-  <si>
-    <t>SkillID_5</t>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-  </si>
-  <si>
-    <t>기본공격</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>포스 블레이드</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격시 확률로 적에게 포스로 데미지를 입힌다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전방 부채꼴 범위의 적에게 데미지를 입힌다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2567,12 +2482,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2595,46 +2510,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3120,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D21" s="6"/>
     </row>
@@ -3267,7 +3176,7 @@
       <c r="F37"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3319,16 +3228,16 @@
         <v>343</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>179</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>257</v>
@@ -3337,7 +3246,7 @@
         <v>350</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>246</v>
@@ -3364,7 +3273,7 @@
         <v>142</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="V2" s="4" t="s">
         <v>288</v>
@@ -3485,7 +3394,7 @@
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>88</v>
@@ -3608,7 +3517,7 @@
         <v>345</v>
       </c>
       <c r="I7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J7">
         <v>20</v>
@@ -4101,7 +4010,7 @@
         <v>5</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>119</v>
@@ -4416,7 +4325,7 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>344</v>
@@ -4431,10 +4340,10 @@
         <v>10</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="L30" s="4">
         <v>0.5</v>
@@ -4452,12 +4361,12 @@
         <v>1</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>344</v>
@@ -4493,12 +4402,12 @@
         <v>1</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>344</v>
@@ -4534,12 +4443,12 @@
         <v>1</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>344</v>
@@ -4575,12 +4484,12 @@
         <v>1</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>344</v>
@@ -4595,7 +4504,7 @@
         <v>5</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>88</v>
@@ -4616,12 +4525,12 @@
         <v>1</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>345</v>
@@ -4642,12 +4551,12 @@
         <v>1</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>345</v>
@@ -4668,12 +4577,12 @@
         <v>1</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>345</v>
@@ -4694,12 +4603,12 @@
         <v>1</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>345</v>
@@ -4720,12 +4629,12 @@
         <v>1</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>345</v>
@@ -4746,11 +4655,11 @@
         <v>1</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4792,25 +4701,25 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>301</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>400</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>21</v>
@@ -4836,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>112</v>
@@ -4874,7 +4783,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>194</v>
@@ -5528,7 +5437,7 @@
         <v>270</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>22</v>
@@ -5656,10 +5565,10 @@
         <v>294</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>12</v>
@@ -5676,10 +5585,10 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>39</v>
@@ -5711,10 +5620,10 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>39</v>
@@ -5746,10 +5655,10 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>39</v>
@@ -5781,10 +5690,10 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>39</v>
@@ -5816,10 +5725,10 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>39</v>
@@ -5851,10 +5760,10 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>39</v>
@@ -5863,13 +5772,13 @@
         <v>109</v>
       </c>
       <c r="F38" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="H38" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>68</v>
@@ -5880,10 +5789,10 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>39</v>
@@ -5892,13 +5801,13 @@
         <v>109</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="H39" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>68</v>
@@ -5909,10 +5818,10 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>39</v>
@@ -5921,10 +5830,10 @@
         <v>109</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>12</v>
@@ -5938,10 +5847,10 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>39</v>
@@ -5950,10 +5859,10 @@
         <v>109</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>12</v>
@@ -5967,22 +5876,22 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>109</v>
       </c>
       <c r="F42" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>12</v>
@@ -5995,7 +5904,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6167,7 +6076,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6379,342 +6288,79 @@
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C16"/>
     </row>
-    <row r="17" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17"/>
     </row>
-    <row r="18" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18"/>
     </row>
-    <row r="19" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19"/>
       <c r="D19"/>
     </row>
-    <row r="20" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D20"/>
     </row>
-    <row r="21" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D21"/>
     </row>
-    <row r="22" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D22"/>
     </row>
-    <row r="23" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D23"/>
     </row>
-    <row r="24" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D24"/>
     </row>
-    <row r="25" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D25"/>
     </row>
-    <row r="26" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D26"/>
     </row>
-    <row r="27" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D27"/>
     </row>
-    <row r="28" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D28"/>
     </row>
-    <row r="29" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D29"/>
     </row>
-    <row r="30" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D30"/>
     </row>
-    <row r="31" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D31"/>
     </row>
-    <row r="32" spans="3:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D32"/>
     </row>
-    <row r="33" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D33"/>
     </row>
-    <row r="34" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D34"/>
     </row>
-    <row r="35" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35"/>
     </row>
-    <row r="36" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36"/>
     </row>
-    <row r="37" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37"/>
     </row>
-    <row r="38" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
     </row>
-    <row r="39" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="26" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="19.25" style="4" customWidth="1"/>
-    <col min="17" max="17" width="12.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="C1" s="14"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="16">
-        <v>101</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>421</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="16">
-        <v>102</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="16"/>
-      <c r="G6" s="16"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="19"/>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="19"/>
-      <c r="G8" s="16"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="19"/>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B11"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B12"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C14"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C15"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C16"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C17"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C18"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C19"/>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D20"/>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D22"/>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D24"/>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D25"/>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D26"/>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D27"/>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D29"/>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="D32"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33"/>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D39"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Shared/XLS/Skill.xlsx
+++ b/Shared/XLS/Skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="531">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -421,10 +421,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>SE_INCREASE_MOVESPEED_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_ACTIVATE_DEBUFF_MOVESPEED_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -521,10 +517,6 @@
   </si>
   <si>
     <t>IncreaseAttribute</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1028,10 +1020,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ActivateAura</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>스턴 디버프</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1165,10 +1153,6 @@
   </si>
   <si>
     <t>Attack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SE_ACTIVATE_BUFF_DASH</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -2100,10 +2084,6 @@
     <t>SKILL_HERO_01_SLOT1_LV5</t>
   </si>
   <si>
-    <t>SKILL_HERO_01_SLOT2_LV1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_HERO_01_SLOT2_LV2</t>
   </si>
   <si>
@@ -2124,10 +2104,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>영웅1의 기본공격 데미지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_HERO_01_SLOT1_DAMAGE_02</t>
   </si>
   <si>
@@ -2140,25 +2116,9 @@
     <t>SE_HERO_01_SLOT1_DAMAGE_05</t>
   </si>
   <si>
-    <t>영웅1의 기본공격 데미지2</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지3</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지4</t>
-  </si>
-  <si>
-    <t>영웅1의 기본공격 데미지5</t>
-  </si>
-  <si>
     <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
   </si>
   <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SE_HERO_01_SLOT2_DAMAGE_02</t>
   </si>
   <si>
@@ -2166,25 +2126,6 @@
   </si>
   <si>
     <t>SE_HERO_01_SLOT2_DAMAGE_04</t>
-  </si>
-  <si>
-    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지2</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지3</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지4</t>
-  </si>
-  <si>
-    <t>영웅1의 확률발동 데미지5</t>
   </si>
   <si>
     <t>focus-hit-1</t>
@@ -2273,6 +2214,509 @@
   <si>
     <t>EffectParam_2</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV5</t>
+  </si>
+  <si>
+    <t>와이드 슬래시1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이드 슬래시2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이드 슬래시3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이드 슬래시4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이드 슬래시5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스 블레이드1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스 블레이드2</t>
+  </si>
+  <si>
+    <t>포스 블레이드3</t>
+  </si>
+  <si>
+    <t>포스 블레이드4</t>
+  </si>
+  <si>
+    <t>포스 블레이드5</t>
+  </si>
+  <si>
+    <t>윈드 러너1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스 필드1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드 포스 버스터1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>윈드 러너2</t>
+  </si>
+  <si>
+    <t>윈드 러너3</t>
+  </si>
+  <si>
+    <t>윈드 러너4</t>
+  </si>
+  <si>
+    <t>윈드 러너5</t>
+  </si>
+  <si>
+    <t>포스 필드2</t>
+  </si>
+  <si>
+    <t>포스 필드3</t>
+  </si>
+  <si>
+    <t>포스 필드4</t>
+  </si>
+  <si>
+    <t>포스 필드5</t>
+  </si>
+  <si>
+    <t>그랜드 포스 버스터2</t>
+  </si>
+  <si>
+    <t>그랜드 포스 버스터3</t>
+  </si>
+  <si>
+    <t>그랜드 포스 버스터4</t>
+  </si>
+  <si>
+    <t>그랜드 포스 버스터5</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_ATTACKSPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_MOVESPEED_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_MOVESPEED_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_MOVESPEED_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_MOVESPEED_05</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_ATTACKSPEED_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_ATTACKSPEED_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_ATTACKSPEED_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_ATTACKSPEED_05</t>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleSkill_01_5</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Compass</t>
+  </si>
+  <si>
+    <t>SampleSkill_02_2</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT5_DAMAGE_05</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT5_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT5_DAMAGE_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT5_DAMAGE_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT5_DAMAGE_04</t>
+  </si>
+  <si>
+    <t>ATK_Ratio</t>
+  </si>
+  <si>
+    <t>ActivateAura</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT2_DAMAGE_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_AURA_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_AURA_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_AURA_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_AURA_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_AURA_05</t>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_DASH</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_ACTIVATE_BUFF_ATTACKSPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증폭 버프1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증폭 버프2</t>
+  </si>
+  <si>
+    <t>공격력 증폭 버프3</t>
+  </si>
+  <si>
+    <t>공격력 증폭 버프4</t>
+  </si>
+  <si>
+    <t>공격력 증폭 버프5</t>
+  </si>
+  <si>
+    <t>SE_INCREASE_MOVESPEED_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT3_INCREASE_ATTACKSPEED_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_04</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_05</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_ACTIVATE_BUFF_ATTACKRATIO_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_02</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_03</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_04</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_04</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_05</t>
+  </si>
+  <si>
+    <t>SE_HERO_01_SLOT4_INCREASE_ATTACKRATIO_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 1스킬 기본공격 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 1스킬 기본공격 데미지2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 1스킬 기본공격 데미지3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 1스킬 기본공격 데미지4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 1스킬 기본공격 데미지5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 2스킬 확률발동 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 2스킬 확률발동 데미지2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 2스킬 확률발동 데미지3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 2스킬 확률발동 데미지4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 2스킬 확률발동 데미지5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 이속스탯1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 이속스탯2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 이속스탯3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 이속스탯4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 이속스탯5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 공속스탯1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 공속스탯2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 공속스탯3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 공속스탯4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 3스킬 패시브 공속스탯5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 스탯1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 스탯2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 스탯3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 스탯4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 스탯5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 버프1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 버프2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 버프3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 버프4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 공격력 증가 버프5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 적 둔화 오라1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 적 둔화 오라2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 적 둔화 오라3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 적 둔화 오라4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 4스킬 적 둔화 오라5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 5스킬 확률발동 데미지1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅1의 5스킬 확률발동 데미지2</t>
+  </si>
+  <si>
+    <t>영웅1의 5스킬 확률발동 데미지3</t>
+  </si>
+  <si>
+    <t>영웅1의 5스킬 확률발동 데미지4</t>
+  </si>
+  <si>
+    <t>영웅1의 5스킬 확률발동 데미지5</t>
+  </si>
+  <si>
+    <t>BUFF_HERO_01_SLOT4_ATTACKRATIO_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUFF_HERO_01_SLOT4_ATTACKRATIO_02</t>
+  </si>
+  <si>
+    <t>BUFF_HERO_01_SLOT4_ATTACKRATIO_03</t>
+  </si>
+  <si>
+    <t>BUFF_HERO_01_SLOT4_ATTACKRATIO_04</t>
+  </si>
+  <si>
+    <t>BUFF_HERO_01_SLOT4_ATTACKRATIO_05</t>
   </si>
 </sst>
 </file>
@@ -2819,7 +3263,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2843,60 +3287,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2918,7 +3362,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>17</v>
@@ -2945,76 +3389,76 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3029,14 +3473,14 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="13"/>
@@ -3045,7 +3489,7 @@
     <row r="23" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="13"/>
@@ -3054,7 +3498,7 @@
     <row r="24" spans="1:6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="13"/>
@@ -3068,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="8" t="s">
@@ -3080,15 +3524,15 @@
         <v>12</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>23</v>
@@ -3105,7 +3549,7 @@
         <v>33</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3132,18 +3576,18 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>154</v>
+        <v>452</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>31</v>
@@ -3160,18 +3604,18 @@
         <v>0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F37"/>
     </row>
@@ -3184,7 +3628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
@@ -3199,8 +3643,8 @@
     <col min="18" max="18" width="16.25" style="4" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19.375" style="4" customWidth="1"/>
-    <col min="21" max="21" width="39.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="36.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="52.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="46.875" style="4" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="28.75" style="4" bestFit="1" customWidth="1"/>
     <col min="24" max="27" width="22" style="4" customWidth="1"/>
     <col min="28" max="16384" width="9" style="4"/>
@@ -3211,7 +3655,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -3222,64 +3666,64 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="O2" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="X2" s="4" t="s">
         <v>20</v>
@@ -3291,66 +3735,66 @@
         <v>28</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="P3" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="U3" s="4" t="s">
         <v>19</v>
@@ -3376,13 +3820,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F4" s="4">
         <v>0.3</v>
@@ -3394,10 +3838,10 @@
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L4" s="4">
         <v>0.5</v>
@@ -3406,7 +3850,7 @@
         <v>120</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O4" s="4">
         <v>0.1</v>
@@ -3415,18 +3859,18 @@
         <v>1</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F5" s="4">
         <v>0.5</v>
@@ -3438,10 +3882,10 @@
         <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L5" s="4">
         <v>0.8</v>
@@ -3450,7 +3894,7 @@
         <v>180</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O5" s="4">
         <v>0.1</v>
@@ -3459,18 +3903,18 @@
         <v>1</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -3482,10 +3926,10 @@
         <v>10</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L6" s="4">
         <v>2</v>
@@ -3494,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O6" s="4">
         <v>0.1</v>
@@ -3503,65 +3947,65 @@
         <v>1</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I7" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="J7">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L7" s="4">
         <v>1</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="I8" t="s">
         <v>274</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="I8" t="s">
-        <v>278</v>
       </c>
       <c r="J8">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L8" s="4">
         <v>0.8</v>
@@ -3570,39 +4014,39 @@
         <v>0.2</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>332</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L9" s="4">
         <v>2</v>
@@ -3611,115 +4055,115 @@
         <v>1</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J10">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L10" s="4">
         <v>0.5</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J11">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L11" s="4">
         <v>0.4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J12">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L12" s="4">
         <v>2</v>
@@ -3728,36 +4172,36 @@
         <v>1</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L13" s="4">
         <v>99999</v>
@@ -3766,24 +4210,24 @@
         <v>1</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L14" s="4">
         <v>99999</v>
@@ -3792,15 +4236,15 @@
         <v>1</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>51</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F15" s="4">
         <v>3</v>
@@ -3812,7 +4256,7 @@
         <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L15" s="4">
         <v>0.4</v>
@@ -3821,21 +4265,21 @@
         <v>1</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O15" s="4">
         <v>0.5</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
@@ -3847,7 +4291,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L16" s="4">
         <v>1</v>
@@ -3856,21 +4300,21 @@
         <v>1</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -3882,7 +4326,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L17" s="4">
         <v>1</v>
@@ -3891,27 +4335,27 @@
         <v>1</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="O17" s="4">
         <v>1</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L18" s="4">
         <v>99999</v>
@@ -3920,123 +4364,123 @@
         <v>1</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R18" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="T18" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="S18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="T18" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="U18" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L19" s="4">
         <v>2</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>189</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F20" s="4">
         <v>1</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L20" s="4">
         <v>0.5</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F21" s="4">
         <v>5</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L21" s="4">
         <v>2</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F22" s="4">
         <v>5</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L22" s="4">
         <v>1</v>
@@ -4045,42 +4489,42 @@
         <v>0.2</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J23" s="4">
         <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L23" s="4">
         <v>1</v>
@@ -4089,45 +4533,45 @@
         <v>5</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="O23" s="4">
         <v>0.2</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F24" s="4">
         <v>5</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J24" s="4">
         <v>2</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L24" s="4">
         <v>1.5</v>
@@ -4136,109 +4580,109 @@
         <v>0.5</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O24" s="4">
         <v>0.2</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F25" s="4">
         <v>5</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J25" s="4">
         <v>2</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L25" s="4">
         <v>2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O25" s="4">
         <v>0.2</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L26" s="4">
         <v>99999</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F27" s="4">
         <v>5</v>
@@ -4250,27 +4694,27 @@
         <v>3</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L27" s="4">
         <v>1</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O27" s="4">
         <v>0.1</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F28" s="4">
         <v>5</v>
@@ -4279,27 +4723,27 @@
         <v>3</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L28" s="4">
         <v>1</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O28" s="4">
         <v>0.1</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F29" s="4">
         <v>5</v>
@@ -4308,27 +4752,30 @@
         <v>3</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L29" s="4">
         <v>1</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O29" s="4">
         <v>0.1</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>404</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F30" s="4">
         <v>1</v>
@@ -4340,10 +4787,10 @@
         <v>10</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="L30" s="4">
         <v>0.5</v>
@@ -4352,7 +4799,7 @@
         <v>120</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O30" s="4">
         <v>0.1</v>
@@ -4361,15 +4808,18 @@
         <v>1</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>405</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F31" s="4">
         <v>1</v>
@@ -4381,10 +4831,10 @@
         <v>10</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L31" s="4">
         <v>0.5</v>
@@ -4393,7 +4843,7 @@
         <v>130</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O31" s="4">
         <v>0.1</v>
@@ -4402,15 +4852,18 @@
         <v>1</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F32" s="4">
         <v>1</v>
@@ -4419,13 +4872,13 @@
         <v>1</v>
       </c>
       <c r="H32" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L32" s="4">
         <v>0.5</v>
@@ -4434,7 +4887,7 @@
         <v>140</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O32" s="4">
         <v>0.1</v>
@@ -4443,15 +4896,18 @@
         <v>1</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>407</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F33" s="4">
         <v>1</v>
@@ -4460,13 +4916,13 @@
         <v>1</v>
       </c>
       <c r="H33" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L33" s="4">
         <v>0.5</v>
@@ -4475,7 +4931,7 @@
         <v>140</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O33" s="4">
         <v>0.1</v>
@@ -4484,15 +4940,18 @@
         <v>1</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>408</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F34" s="4">
         <v>1</v>
@@ -4501,13 +4960,13 @@
         <v>1</v>
       </c>
       <c r="H34" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L34" s="4">
         <v>0.5</v>
@@ -4516,7 +4975,7 @@
         <v>150</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O34" s="4">
         <v>0.1</v>
@@ -4525,24 +4984,27 @@
         <v>1</v>
       </c>
       <c r="U34" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>356</v>
+        <v>388</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>409</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J35">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L35" s="4">
         <v>1</v>
@@ -4551,24 +5013,27 @@
         <v>1</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J36">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L36" s="4">
         <v>1</v>
@@ -4577,24 +5042,27 @@
         <v>1</v>
       </c>
       <c r="U36" s="4" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>411</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J37">
         <v>25</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L37" s="4">
         <v>1</v>
@@ -4603,24 +5071,27 @@
         <v>1</v>
       </c>
       <c r="U37" s="4" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.3">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>412</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J38">
         <v>30</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L38" s="4">
         <v>1</v>
@@ -4629,24 +5100,27 @@
         <v>1</v>
       </c>
       <c r="U38" s="4" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>413</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J39">
         <v>35</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L39" s="4">
         <v>1</v>
@@ -4655,7 +5129,472 @@
         <v>1</v>
       </c>
       <c r="U39" s="4" t="s">
-        <v>377</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B40" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L40" s="4">
+        <v>99999</v>
+      </c>
+      <c r="M40" s="4">
+        <v>1</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="V40" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L41" s="4">
+        <v>99999</v>
+      </c>
+      <c r="M41" s="4">
+        <v>1</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="V41" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L42" s="4">
+        <v>99999</v>
+      </c>
+      <c r="M42" s="4">
+        <v>1</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="V42" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B43" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L43" s="4">
+        <v>99999</v>
+      </c>
+      <c r="M43" s="4">
+        <v>1</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B44" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L44" s="4">
+        <v>99999</v>
+      </c>
+      <c r="M44" s="4">
+        <v>1</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="V44" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B45" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L45" s="4">
+        <v>1</v>
+      </c>
+      <c r="U45" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B46" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L46" s="4">
+        <v>1</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B47" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L47" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="U47" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B48" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L48" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B49" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L49" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B50" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="I50" t="s">
+        <v>274</v>
+      </c>
+      <c r="J50">
+        <v>10</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L50" s="4">
+        <v>1</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q50" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="T50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B51" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="I51" t="s">
+        <v>274</v>
+      </c>
+      <c r="J51" s="4">
+        <v>10</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L51" s="4">
+        <v>1</v>
+      </c>
+      <c r="M51" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q51" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R51" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="T51" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B52" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="I52" t="s">
+        <v>274</v>
+      </c>
+      <c r="J52" s="4">
+        <v>15</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L52" s="4">
+        <v>1</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R52" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="T52" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B53" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="I53" t="s">
+        <v>274</v>
+      </c>
+      <c r="J53" s="4">
+        <v>15</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L53" s="4">
+        <v>1</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q53" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R53" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="T53" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B54" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="I54" t="s">
+        <v>274</v>
+      </c>
+      <c r="J54" s="4">
+        <v>20</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L54" s="4">
+        <v>1</v>
+      </c>
+      <c r="M54" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q54" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="R54" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="T54" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -4667,16 +5606,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="37.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.25" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.75" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="17.375" style="4" customWidth="1"/>
     <col min="7" max="7" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="32.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="39" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.375" style="4" customWidth="1"/>
     <col min="11" max="11" width="19.25" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27.5" style="4" bestFit="1" customWidth="1"/>
@@ -4687,7 +5626,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>6</v>
@@ -4701,40 +5640,40 @@
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -4745,19 +5684,19 @@
         <v>5</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>5</v>
@@ -4783,22 +5722,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>40</v>
@@ -4807,7 +5746,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -4821,22 +5760,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>40</v>
@@ -4845,7 +5784,7 @@
         <v>50</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K5" s="4">
         <v>2</v>
@@ -4859,22 +5798,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>40</v>
@@ -4883,7 +5822,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6" s="4">
         <v>1</v>
@@ -4897,16 +5836,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>40</v>
@@ -4915,7 +5854,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="4">
         <v>1</v>
@@ -4923,16 +5862,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>40</v>
@@ -4941,7 +5880,7 @@
         <v>70</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="4">
         <v>1</v>
@@ -4949,22 +5888,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -4972,22 +5911,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K10" s="4">
         <v>1</v>
@@ -4995,16 +5934,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>40</v>
@@ -5013,7 +5952,7 @@
         <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -5021,16 +5960,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>40</v>
@@ -5039,7 +5978,7 @@
         <v>150</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K12" s="4">
         <v>1</v>
@@ -5047,25 +5986,25 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I13" s="4">
         <v>200</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>
@@ -5073,7 +6012,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>42</v>
@@ -5082,15 +6021,15 @@
         <v>10</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>43</v>
@@ -5099,10 +6038,10 @@
         <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="J15" s="4">
         <v>20</v>
@@ -5110,10 +6049,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>10</v>
@@ -5122,15 +6061,15 @@
         <v>22</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>10</v>
@@ -5139,7 +6078,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>72</v>
+        <v>440</v>
       </c>
       <c r="J17" s="4">
         <v>30</v>
@@ -5147,7 +6086,7 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>45</v>
@@ -5156,15 +6095,15 @@
         <v>10</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>44</v>
@@ -5173,10 +6112,10 @@
         <v>10</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J19" s="4">
         <v>20</v>
@@ -5184,22 +6123,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>12</v>
@@ -5208,7 +6147,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K20" s="4">
         <v>5</v>
@@ -5222,19 +6161,19 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J21" s="4">
         <v>2</v>
@@ -5242,19 +6181,19 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J22" s="4">
         <v>2</v>
@@ -5262,19 +6201,19 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J23" s="4">
         <v>30</v>
@@ -5282,22 +6221,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>12</v>
@@ -5306,7 +6245,7 @@
         <v>100</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K24" s="4">
         <v>3</v>
@@ -5320,22 +6259,22 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>12</v>
@@ -5344,7 +6283,7 @@
         <v>200</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K25" s="4">
         <v>1</v>
@@ -5358,22 +6297,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>12</v>
@@ -5382,7 +6321,7 @@
         <v>400</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K26" s="4">
         <v>1</v>
@@ -5396,22 +6335,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>12</v>
@@ -5420,7 +6359,7 @@
         <v>300</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K27" s="4">
         <v>1</v>
@@ -5431,19 +6370,19 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J28" s="4">
         <v>2</v>
@@ -5451,57 +6390,57 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I30" s="4">
         <v>3</v>
@@ -5510,42 +6449,42 @@
         <v>30</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M31" s="4">
         <v>0.1</v>
@@ -5553,22 +6492,22 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>12</v>
@@ -5577,7 +6516,7 @@
         <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K32" s="4">
         <v>1</v>
@@ -5585,28 +6524,28 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>363</v>
+        <v>486</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K33" s="4">
         <v>1</v>
@@ -5620,28 +6559,28 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>368</v>
+        <v>487</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K34" s="4">
         <v>1.25</v>
@@ -5655,28 +6594,28 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>369</v>
+        <v>488</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K35" s="4">
         <v>1.5</v>
@@ -5690,28 +6629,28 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K36" s="4">
         <v>1.75</v>
@@ -5725,28 +6664,28 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>371</v>
+        <v>490</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K37" s="4">
         <v>2</v>
@@ -5760,28 +6699,28 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>373</v>
+        <v>453</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>378</v>
+        <v>491</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K38" s="4">
         <v>2.5</v>
@@ -5789,28 +6728,28 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>379</v>
+        <v>492</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K39" s="4">
         <v>3</v>
@@ -5818,28 +6757,28 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>380</v>
+        <v>493</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K40" s="4">
         <v>3.5</v>
@@ -5847,28 +6786,28 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>381</v>
+        <v>494</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K41" s="4">
         <v>4</v>
@@ -5876,31 +6815,616 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>377</v>
+        <v>429</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>382</v>
+        <v>495</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K42" s="4">
         <v>4.